--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geral Diário" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Geral Diário" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="D3" t="n">
-        <v>2328</v>
+        <v>2296</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9725</v>
+        <v>0.9848</v>
       </c>
     </row>
     <row r="4">
@@ -514,10 +514,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>3370</v>
+        <v>3365</v>
       </c>
       <c r="D4" t="n">
-        <v>3370</v>
+        <v>3365</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>2740</v>
+        <v>2738</v>
       </c>
       <c r="D6" t="n">
-        <v>2742</v>
+        <v>2738</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9993000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -634,13 +634,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C11" t="n">
-        <v>2059</v>
+        <v>2054</v>
       </c>
       <c r="D11" t="n">
-        <v>2482</v>
+        <v>2476</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0.8295999999999999</v>
@@ -670,16 +670,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>3595</v>
+        <v>3626</v>
       </c>
       <c r="D13" t="n">
-        <v>3635</v>
+        <v>3629</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9890000000000001</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="14">
@@ -692,10 +692,10 @@
         <v>42</v>
       </c>
       <c r="C14" t="n">
-        <v>6779</v>
+        <v>6764</v>
       </c>
       <c r="D14" t="n">
-        <v>6821</v>
+        <v>6806</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0.9937999999999999</v>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="D3" t="n">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="E3" t="n">
-        <v>2328</v>
+        <v>2296</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9725</v>
+        <v>0.9848</v>
       </c>
     </row>
     <row r="4">
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3370</v>
+        <v>3365</v>
       </c>
       <c r="E4" t="n">
-        <v>3370</v>
+        <v>3365</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2740</v>
+        <v>2738</v>
       </c>
       <c r="E6" t="n">
-        <v>2742</v>
+        <v>2738</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9993000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D11" t="n">
-        <v>2059</v>
+        <v>2054</v>
       </c>
       <c r="E11" t="n">
-        <v>2482</v>
+        <v>2476</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0.8295999999999999</v>
@@ -1035,16 +1035,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>3595</v>
+        <v>3626</v>
       </c>
       <c r="E13" t="n">
-        <v>3635</v>
+        <v>3629</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9890000000000001</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="14">
@@ -1062,10 +1062,10 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>6779</v>
+        <v>6764</v>
       </c>
       <c r="E14" t="n">
-        <v>6821</v>
+        <v>6806</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0.9937999999999999</v>

--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>416</v>
       </c>
       <c r="C3" t="n">
-        <v>2261</v>
+        <v>3043</v>
       </c>
       <c r="D3" t="n">
-        <v>2296</v>
+        <v>3459</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9848</v>
+        <v>0.8797</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>3365</v>
+        <v>6565</v>
       </c>
       <c r="D4" t="n">
-        <v>3365</v>
+        <v>6593</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0.9958</v>
       </c>
     </row>
     <row r="5">
@@ -550,10 +550,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>2738</v>
+        <v>5381</v>
       </c>
       <c r="D6" t="n">
-        <v>2738</v>
+        <v>5381</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -617,15 +617,17 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2" t="n"/>
+        <v>94</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.9893999999999999</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -634,16 +636,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>422</v>
+        <v>462</v>
       </c>
       <c r="C11" t="n">
-        <v>2054</v>
+        <v>3992</v>
       </c>
       <c r="D11" t="n">
-        <v>2476</v>
+        <v>4454</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.8295999999999999</v>
+        <v>0.8963</v>
       </c>
     </row>
     <row r="12">
@@ -670,16 +672,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>3626</v>
+        <v>6838</v>
       </c>
       <c r="D13" t="n">
-        <v>3629</v>
+        <v>6845</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9992</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -689,16 +691,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C14" t="n">
-        <v>6764</v>
+        <v>11610</v>
       </c>
       <c r="D14" t="n">
-        <v>6806</v>
+        <v>11654</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9937999999999999</v>
+        <v>0.9962000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1093,8 +1095,330 @@
       </c>
       <c r="F15" s="2" t="n"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>381</v>
+      </c>
+      <c r="D17" t="n">
+        <v>782</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1163</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0.6724</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>28</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3228</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0.9913</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2643</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2643</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>93</v>
+      </c>
+      <c r="E24" t="n">
+        <v>94</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0.9893999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>40</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1938</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1978</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0.9798</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3212</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3216</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0.9987999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4846</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4848</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0.9995999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F15"/>
+  <autoFilter ref="A1:F29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="C3" t="n">
-        <v>3043</v>
+        <v>4286</v>
       </c>
       <c r="D3" t="n">
-        <v>3459</v>
+        <v>4716</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8797</v>
+        <v>0.9087999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="C4" t="n">
-        <v>6565</v>
+        <v>9362</v>
       </c>
       <c r="D4" t="n">
-        <v>6593</v>
+        <v>9478</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9958</v>
+        <v>0.9878</v>
       </c>
     </row>
     <row r="5">
@@ -550,10 +550,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>5381</v>
+        <v>6810</v>
       </c>
       <c r="D6" t="n">
-        <v>5381</v>
+        <v>6810</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -620,13 +620,13 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9932</v>
       </c>
     </row>
     <row r="11">
@@ -639,13 +639,13 @@
         <v>462</v>
       </c>
       <c r="C11" t="n">
-        <v>3992</v>
+        <v>4978</v>
       </c>
       <c r="D11" t="n">
-        <v>4454</v>
+        <v>5440</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.8963</v>
+        <v>0.9151</v>
       </c>
     </row>
     <row r="12">
@@ -675,13 +675,13 @@
         <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>6838</v>
+        <v>8763</v>
       </c>
       <c r="D13" t="n">
-        <v>6845</v>
+        <v>8770</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="14">
@@ -694,13 +694,13 @@
         <v>44</v>
       </c>
       <c r="C14" t="n">
-        <v>11610</v>
+        <v>14961</v>
       </c>
       <c r="D14" t="n">
-        <v>11654</v>
+        <v>15005</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9962000000000001</v>
+        <v>0.9971</v>
       </c>
     </row>
     <row r="15">
@@ -732,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1417,8 +1417,330 @@
       </c>
       <c r="F29" s="2" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>14</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1243</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1257</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0.9889</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>88</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2797</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2885</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.9695</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1429</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1429</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>54</v>
+      </c>
+      <c r="E38" t="n">
+        <v>54</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>986</v>
+      </c>
+      <c r="E39" t="n">
+        <v>986</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1925</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3351</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3351</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F29"/>
+  <autoFilter ref="A1:F43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C3" t="n">
-        <v>4286</v>
+        <v>12931</v>
       </c>
       <c r="D3" t="n">
-        <v>4716</v>
+        <v>13362</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9087999999999999</v>
+        <v>0.9677</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>116</v>
+        <v>319</v>
       </c>
       <c r="C4" t="n">
-        <v>9362</v>
+        <v>23828</v>
       </c>
       <c r="D4" t="n">
-        <v>9478</v>
+        <v>24147</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9878</v>
+        <v>0.9868000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -550,10 +550,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>6810</v>
+        <v>15885</v>
       </c>
       <c r="D6" t="n">
-        <v>6810</v>
+        <v>15885</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
@@ -620,13 +620,13 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>1292</v>
       </c>
       <c r="D10" t="n">
-        <v>148</v>
+        <v>1293</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9932</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="11">
@@ -639,13 +639,13 @@
         <v>462</v>
       </c>
       <c r="C11" t="n">
-        <v>4978</v>
+        <v>12996</v>
       </c>
       <c r="D11" t="n">
-        <v>5440</v>
+        <v>13458</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9151</v>
+        <v>0.9656999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -658,12 +658,14 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -672,16 +674,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>8763</v>
+        <v>20245</v>
       </c>
       <c r="D13" t="n">
-        <v>8770</v>
+        <v>20258</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9992</v>
+        <v>0.9994</v>
       </c>
     </row>
     <row r="14">
@@ -691,16 +693,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C14" t="n">
-        <v>14961</v>
+        <v>41400</v>
       </c>
       <c r="D14" t="n">
-        <v>15005</v>
+        <v>41459</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9971</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="15">
@@ -732,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -778,7 +780,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -800,7 +802,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -809,22 +811,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2261</v>
+        <v>143</v>
       </c>
       <c r="E3" t="n">
-        <v>2296</v>
+        <v>143</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9848</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -836,10 +838,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3365</v>
+        <v>471</v>
       </c>
       <c r="E4" t="n">
-        <v>3365</v>
+        <v>471</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
@@ -848,7 +850,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -870,7 +872,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -882,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2738</v>
+        <v>246</v>
       </c>
       <c r="E6" t="n">
-        <v>2738</v>
+        <v>246</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -894,7 +896,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -916,7 +918,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -938,7 +940,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -960,7 +962,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -982,7 +984,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -991,22 +993,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>422</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2054</v>
+        <v>287</v>
       </c>
       <c r="E11" t="n">
-        <v>2476</v>
+        <v>287</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.8295999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1028,7 +1030,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1037,22 +1039,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3626</v>
+        <v>292</v>
       </c>
       <c r="E13" t="n">
-        <v>3629</v>
+        <v>292</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9992</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1061,22 +1063,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>6764</v>
+        <v>1014</v>
       </c>
       <c r="E14" t="n">
-        <v>6806</v>
+        <v>1014</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9937999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1098,7 +1100,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1120,7 +1122,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1129,22 +1131,20 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>782</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1163</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>0.6724</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1153,22 +1153,20 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>3228</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>0.9913</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1190,7 +1188,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1202,19 +1200,17 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2643</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>2643</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1236,7 +1232,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1258,7 +1254,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1280,7 +1276,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1289,22 +1285,20 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>94</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>0.9893999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1313,22 +1307,20 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1938</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1978</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>0.9798</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1350,7 +1342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1359,22 +1351,20 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>3212</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>3216</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>0.9987999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1383,22 +1373,20 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>4846</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4848</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0.9995999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1420,7 +1408,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1442,7 +1430,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1451,22 +1439,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1243</v>
+        <v>2349</v>
       </c>
       <c r="E31" t="n">
-        <v>1257</v>
+        <v>2349</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.9889</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1475,22 +1463,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>2797</v>
+        <v>2845</v>
       </c>
       <c r="E32" t="n">
-        <v>2885</v>
+        <v>2845</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.9695</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1512,7 +1500,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1524,10 +1512,10 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1429</v>
+        <v>2294</v>
       </c>
       <c r="E34" t="n">
-        <v>1429</v>
+        <v>2294</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>1</v>
@@ -1536,7 +1524,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1558,7 +1546,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1580,7 +1568,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1602,7 +1590,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1614,19 +1602,17 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>54</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1638,10 +1624,10 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>986</v>
+        <v>1810</v>
       </c>
       <c r="E39" t="n">
-        <v>986</v>
+        <v>1810</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>1</v>
@@ -1650,7 +1636,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1672,7 +1658,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1684,10 +1670,10 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1925</v>
+        <v>2687</v>
       </c>
       <c r="E41" t="n">
-        <v>1925</v>
+        <v>2687</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
@@ -1696,7 +1682,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1708,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>3351</v>
+        <v>6080</v>
       </c>
       <c r="E42" t="n">
-        <v>3351</v>
+        <v>6080</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>1</v>
@@ -1720,27 +1706,3223 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1556</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1556</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3028</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3029</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0.9997</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1576</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1576</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1833</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1833</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1650</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3664</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3664</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1008</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2109</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2109</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1542</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1542</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1171</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1171</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1691</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3171</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3171</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1034</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1034</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1900</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>994</v>
+      </c>
+      <c r="E76" t="n">
+        <v>994</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1106</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1788</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1788</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3651</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3651</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1024</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1849</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1849</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>957</v>
+      </c>
+      <c r="E90" t="n">
+        <v>957</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1353</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1353</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1643</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1643</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>3498</v>
+      </c>
+      <c r="E98" t="n">
+        <v>3498</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>503</v>
+      </c>
+      <c r="E101" t="n">
+        <v>503</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>335</v>
+      </c>
+      <c r="E102" t="n">
+        <v>335</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>165</v>
+      </c>
+      <c r="E104" t="n">
+        <v>165</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>368</v>
+      </c>
+      <c r="E109" t="n">
+        <v>368</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>196</v>
+      </c>
+      <c r="E111" t="n">
+        <v>196</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>974</v>
+      </c>
+      <c r="E112" t="n">
+        <v>974</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>35</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2261</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2296</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>0.9848</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3365</v>
+      </c>
+      <c r="E130" t="n">
+        <v>3365</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2738</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2738</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>422</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2054</v>
+      </c>
+      <c r="E137" t="n">
+        <v>2476</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>0.8295999999999999</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>3</v>
+      </c>
+      <c r="D139" t="n">
+        <v>3626</v>
+      </c>
+      <c r="E139" t="n">
+        <v>3629</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>0.9992</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>42</v>
+      </c>
+      <c r="D140" t="n">
+        <v>6764</v>
+      </c>
+      <c r="E140" t="n">
+        <v>6806</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>0.9937999999999999</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>381</v>
+      </c>
+      <c r="D143" t="n">
+        <v>782</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1163</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>0.6724</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>28</v>
+      </c>
+      <c r="D144" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E144" t="n">
+        <v>3228</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>0.9913</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>2643</v>
+      </c>
+      <c r="E146" t="n">
+        <v>2643</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="n">
+        <v>93</v>
+      </c>
+      <c r="E150" t="n">
+        <v>94</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>0.9893999999999999</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>40</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1938</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1978</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>0.9798</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>4</v>
+      </c>
+      <c r="D153" t="n">
+        <v>3212</v>
+      </c>
+      <c r="E153" t="n">
+        <v>3216</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>0.9987999999999999</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>2</v>
+      </c>
+      <c r="D154" t="n">
+        <v>4846</v>
+      </c>
+      <c r="E154" t="n">
+        <v>4848</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>0.9995999999999999</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>14</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1243</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1257</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>0.9889</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>88</v>
+      </c>
+      <c r="D158" t="n">
+        <v>2797</v>
+      </c>
+      <c r="E158" t="n">
+        <v>2885</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>0.9695</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1429</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1429</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" t="n">
+        <v>54</v>
+      </c>
+      <c r="E164" t="n">
+        <v>54</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" t="n">
+        <v>986</v>
+      </c>
+      <c r="E165" t="n">
+        <v>986</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1925</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" t="n">
+        <v>3351</v>
+      </c>
+      <c r="E168" t="n">
+        <v>3351</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
         <is>
           <t>S-FREG-SP</t>
         </is>
       </c>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2" t="n"/>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1028</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1029</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>0.9990000000000001</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>202</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1929</v>
+      </c>
+      <c r="E172" t="n">
+        <v>2131</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>0.9052</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1301</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1301</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1145</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1145</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>90</v>
+      </c>
+      <c r="E179" t="n">
+        <v>90</v>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>6</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1535</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1541</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>0.9961</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>15</v>
+      </c>
+      <c r="D182" t="n">
+        <v>4387</v>
+      </c>
+      <c r="E182" t="n">
+        <v>4402</v>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>0.9965999999999999</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F43"/>
+  <autoFilter ref="A1:F183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>431</v>
+        <v>488</v>
       </c>
       <c r="C3" t="n">
-        <v>12931</v>
+        <v>13882</v>
       </c>
       <c r="D3" t="n">
-        <v>13362</v>
+        <v>14370</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9677</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="4">
@@ -514,13 +514,13 @@
         <v>319</v>
       </c>
       <c r="C4" t="n">
-        <v>23828</v>
+        <v>26122</v>
       </c>
       <c r="D4" t="n">
-        <v>24147</v>
+        <v>26441</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9868000000000001</v>
+        <v>0.9879000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C6" t="n">
-        <v>15885</v>
+        <v>16880</v>
       </c>
       <c r="D6" t="n">
-        <v>15885</v>
+        <v>16911</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0.9982</v>
       </c>
     </row>
     <row r="7">
@@ -620,13 +620,13 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1292</v>
+        <v>2378</v>
       </c>
       <c r="D10" t="n">
-        <v>1293</v>
+        <v>2379</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9992</v>
+        <v>0.9995999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -639,13 +639,13 @@
         <v>462</v>
       </c>
       <c r="C11" t="n">
-        <v>12996</v>
+        <v>13098</v>
       </c>
       <c r="D11" t="n">
-        <v>13458</v>
+        <v>13560</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9656999999999999</v>
+        <v>0.9659</v>
       </c>
     </row>
     <row r="12">
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="C13" t="n">
-        <v>20245</v>
+        <v>21539</v>
       </c>
       <c r="D13" t="n">
-        <v>20258</v>
+        <v>21662</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9994</v>
+        <v>0.9943000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -693,16 +693,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C14" t="n">
-        <v>41400</v>
+        <v>44870</v>
       </c>
       <c r="D14" t="n">
-        <v>41459</v>
+        <v>44950</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9986</v>
+        <v>0.9982</v>
       </c>
     </row>
     <row r="15">
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4921,8 +4921,330 @@
       </c>
       <c r="F183" s="2" t="n"/>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>57</v>
+      </c>
+      <c r="D185" t="n">
+        <v>951</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1008</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>0.9434999999999999</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2294</v>
+      </c>
+      <c r="E186" t="n">
+        <v>2294</v>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>31</v>
+      </c>
+      <c r="D188" t="n">
+        <v>995</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>0.9698</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1086</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1086</v>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" t="n">
+        <v>102</v>
+      </c>
+      <c r="E193" t="n">
+        <v>102</v>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>110</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1294</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1404</v>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>0.9217</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>21</v>
+      </c>
+      <c r="D196" t="n">
+        <v>3470</v>
+      </c>
+      <c r="E196" t="n">
+        <v>3491</v>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v>0.9940000000000001</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F183"/>
+  <autoFilter ref="A1:F197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$211</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>488</v>
       </c>
       <c r="C3" t="n">
-        <v>13882</v>
+        <v>14191</v>
       </c>
       <c r="D3" t="n">
-        <v>14370</v>
+        <v>14679</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.966</v>
+        <v>0.9668000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="C4" t="n">
-        <v>26122</v>
+        <v>27146</v>
       </c>
       <c r="D4" t="n">
-        <v>26441</v>
+        <v>27478</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.9879000000000001</v>
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C6" t="n">
-        <v>16880</v>
+        <v>17040</v>
       </c>
       <c r="D6" t="n">
-        <v>16911</v>
+        <v>17084</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9982</v>
+        <v>0.9974</v>
       </c>
     </row>
     <row r="7">
@@ -620,10 +620,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>2378</v>
+        <v>2644</v>
       </c>
       <c r="D10" t="n">
-        <v>2379</v>
+        <v>2645</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0.9995999999999999</v>
@@ -639,10 +639,10 @@
         <v>462</v>
       </c>
       <c r="C11" t="n">
-        <v>13098</v>
+        <v>13102</v>
       </c>
       <c r="D11" t="n">
-        <v>13560</v>
+        <v>13564</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0.9659</v>
@@ -677,13 +677,13 @@
         <v>123</v>
       </c>
       <c r="C13" t="n">
-        <v>21539</v>
+        <v>21935</v>
       </c>
       <c r="D13" t="n">
-        <v>21662</v>
+        <v>22058</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9943000000000001</v>
+        <v>0.9944</v>
       </c>
     </row>
     <row r="14">
@@ -693,16 +693,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="C14" t="n">
-        <v>44870</v>
+        <v>46086</v>
       </c>
       <c r="D14" t="n">
-        <v>44950</v>
+        <v>46183</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9982</v>
+        <v>0.9979</v>
       </c>
     </row>
     <row r="15">
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F197"/>
+  <dimension ref="A1:F211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5243,8 +5243,330 @@
       </c>
       <c r="F197" s="2" t="n"/>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" t="n">
+        <v>309</v>
+      </c>
+      <c r="E199" t="n">
+        <v>309</v>
+      </c>
+      <c r="F199" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>13</v>
+      </c>
+      <c r="D200" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1037</v>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>0.9875</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>13</v>
+      </c>
+      <c r="D202" t="n">
+        <v>160</v>
+      </c>
+      <c r="E202" t="n">
+        <v>173</v>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>0.9248999999999999</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" s="2" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" s="2" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>0</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" s="2" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" t="n">
+        <v>266</v>
+      </c>
+      <c r="E206" t="n">
+        <v>266</v>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" t="n">
+        <v>4</v>
+      </c>
+      <c r="E207" t="n">
+        <v>4</v>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" t="n">
+        <v>396</v>
+      </c>
+      <c r="E209" t="n">
+        <v>396</v>
+      </c>
+      <c r="F209" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>17</v>
+      </c>
+      <c r="D210" t="n">
+        <v>1216</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1233</v>
+      </c>
+      <c r="F210" s="2" t="n">
+        <v>0.9862000000000001</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>0</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F197"/>
+  <autoFilter ref="A1:F211"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$225</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F211"/>
+  <dimension ref="A1:F225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5565,8 +5565,316 @@
       </c>
       <c r="F211" s="2" t="n"/>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" s="2" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>0</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" s="2" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>0</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" s="2" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" s="2" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>0</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" s="2" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" s="2" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>0</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" s="2" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>0</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" s="2" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>0</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" s="2" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>0</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" s="2" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" s="2" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>0</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" s="2" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>0</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" s="2" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>0</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F211"/>
+  <autoFilter ref="A1:F225"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$239</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>488</v>
       </c>
       <c r="C3" t="n">
-        <v>14191</v>
+        <v>16254</v>
       </c>
       <c r="D3" t="n">
-        <v>14679</v>
+        <v>16742</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9668000000000001</v>
+        <v>0.9709</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>332</v>
+        <v>542</v>
       </c>
       <c r="C4" t="n">
-        <v>27146</v>
+        <v>30920</v>
       </c>
       <c r="D4" t="n">
-        <v>27478</v>
+        <v>31462</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9879000000000001</v>
+        <v>0.9828</v>
       </c>
     </row>
     <row r="5">
@@ -550,13 +550,13 @@
         <v>44</v>
       </c>
       <c r="C6" t="n">
-        <v>17040</v>
+        <v>19450</v>
       </c>
       <c r="D6" t="n">
-        <v>17084</v>
+        <v>19494</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9974</v>
+        <v>0.9976999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -620,13 +620,13 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>2644</v>
+        <v>4524</v>
       </c>
       <c r="D10" t="n">
-        <v>2645</v>
+        <v>4525</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="11">
@@ -639,13 +639,13 @@
         <v>462</v>
       </c>
       <c r="C11" t="n">
-        <v>13102</v>
+        <v>13401</v>
       </c>
       <c r="D11" t="n">
-        <v>13564</v>
+        <v>13863</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9659</v>
+        <v>0.9667</v>
       </c>
     </row>
     <row r="12">
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>123</v>
+        <v>220</v>
       </c>
       <c r="C13" t="n">
-        <v>21935</v>
+        <v>25115</v>
       </c>
       <c r="D13" t="n">
-        <v>22058</v>
+        <v>25335</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9944</v>
+        <v>0.9913</v>
       </c>
     </row>
     <row r="14">
@@ -693,16 +693,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>97</v>
+        <v>1863</v>
       </c>
       <c r="C14" t="n">
-        <v>46086</v>
+        <v>50892</v>
       </c>
       <c r="D14" t="n">
-        <v>46183</v>
+        <v>52755</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9979</v>
+        <v>0.9647</v>
       </c>
     </row>
     <row r="15">
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F225"/>
+  <dimension ref="A1:F239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5873,8 +5873,330 @@
       </c>
       <c r="F225" s="2" t="n"/>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" s="2" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>0</v>
+      </c>
+      <c r="D227" t="n">
+        <v>2063</v>
+      </c>
+      <c r="E227" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F227" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>210</v>
+      </c>
+      <c r="D228" t="n">
+        <v>3774</v>
+      </c>
+      <c r="E228" t="n">
+        <v>3984</v>
+      </c>
+      <c r="F228" s="2" t="n">
+        <v>0.9473</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>0</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" s="2" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>0</v>
+      </c>
+      <c r="D230" t="n">
+        <v>2410</v>
+      </c>
+      <c r="E230" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F230" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>0</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" s="2" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>0</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" s="2" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>0</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" s="2" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>0</v>
+      </c>
+      <c r="D234" t="n">
+        <v>1880</v>
+      </c>
+      <c r="E234" t="n">
+        <v>1880</v>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" t="n">
+        <v>299</v>
+      </c>
+      <c r="E235" t="n">
+        <v>299</v>
+      </c>
+      <c r="F235" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>97</v>
+      </c>
+      <c r="D237" t="n">
+        <v>3180</v>
+      </c>
+      <c r="E237" t="n">
+        <v>3277</v>
+      </c>
+      <c r="F237" s="2" t="n">
+        <v>0.9704</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>1766</v>
+      </c>
+      <c r="D238" t="n">
+        <v>4806</v>
+      </c>
+      <c r="E238" t="n">
+        <v>6572</v>
+      </c>
+      <c r="F238" s="2" t="n">
+        <v>0.7313</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>0</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F225"/>
+  <autoFilter ref="A1:F239"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$239</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$253</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C3" t="n">
-        <v>16254</v>
+        <v>18154</v>
       </c>
       <c r="D3" t="n">
-        <v>16742</v>
+        <v>18643</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9709</v>
+        <v>0.9738</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>542</v>
+        <v>634</v>
       </c>
       <c r="C4" t="n">
-        <v>30920</v>
+        <v>34454</v>
       </c>
       <c r="D4" t="n">
-        <v>31462</v>
+        <v>35088</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9828</v>
+        <v>0.9819</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="n">
-        <v>19450</v>
+        <v>21374</v>
       </c>
       <c r="D6" t="n">
-        <v>19494</v>
+        <v>21419</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9976999999999999</v>
+        <v>0.9979</v>
       </c>
     </row>
     <row r="7">
@@ -617,16 +617,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>4524</v>
+        <v>6054</v>
       </c>
       <c r="D10" t="n">
-        <v>4525</v>
+        <v>6059</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9998</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="11">
@@ -639,13 +639,13 @@
         <v>462</v>
       </c>
       <c r="C11" t="n">
-        <v>13401</v>
+        <v>13528</v>
       </c>
       <c r="D11" t="n">
-        <v>13863</v>
+        <v>13990</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9667</v>
+        <v>0.9670000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="C13" t="n">
-        <v>25115</v>
+        <v>27299</v>
       </c>
       <c r="D13" t="n">
-        <v>25335</v>
+        <v>27565</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9913</v>
+        <v>0.9904000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -693,16 +693,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1863</v>
+        <v>1878</v>
       </c>
       <c r="C14" t="n">
-        <v>50892</v>
+        <v>57242</v>
       </c>
       <c r="D14" t="n">
-        <v>52755</v>
+        <v>59120</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9647</v>
+        <v>0.9681999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -734,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F239"/>
+  <dimension ref="A1:F253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6195,8 +6195,330 @@
       </c>
       <c r="F239" s="2" t="n"/>
     </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" s="2" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>1</v>
+      </c>
+      <c r="D241" t="n">
+        <v>1900</v>
+      </c>
+      <c r="E241" t="n">
+        <v>1901</v>
+      </c>
+      <c r="F241" s="2" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>92</v>
+      </c>
+      <c r="D242" t="n">
+        <v>3534</v>
+      </c>
+      <c r="E242" t="n">
+        <v>3626</v>
+      </c>
+      <c r="F242" s="2" t="n">
+        <v>0.9745999999999999</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>0</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" s="2" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>1</v>
+      </c>
+      <c r="D244" t="n">
+        <v>1924</v>
+      </c>
+      <c r="E244" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F244" s="2" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>0</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" s="2" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>0</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" s="2" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" s="2" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>4</v>
+      </c>
+      <c r="D248" t="n">
+        <v>1530</v>
+      </c>
+      <c r="E248" t="n">
+        <v>1534</v>
+      </c>
+      <c r="F248" s="2" t="n">
+        <v>0.9974</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>0</v>
+      </c>
+      <c r="D249" t="n">
+        <v>127</v>
+      </c>
+      <c r="E249" t="n">
+        <v>127</v>
+      </c>
+      <c r="F249" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>0</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" s="2" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>46</v>
+      </c>
+      <c r="D251" t="n">
+        <v>2184</v>
+      </c>
+      <c r="E251" t="n">
+        <v>2230</v>
+      </c>
+      <c r="F251" s="2" t="n">
+        <v>0.9793999999999999</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>15</v>
+      </c>
+      <c r="D252" t="n">
+        <v>6350</v>
+      </c>
+      <c r="E252" t="n">
+        <v>6365</v>
+      </c>
+      <c r="F252" s="2" t="n">
+        <v>0.9976</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>0</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F239"/>
+  <autoFilter ref="A1:F253"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$253</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$267</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>489</v>
+        <v>567</v>
       </c>
       <c r="C3" t="n">
-        <v>18154</v>
+        <v>19299</v>
       </c>
       <c r="D3" t="n">
-        <v>18643</v>
+        <v>19866</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9738</v>
+        <v>0.9715</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="C4" t="n">
-        <v>34454</v>
+        <v>36751</v>
       </c>
       <c r="D4" t="n">
-        <v>35088</v>
+        <v>37396</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9819</v>
+        <v>0.9828</v>
       </c>
     </row>
     <row r="5">
@@ -550,13 +550,13 @@
         <v>45</v>
       </c>
       <c r="C6" t="n">
-        <v>21374</v>
+        <v>22532</v>
       </c>
       <c r="D6" t="n">
-        <v>21419</v>
+        <v>22577</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9979</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="7">
@@ -600,15 +600,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -617,16 +619,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>6054</v>
+        <v>7213</v>
       </c>
       <c r="D10" t="n">
-        <v>6059</v>
+        <v>7224</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9992</v>
+        <v>0.9984999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -639,13 +641,13 @@
         <v>462</v>
       </c>
       <c r="C11" t="n">
-        <v>13528</v>
+        <v>13637</v>
       </c>
       <c r="D11" t="n">
-        <v>13990</v>
+        <v>14099</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9670000000000001</v>
+        <v>0.9671999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -655,16 +657,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>191</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="13">
@@ -674,16 +676,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="C13" t="n">
-        <v>27299</v>
+        <v>29217</v>
       </c>
       <c r="D13" t="n">
-        <v>27565</v>
+        <v>29508</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9904000000000001</v>
+        <v>0.9901000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -693,16 +695,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1878</v>
+        <v>1889</v>
       </c>
       <c r="C14" t="n">
-        <v>57242</v>
+        <v>61254</v>
       </c>
       <c r="D14" t="n">
-        <v>59120</v>
+        <v>63143</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9701000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -734,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F253"/>
+  <dimension ref="A1:F267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6517,8 +6519,334 @@
       </c>
       <c r="F253" s="2" t="n"/>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>0</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" s="2" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>78</v>
+      </c>
+      <c r="D255" t="n">
+        <v>1145</v>
+      </c>
+      <c r="E255" t="n">
+        <v>1223</v>
+      </c>
+      <c r="F255" s="2" t="n">
+        <v>0.9362</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>11</v>
+      </c>
+      <c r="D256" t="n">
+        <v>2297</v>
+      </c>
+      <c r="E256" t="n">
+        <v>2308</v>
+      </c>
+      <c r="F256" s="2" t="n">
+        <v>0.9952</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>0</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" s="2" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>0</v>
+      </c>
+      <c r="D258" t="n">
+        <v>1158</v>
+      </c>
+      <c r="E258" t="n">
+        <v>1158</v>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>0</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" s="2" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>0</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+      <c r="F260" s="2" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>22</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="n">
+        <v>22</v>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>6</v>
+      </c>
+      <c r="D262" t="n">
+        <v>1159</v>
+      </c>
+      <c r="E262" t="n">
+        <v>1165</v>
+      </c>
+      <c r="F262" s="2" t="n">
+        <v>0.9948</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>0</v>
+      </c>
+      <c r="D263" t="n">
+        <v>109</v>
+      </c>
+      <c r="E263" t="n">
+        <v>109</v>
+      </c>
+      <c r="F263" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>188</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="n">
+        <v>188</v>
+      </c>
+      <c r="F264" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>25</v>
+      </c>
+      <c r="D265" t="n">
+        <v>1918</v>
+      </c>
+      <c r="E265" t="n">
+        <v>1943</v>
+      </c>
+      <c r="F265" s="2" t="n">
+        <v>0.9871</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>11</v>
+      </c>
+      <c r="D266" t="n">
+        <v>4012</v>
+      </c>
+      <c r="E266" t="n">
+        <v>4023</v>
+      </c>
+      <c r="F266" s="2" t="n">
+        <v>0.9973000000000001</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+      <c r="F267" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F253"/>
+  <autoFilter ref="A1:F267"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$281</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="C3" t="n">
-        <v>19299</v>
+        <v>20618</v>
       </c>
       <c r="D3" t="n">
-        <v>19866</v>
+        <v>21201</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9715</v>
+        <v>0.9725</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C4" t="n">
-        <v>36751</v>
+        <v>39017</v>
       </c>
       <c r="D4" t="n">
-        <v>37396</v>
+        <v>39666</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9828</v>
+        <v>0.9836</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C6" t="n">
-        <v>22532</v>
+        <v>23727</v>
       </c>
       <c r="D6" t="n">
-        <v>22577</v>
+        <v>23778</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.998</v>
+        <v>0.9979</v>
       </c>
     </row>
     <row r="7">
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -622,13 +622,13 @@
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>7213</v>
+        <v>8347</v>
       </c>
       <c r="D10" t="n">
-        <v>7224</v>
+        <v>8358</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9984999999999999</v>
+        <v>0.9987</v>
       </c>
     </row>
     <row r="11">
@@ -641,13 +641,13 @@
         <v>462</v>
       </c>
       <c r="C11" t="n">
-        <v>13637</v>
+        <v>13717</v>
       </c>
       <c r="D11" t="n">
-        <v>14099</v>
+        <v>14179</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9673999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -660,13 +660,13 @@
         <v>188</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.0157</v>
+        <v>0.08289999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -679,13 +679,13 @@
         <v>291</v>
       </c>
       <c r="C13" t="n">
-        <v>29217</v>
+        <v>31041</v>
       </c>
       <c r="D13" t="n">
-        <v>29508</v>
+        <v>31332</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9901000000000001</v>
+        <v>0.9906999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -695,16 +695,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1889</v>
+        <v>1983</v>
       </c>
       <c r="C14" t="n">
-        <v>61254</v>
+        <v>64981</v>
       </c>
       <c r="D14" t="n">
-        <v>63143</v>
+        <v>66964</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9701000000000001</v>
+        <v>0.9704</v>
       </c>
     </row>
     <row r="15">
@@ -736,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F267"/>
+  <dimension ref="A1:F281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6845,8 +6845,334 @@
       </c>
       <c r="F267" s="2" t="n"/>
     </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>0</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" s="2" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>16</v>
+      </c>
+      <c r="D269" t="n">
+        <v>1319</v>
+      </c>
+      <c r="E269" t="n">
+        <v>1335</v>
+      </c>
+      <c r="F269" s="2" t="n">
+        <v>0.988</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>4</v>
+      </c>
+      <c r="D270" t="n">
+        <v>2266</v>
+      </c>
+      <c r="E270" t="n">
+        <v>2270</v>
+      </c>
+      <c r="F270" s="2" t="n">
+        <v>0.9982</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>0</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" s="2" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>6</v>
+      </c>
+      <c r="D272" t="n">
+        <v>1195</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1201</v>
+      </c>
+      <c r="F272" s="2" t="n">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>0</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" s="2" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>0</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" s="2" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>1</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" t="n">
+        <v>1</v>
+      </c>
+      <c r="F275" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>0</v>
+      </c>
+      <c r="D276" t="n">
+        <v>1134</v>
+      </c>
+      <c r="E276" t="n">
+        <v>1134</v>
+      </c>
+      <c r="F276" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>0</v>
+      </c>
+      <c r="D277" t="n">
+        <v>80</v>
+      </c>
+      <c r="E277" t="n">
+        <v>80</v>
+      </c>
+      <c r="F277" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>0</v>
+      </c>
+      <c r="D278" t="n">
+        <v>14</v>
+      </c>
+      <c r="E278" t="n">
+        <v>14</v>
+      </c>
+      <c r="F278" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>0</v>
+      </c>
+      <c r="D279" t="n">
+        <v>1824</v>
+      </c>
+      <c r="E279" t="n">
+        <v>1824</v>
+      </c>
+      <c r="F279" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>94</v>
+      </c>
+      <c r="D280" t="n">
+        <v>3727</v>
+      </c>
+      <c r="E280" t="n">
+        <v>3821</v>
+      </c>
+      <c r="F280" s="2" t="n">
+        <v>0.9754</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>0</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F267"/>
+  <autoFilter ref="A1:F281"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$295</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>583</v>
       </c>
       <c r="C3" t="n">
-        <v>20618</v>
+        <v>21754</v>
       </c>
       <c r="D3" t="n">
-        <v>21201</v>
+        <v>22337</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9725</v>
+        <v>0.9739</v>
       </c>
     </row>
     <row r="4">
@@ -514,13 +514,13 @@
         <v>649</v>
       </c>
       <c r="C4" t="n">
-        <v>39017</v>
+        <v>40819</v>
       </c>
       <c r="D4" t="n">
-        <v>39666</v>
+        <v>41468</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9836</v>
+        <v>0.9843000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C6" t="n">
-        <v>23727</v>
+        <v>24711</v>
       </c>
       <c r="D6" t="n">
-        <v>23778</v>
+        <v>24764</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0.9979</v>
@@ -583,15 +583,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="n"/>
+        <v>69</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.971</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -600,13 +602,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -619,16 +621,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>8347</v>
+        <v>9345</v>
       </c>
       <c r="D10" t="n">
-        <v>8358</v>
+        <v>9373</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9987</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="11">
@@ -641,13 +643,13 @@
         <v>462</v>
       </c>
       <c r="C11" t="n">
-        <v>13717</v>
+        <v>13830</v>
       </c>
       <c r="D11" t="n">
-        <v>14179</v>
+        <v>14292</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9673999999999999</v>
+        <v>0.9677</v>
       </c>
     </row>
     <row r="12">
@@ -676,16 +678,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="C13" t="n">
-        <v>31041</v>
+        <v>32356</v>
       </c>
       <c r="D13" t="n">
-        <v>31332</v>
+        <v>32675</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9906999999999999</v>
+        <v>0.9902</v>
       </c>
     </row>
     <row r="14">
@@ -695,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1983</v>
+        <v>2010</v>
       </c>
       <c r="C14" t="n">
-        <v>64981</v>
+        <v>70886</v>
       </c>
       <c r="D14" t="n">
-        <v>66964</v>
+        <v>72896</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9704</v>
+        <v>0.9723999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -736,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F281"/>
+  <dimension ref="A1:F295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7171,8 +7173,334 @@
       </c>
       <c r="F281" s="2" t="n"/>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>0</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" s="2" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>0</v>
+      </c>
+      <c r="D283" t="n">
+        <v>1136</v>
+      </c>
+      <c r="E283" t="n">
+        <v>1136</v>
+      </c>
+      <c r="F283" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>0</v>
+      </c>
+      <c r="D284" t="n">
+        <v>1802</v>
+      </c>
+      <c r="E284" t="n">
+        <v>1802</v>
+      </c>
+      <c r="F284" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>0</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" s="2" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>2</v>
+      </c>
+      <c r="D286" t="n">
+        <v>984</v>
+      </c>
+      <c r="E286" t="n">
+        <v>986</v>
+      </c>
+      <c r="F286" s="2" t="n">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>0</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" t="n">
+        <v>0</v>
+      </c>
+      <c r="F287" s="2" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>2</v>
+      </c>
+      <c r="D288" t="n">
+        <v>67</v>
+      </c>
+      <c r="E288" t="n">
+        <v>69</v>
+      </c>
+      <c r="F288" s="2" t="n">
+        <v>0.971</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>13</v>
+      </c>
+      <c r="D289" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" t="n">
+        <v>13</v>
+      </c>
+      <c r="F289" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>17</v>
+      </c>
+      <c r="D290" t="n">
+        <v>998</v>
+      </c>
+      <c r="E290" t="n">
+        <v>1015</v>
+      </c>
+      <c r="F290" s="2" t="n">
+        <v>0.9833</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>0</v>
+      </c>
+      <c r="D291" t="n">
+        <v>113</v>
+      </c>
+      <c r="E291" t="n">
+        <v>113</v>
+      </c>
+      <c r="F291" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>0</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" t="n">
+        <v>0</v>
+      </c>
+      <c r="F292" s="2" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>28</v>
+      </c>
+      <c r="D293" t="n">
+        <v>1315</v>
+      </c>
+      <c r="E293" t="n">
+        <v>1343</v>
+      </c>
+      <c r="F293" s="2" t="n">
+        <v>0.9792000000000001</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>27</v>
+      </c>
+      <c r="D294" t="n">
+        <v>5905</v>
+      </c>
+      <c r="E294" t="n">
+        <v>5932</v>
+      </c>
+      <c r="F294" s="2" t="n">
+        <v>0.9954000000000001</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>0</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0</v>
+      </c>
+      <c r="F295" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F281"/>
+  <autoFilter ref="A1:F295"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$309</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>583</v>
       </c>
       <c r="C3" t="n">
-        <v>21754</v>
+        <v>22164</v>
       </c>
       <c r="D3" t="n">
-        <v>22337</v>
+        <v>22747</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9739</v>
+        <v>0.9743999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -514,13 +514,13 @@
         <v>649</v>
       </c>
       <c r="C4" t="n">
-        <v>40819</v>
+        <v>41438</v>
       </c>
       <c r="D4" t="n">
-        <v>41468</v>
+        <v>42087</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9843000000000001</v>
+        <v>0.9845999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C6" t="n">
-        <v>24711</v>
+        <v>24807</v>
       </c>
       <c r="D6" t="n">
-        <v>24764</v>
+        <v>24862</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9979</v>
+        <v>0.9978</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
         <v>67</v>
       </c>
       <c r="D8" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.971</v>
+        <v>0.9054000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -621,16 +621,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>9345</v>
+        <v>9871</v>
       </c>
       <c r="D10" t="n">
-        <v>9373</v>
+        <v>9906</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.997</v>
+        <v>0.9965000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -640,16 +640,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="C11" t="n">
-        <v>13830</v>
+        <v>13884</v>
       </c>
       <c r="D11" t="n">
-        <v>14292</v>
+        <v>14356</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9677</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C13" t="n">
-        <v>32356</v>
+        <v>32644</v>
       </c>
       <c r="D13" t="n">
-        <v>32675</v>
+        <v>32964</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9902</v>
+        <v>0.9903</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2010</v>
+        <v>2249</v>
       </c>
       <c r="C14" t="n">
-        <v>70886</v>
+        <v>72842</v>
       </c>
       <c r="D14" t="n">
-        <v>72896</v>
+        <v>75091</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9723999999999999</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F295"/>
+  <dimension ref="A1:F309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7499,8 +7499,334 @@
       </c>
       <c r="F295" s="2" t="n"/>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>0</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0</v>
+      </c>
+      <c r="F296" s="2" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>0</v>
+      </c>
+      <c r="D297" t="n">
+        <v>410</v>
+      </c>
+      <c r="E297" t="n">
+        <v>410</v>
+      </c>
+      <c r="F297" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>0</v>
+      </c>
+      <c r="D298" t="n">
+        <v>619</v>
+      </c>
+      <c r="E298" t="n">
+        <v>619</v>
+      </c>
+      <c r="F298" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>0</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0</v>
+      </c>
+      <c r="F299" s="2" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>2</v>
+      </c>
+      <c r="D300" t="n">
+        <v>96</v>
+      </c>
+      <c r="E300" t="n">
+        <v>98</v>
+      </c>
+      <c r="F300" s="2" t="n">
+        <v>0.9795999999999999</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>0</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" t="n">
+        <v>0</v>
+      </c>
+      <c r="F301" s="2" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>5</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" t="n">
+        <v>5</v>
+      </c>
+      <c r="F302" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>9</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" t="n">
+        <v>9</v>
+      </c>
+      <c r="F303" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>7</v>
+      </c>
+      <c r="D304" t="n">
+        <v>526</v>
+      </c>
+      <c r="E304" t="n">
+        <v>533</v>
+      </c>
+      <c r="F304" s="2" t="n">
+        <v>0.9869</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>10</v>
+      </c>
+      <c r="D305" t="n">
+        <v>54</v>
+      </c>
+      <c r="E305" t="n">
+        <v>64</v>
+      </c>
+      <c r="F305" s="2" t="n">
+        <v>0.8438</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>0</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="n">
+        <v>0</v>
+      </c>
+      <c r="F306" s="2" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>1</v>
+      </c>
+      <c r="D307" t="n">
+        <v>288</v>
+      </c>
+      <c r="E307" t="n">
+        <v>289</v>
+      </c>
+      <c r="F307" s="2" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>239</v>
+      </c>
+      <c r="D308" t="n">
+        <v>1956</v>
+      </c>
+      <c r="E308" t="n">
+        <v>2195</v>
+      </c>
+      <c r="F308" s="2" t="n">
+        <v>0.8911</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>0</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0</v>
+      </c>
+      <c r="F309" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F295"/>
+  <autoFilter ref="A1:F309"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$309</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$323</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F309"/>
+  <dimension ref="A1:F323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7825,8 +7825,316 @@
       </c>
       <c r="F309" s="2" t="n"/>
     </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>0</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" t="n">
+        <v>0</v>
+      </c>
+      <c r="F310" s="2" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>0</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0</v>
+      </c>
+      <c r="E311" t="n">
+        <v>0</v>
+      </c>
+      <c r="F311" s="2" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>0</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0</v>
+      </c>
+      <c r="E312" t="n">
+        <v>0</v>
+      </c>
+      <c r="F312" s="2" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>0</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" t="n">
+        <v>0</v>
+      </c>
+      <c r="F313" s="2" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>0</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" t="n">
+        <v>0</v>
+      </c>
+      <c r="F314" s="2" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>0</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0</v>
+      </c>
+      <c r="E315" t="n">
+        <v>0</v>
+      </c>
+      <c r="F315" s="2" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>0</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0</v>
+      </c>
+      <c r="E316" t="n">
+        <v>0</v>
+      </c>
+      <c r="F316" s="2" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>0</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0</v>
+      </c>
+      <c r="E317" t="n">
+        <v>0</v>
+      </c>
+      <c r="F317" s="2" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>0</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0</v>
+      </c>
+      <c r="E318" t="n">
+        <v>0</v>
+      </c>
+      <c r="F318" s="2" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>0</v>
+      </c>
+      <c r="D319" t="n">
+        <v>0</v>
+      </c>
+      <c r="E319" t="n">
+        <v>0</v>
+      </c>
+      <c r="F319" s="2" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>0</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" t="n">
+        <v>0</v>
+      </c>
+      <c r="F320" s="2" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>0</v>
+      </c>
+      <c r="D321" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" t="n">
+        <v>0</v>
+      </c>
+      <c r="F321" s="2" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>0</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0</v>
+      </c>
+      <c r="E322" t="n">
+        <v>0</v>
+      </c>
+      <c r="F322" s="2" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>0</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>0</v>
+      </c>
+      <c r="F323" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F309"/>
+  <autoFilter ref="A1:F323"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$323</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$337</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>583</v>
+        <v>640</v>
       </c>
       <c r="C3" t="n">
-        <v>22164</v>
+        <v>24551</v>
       </c>
       <c r="D3" t="n">
-        <v>22747</v>
+        <v>25191</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9743999999999999</v>
+        <v>0.9745999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C4" t="n">
-        <v>41438</v>
+        <v>45212</v>
       </c>
       <c r="D4" t="n">
-        <v>42087</v>
+        <v>45863</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9845999999999999</v>
+        <v>0.9858</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6" t="n">
-        <v>24807</v>
+        <v>27510</v>
       </c>
       <c r="D6" t="n">
-        <v>24862</v>
+        <v>27566</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9978</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>208</v>
       </c>
       <c r="D8" t="n">
-        <v>74</v>
+        <v>260</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9054000000000001</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -621,16 +621,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>9871</v>
+        <v>12258</v>
       </c>
       <c r="D10" t="n">
-        <v>9906</v>
+        <v>12294</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9971</v>
       </c>
     </row>
     <row r="11">
@@ -643,13 +643,13 @@
         <v>472</v>
       </c>
       <c r="C11" t="n">
-        <v>13884</v>
+        <v>14142</v>
       </c>
       <c r="D11" t="n">
-        <v>14356</v>
+        <v>14614</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9671</v>
+        <v>0.9677</v>
       </c>
     </row>
     <row r="12">
@@ -681,13 +681,13 @@
         <v>320</v>
       </c>
       <c r="C13" t="n">
-        <v>32644</v>
+        <v>35425</v>
       </c>
       <c r="D13" t="n">
-        <v>32964</v>
+        <v>35745</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9903</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2249</v>
+        <v>2534</v>
       </c>
       <c r="C14" t="n">
-        <v>72842</v>
+        <v>83949</v>
       </c>
       <c r="D14" t="n">
-        <v>75091</v>
+        <v>86483</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.97</v>
+        <v>0.9706999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F323"/>
+  <dimension ref="A1:F337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8133,8 +8133,334 @@
       </c>
       <c r="F323" s="2" t="n"/>
     </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>0</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" t="n">
+        <v>0</v>
+      </c>
+      <c r="F324" s="2" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>57</v>
+      </c>
+      <c r="D325" t="n">
+        <v>2387</v>
+      </c>
+      <c r="E325" t="n">
+        <v>2444</v>
+      </c>
+      <c r="F325" s="2" t="n">
+        <v>0.9767</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>2</v>
+      </c>
+      <c r="D326" t="n">
+        <v>3774</v>
+      </c>
+      <c r="E326" t="n">
+        <v>3776</v>
+      </c>
+      <c r="F326" s="2" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>0</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0</v>
+      </c>
+      <c r="E327" t="n">
+        <v>0</v>
+      </c>
+      <c r="F327" s="2" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>1</v>
+      </c>
+      <c r="D328" t="n">
+        <v>2703</v>
+      </c>
+      <c r="E328" t="n">
+        <v>2704</v>
+      </c>
+      <c r="F328" s="2" t="n">
+        <v>0.9995999999999999</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>0</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0</v>
+      </c>
+      <c r="E329" t="n">
+        <v>0</v>
+      </c>
+      <c r="F329" s="2" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>45</v>
+      </c>
+      <c r="D330" t="n">
+        <v>141</v>
+      </c>
+      <c r="E330" t="n">
+        <v>186</v>
+      </c>
+      <c r="F330" s="2" t="n">
+        <v>0.7581</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>17</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0</v>
+      </c>
+      <c r="E331" t="n">
+        <v>17</v>
+      </c>
+      <c r="F331" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>1</v>
+      </c>
+      <c r="D332" t="n">
+        <v>2387</v>
+      </c>
+      <c r="E332" t="n">
+        <v>2388</v>
+      </c>
+      <c r="F332" s="2" t="n">
+        <v>0.9995999999999999</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>0</v>
+      </c>
+      <c r="D333" t="n">
+        <v>258</v>
+      </c>
+      <c r="E333" t="n">
+        <v>258</v>
+      </c>
+      <c r="F333" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>0</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" t="n">
+        <v>0</v>
+      </c>
+      <c r="F334" s="2" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>0</v>
+      </c>
+      <c r="D335" t="n">
+        <v>2781</v>
+      </c>
+      <c r="E335" t="n">
+        <v>2781</v>
+      </c>
+      <c r="F335" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>285</v>
+      </c>
+      <c r="D336" t="n">
+        <v>11107</v>
+      </c>
+      <c r="E336" t="n">
+        <v>11392</v>
+      </c>
+      <c r="F336" s="2" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>0</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0</v>
+      </c>
+      <c r="E337" t="n">
+        <v>0</v>
+      </c>
+      <c r="F337" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F323"/>
+  <autoFilter ref="A1:F337"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$337</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$351</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C3" t="n">
-        <v>24551</v>
+        <v>25774</v>
       </c>
       <c r="D3" t="n">
-        <v>25191</v>
+        <v>26418</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9745999999999999</v>
+        <v>0.9756</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C4" t="n">
-        <v>45212</v>
+        <v>48026</v>
       </c>
       <c r="D4" t="n">
-        <v>45863</v>
+        <v>48679</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9858</v>
+        <v>0.9865999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C6" t="n">
-        <v>27510</v>
+        <v>29558</v>
       </c>
       <c r="D6" t="n">
-        <v>27566</v>
+        <v>29623</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.998</v>
+        <v>0.9978</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>208</v>
+        <v>649</v>
       </c>
       <c r="D8" t="n">
-        <v>260</v>
+        <v>770</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8</v>
+        <v>0.8429000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -621,16 +621,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>12258</v>
+        <v>13579</v>
       </c>
       <c r="D10" t="n">
-        <v>12294</v>
+        <v>13637</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9971</v>
+        <v>0.9956999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -643,13 +643,13 @@
         <v>472</v>
       </c>
       <c r="C11" t="n">
-        <v>14142</v>
+        <v>14282</v>
       </c>
       <c r="D11" t="n">
-        <v>14614</v>
+        <v>14754</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9677</v>
+        <v>0.968</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C13" t="n">
-        <v>35425</v>
+        <v>37534</v>
       </c>
       <c r="D13" t="n">
-        <v>35745</v>
+        <v>37857</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.991</v>
+        <v>0.9915</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2534</v>
+        <v>2675</v>
       </c>
       <c r="C14" t="n">
-        <v>83949</v>
+        <v>91653</v>
       </c>
       <c r="D14" t="n">
-        <v>86483</v>
+        <v>94328</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9706999999999999</v>
+        <v>0.9716</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F337"/>
+  <dimension ref="A1:F351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8459,8 +8459,332 @@
       </c>
       <c r="F337" s="2" t="n"/>
     </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>0</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+      <c r="F338" s="2" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>4</v>
+      </c>
+      <c r="D339" t="n">
+        <v>1223</v>
+      </c>
+      <c r="E339" t="n">
+        <v>1227</v>
+      </c>
+      <c r="F339" s="2" t="n">
+        <v>0.9967</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>2</v>
+      </c>
+      <c r="D340" t="n">
+        <v>2814</v>
+      </c>
+      <c r="E340" t="n">
+        <v>2816</v>
+      </c>
+      <c r="F340" s="2" t="n">
+        <v>0.9993000000000001</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>0</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" t="n">
+        <v>0</v>
+      </c>
+      <c r="F341" s="2" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>9</v>
+      </c>
+      <c r="D342" t="n">
+        <v>2048</v>
+      </c>
+      <c r="E342" t="n">
+        <v>2057</v>
+      </c>
+      <c r="F342" s="2" t="n">
+        <v>0.9956</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>0</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0</v>
+      </c>
+      <c r="E343" t="n">
+        <v>0</v>
+      </c>
+      <c r="F343" s="2" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>69</v>
+      </c>
+      <c r="D344" t="n">
+        <v>441</v>
+      </c>
+      <c r="E344" t="n">
+        <v>510</v>
+      </c>
+      <c r="F344" s="2" t="n">
+        <v>0.8647</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>0</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0</v>
+      </c>
+      <c r="E345" t="n">
+        <v>0</v>
+      </c>
+      <c r="F345" s="2" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>22</v>
+      </c>
+      <c r="D346" t="n">
+        <v>1321</v>
+      </c>
+      <c r="E346" t="n">
+        <v>1343</v>
+      </c>
+      <c r="F346" s="2" t="n">
+        <v>0.9836</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>0</v>
+      </c>
+      <c r="D347" t="n">
+        <v>140</v>
+      </c>
+      <c r="E347" t="n">
+        <v>140</v>
+      </c>
+      <c r="F347" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>0</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0</v>
+      </c>
+      <c r="E348" t="n">
+        <v>0</v>
+      </c>
+      <c r="F348" s="2" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>3</v>
+      </c>
+      <c r="D349" t="n">
+        <v>2109</v>
+      </c>
+      <c r="E349" t="n">
+        <v>2112</v>
+      </c>
+      <c r="F349" s="2" t="n">
+        <v>0.9986</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>141</v>
+      </c>
+      <c r="D350" t="n">
+        <v>7704</v>
+      </c>
+      <c r="E350" t="n">
+        <v>7845</v>
+      </c>
+      <c r="F350" s="2" t="n">
+        <v>0.982</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>0</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" t="n">
+        <v>0</v>
+      </c>
+      <c r="F351" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F337"/>
+  <autoFilter ref="A1:F351"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$351</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$365</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>644</v>
       </c>
       <c r="C3" t="n">
-        <v>25774</v>
+        <v>26958</v>
       </c>
       <c r="D3" t="n">
-        <v>26418</v>
+        <v>27602</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9756</v>
+        <v>0.9767</v>
       </c>
     </row>
     <row r="4">
@@ -514,13 +514,13 @@
         <v>653</v>
       </c>
       <c r="C4" t="n">
-        <v>48026</v>
+        <v>49706</v>
       </c>
       <c r="D4" t="n">
-        <v>48679</v>
+        <v>50359</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9865999999999999</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C6" t="n">
-        <v>29558</v>
+        <v>31169</v>
       </c>
       <c r="D6" t="n">
-        <v>29623</v>
+        <v>31250</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9978</v>
+        <v>0.9974</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>265</v>
       </c>
       <c r="C8" t="n">
-        <v>649</v>
+        <v>968</v>
       </c>
       <c r="D8" t="n">
-        <v>770</v>
+        <v>1233</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8429000000000001</v>
+        <v>0.7851</v>
       </c>
     </row>
     <row r="9">
@@ -621,16 +621,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C10" t="n">
-        <v>13579</v>
+        <v>14534</v>
       </c>
       <c r="D10" t="n">
-        <v>13637</v>
+        <v>14612</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9956999999999999</v>
+        <v>0.9947</v>
       </c>
     </row>
     <row r="11">
@@ -643,13 +643,13 @@
         <v>472</v>
       </c>
       <c r="C11" t="n">
-        <v>14282</v>
+        <v>14408</v>
       </c>
       <c r="D11" t="n">
-        <v>14754</v>
+        <v>14880</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.968</v>
+        <v>0.9682999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -681,13 +681,13 @@
         <v>323</v>
       </c>
       <c r="C13" t="n">
-        <v>37534</v>
+        <v>38921</v>
       </c>
       <c r="D13" t="n">
-        <v>37857</v>
+        <v>39244</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9915</v>
+        <v>0.9918</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2675</v>
+        <v>2715</v>
       </c>
       <c r="C14" t="n">
-        <v>91653</v>
+        <v>98426</v>
       </c>
       <c r="D14" t="n">
-        <v>94328</v>
+        <v>101141</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9716</v>
+        <v>0.9732</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F351"/>
+  <dimension ref="A1:F365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8783,8 +8783,332 @@
       </c>
       <c r="F351" s="2" t="n"/>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>0</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" t="n">
+        <v>0</v>
+      </c>
+      <c r="F352" s="2" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>0</v>
+      </c>
+      <c r="D353" t="n">
+        <v>1184</v>
+      </c>
+      <c r="E353" t="n">
+        <v>1184</v>
+      </c>
+      <c r="F353" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>0</v>
+      </c>
+      <c r="D354" t="n">
+        <v>1680</v>
+      </c>
+      <c r="E354" t="n">
+        <v>1680</v>
+      </c>
+      <c r="F354" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>0</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" t="n">
+        <v>0</v>
+      </c>
+      <c r="F355" s="2" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>16</v>
+      </c>
+      <c r="D356" t="n">
+        <v>1611</v>
+      </c>
+      <c r="E356" t="n">
+        <v>1627</v>
+      </c>
+      <c r="F356" s="2" t="n">
+        <v>0.9902</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>0</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0</v>
+      </c>
+      <c r="E357" t="n">
+        <v>0</v>
+      </c>
+      <c r="F357" s="2" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>144</v>
+      </c>
+      <c r="D358" t="n">
+        <v>319</v>
+      </c>
+      <c r="E358" t="n">
+        <v>463</v>
+      </c>
+      <c r="F358" s="2" t="n">
+        <v>0.6890000000000001</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>0</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0</v>
+      </c>
+      <c r="E359" t="n">
+        <v>0</v>
+      </c>
+      <c r="F359" s="2" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>20</v>
+      </c>
+      <c r="D360" t="n">
+        <v>955</v>
+      </c>
+      <c r="E360" t="n">
+        <v>975</v>
+      </c>
+      <c r="F360" s="2" t="n">
+        <v>0.9795</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>0</v>
+      </c>
+      <c r="D361" t="n">
+        <v>126</v>
+      </c>
+      <c r="E361" t="n">
+        <v>126</v>
+      </c>
+      <c r="F361" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>0</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0</v>
+      </c>
+      <c r="E362" t="n">
+        <v>0</v>
+      </c>
+      <c r="F362" s="2" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>0</v>
+      </c>
+      <c r="D363" t="n">
+        <v>1387</v>
+      </c>
+      <c r="E363" t="n">
+        <v>1387</v>
+      </c>
+      <c r="F363" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>40</v>
+      </c>
+      <c r="D364" t="n">
+        <v>6773</v>
+      </c>
+      <c r="E364" t="n">
+        <v>6813</v>
+      </c>
+      <c r="F364" s="2" t="n">
+        <v>0.9941</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>0</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0</v>
+      </c>
+      <c r="E365" t="n">
+        <v>0</v>
+      </c>
+      <c r="F365" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F351"/>
+  <autoFilter ref="A1:F365"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$365</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$379</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>644</v>
       </c>
       <c r="C3" t="n">
-        <v>26958</v>
+        <v>28046</v>
       </c>
       <c r="D3" t="n">
-        <v>27602</v>
+        <v>28690</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9767</v>
+        <v>0.9776</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>653</v>
+        <v>687</v>
       </c>
       <c r="C4" t="n">
-        <v>49706</v>
+        <v>51495</v>
       </c>
       <c r="D4" t="n">
-        <v>50359</v>
+        <v>52182</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.987</v>
+        <v>0.9868000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>31169</v>
+        <v>32780</v>
       </c>
       <c r="D6" t="n">
-        <v>31250</v>
+        <v>32891</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9974</v>
+        <v>0.9965999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>265</v>
+        <v>380</v>
       </c>
       <c r="C8" t="n">
-        <v>968</v>
+        <v>1265</v>
       </c>
       <c r="D8" t="n">
-        <v>1233</v>
+        <v>1645</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7851</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="9">
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -621,16 +621,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>14534</v>
+        <v>16049</v>
       </c>
       <c r="D10" t="n">
-        <v>14612</v>
+        <v>16155</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9947</v>
+        <v>0.9934000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -640,16 +640,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C11" t="n">
-        <v>14408</v>
+        <v>14590</v>
       </c>
       <c r="D11" t="n">
-        <v>14880</v>
+        <v>15063</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9682999999999999</v>
+        <v>0.9686</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>323</v>
+        <v>365</v>
       </c>
       <c r="C13" t="n">
-        <v>38921</v>
+        <v>40280</v>
       </c>
       <c r="D13" t="n">
-        <v>39244</v>
+        <v>40645</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9918</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2715</v>
+        <v>2736</v>
       </c>
       <c r="C14" t="n">
-        <v>98426</v>
+        <v>104213</v>
       </c>
       <c r="D14" t="n">
-        <v>101141</v>
+        <v>106949</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9732</v>
+        <v>0.9743999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F365"/>
+  <dimension ref="A1:F379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9107,8 +9107,334 @@
       </c>
       <c r="F365" s="2" t="n"/>
     </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>0</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0</v>
+      </c>
+      <c r="E366" t="n">
+        <v>0</v>
+      </c>
+      <c r="F366" s="2" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>0</v>
+      </c>
+      <c r="D367" t="n">
+        <v>1088</v>
+      </c>
+      <c r="E367" t="n">
+        <v>1088</v>
+      </c>
+      <c r="F367" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>34</v>
+      </c>
+      <c r="D368" t="n">
+        <v>1789</v>
+      </c>
+      <c r="E368" t="n">
+        <v>1823</v>
+      </c>
+      <c r="F368" s="2" t="n">
+        <v>0.9813</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>0</v>
+      </c>
+      <c r="D369" t="n">
+        <v>0</v>
+      </c>
+      <c r="E369" t="n">
+        <v>0</v>
+      </c>
+      <c r="F369" s="2" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>30</v>
+      </c>
+      <c r="D370" t="n">
+        <v>1611</v>
+      </c>
+      <c r="E370" t="n">
+        <v>1641</v>
+      </c>
+      <c r="F370" s="2" t="n">
+        <v>0.9817</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>0</v>
+      </c>
+      <c r="D371" t="n">
+        <v>0</v>
+      </c>
+      <c r="E371" t="n">
+        <v>0</v>
+      </c>
+      <c r="F371" s="2" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>115</v>
+      </c>
+      <c r="D372" t="n">
+        <v>297</v>
+      </c>
+      <c r="E372" t="n">
+        <v>412</v>
+      </c>
+      <c r="F372" s="2" t="n">
+        <v>0.7209</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>3</v>
+      </c>
+      <c r="D373" t="n">
+        <v>0</v>
+      </c>
+      <c r="E373" t="n">
+        <v>3</v>
+      </c>
+      <c r="F373" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>28</v>
+      </c>
+      <c r="D374" t="n">
+        <v>1515</v>
+      </c>
+      <c r="E374" t="n">
+        <v>1543</v>
+      </c>
+      <c r="F374" s="2" t="n">
+        <v>0.9819</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>1</v>
+      </c>
+      <c r="D375" t="n">
+        <v>182</v>
+      </c>
+      <c r="E375" t="n">
+        <v>183</v>
+      </c>
+      <c r="F375" s="2" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>0</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0</v>
+      </c>
+      <c r="E376" t="n">
+        <v>0</v>
+      </c>
+      <c r="F376" s="2" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>42</v>
+      </c>
+      <c r="D377" t="n">
+        <v>1359</v>
+      </c>
+      <c r="E377" t="n">
+        <v>1401</v>
+      </c>
+      <c r="F377" s="2" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>21</v>
+      </c>
+      <c r="D378" t="n">
+        <v>5787</v>
+      </c>
+      <c r="E378" t="n">
+        <v>5808</v>
+      </c>
+      <c r="F378" s="2" t="n">
+        <v>0.9964</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>0</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0</v>
+      </c>
+      <c r="E379" t="n">
+        <v>0</v>
+      </c>
+      <c r="F379" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F365"/>
+  <autoFilter ref="A1:F379"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>380</v>
+        <v>293</v>
       </c>
       <c r="C8" t="n">
-        <v>1265</v>
+        <v>1352</v>
       </c>
       <c r="D8" t="n">
         <v>1645</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.769</v>
+        <v>0.8219</v>
       </c>
     </row>
     <row r="9">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>65</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>0.0462</v>
       </c>
     </row>
     <row r="10">
@@ -621,16 +621,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C10" t="n">
-        <v>16049</v>
+        <v>16053</v>
       </c>
       <c r="D10" t="n">
         <v>16155</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9934000000000001</v>
+        <v>0.9937</v>
       </c>
     </row>
     <row r="11">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2736</v>
+        <v>2717</v>
       </c>
       <c r="C14" t="n">
-        <v>104213</v>
+        <v>104232</v>
       </c>
       <c r="D14" t="n">
         <v>106949</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9743999999999999</v>
+        <v>0.9745999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -9257,16 +9257,16 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="D372" t="n">
-        <v>297</v>
+        <v>384</v>
       </c>
       <c r="E372" t="n">
         <v>412</v>
       </c>
       <c r="F372" s="2" t="n">
-        <v>0.7209</v>
+        <v>0.9320000000000001</v>
       </c>
     </row>
     <row r="373">
@@ -9281,16 +9281,16 @@
         </is>
       </c>
       <c r="C373" t="n">
+        <v>0</v>
+      </c>
+      <c r="D373" t="n">
         <v>3</v>
-      </c>
-      <c r="D373" t="n">
-        <v>0</v>
       </c>
       <c r="E373" t="n">
         <v>3</v>
       </c>
       <c r="F373" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374">
@@ -9305,16 +9305,16 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D374" t="n">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="E374" t="n">
         <v>1543</v>
       </c>
       <c r="F374" s="2" t="n">
-        <v>0.9819</v>
+        <v>0.9843999999999999</v>
       </c>
     </row>
     <row r="375">
@@ -9399,16 +9399,16 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D378" t="n">
-        <v>5787</v>
+        <v>5806</v>
       </c>
       <c r="E378" t="n">
         <v>5808</v>
       </c>
       <c r="F378" s="2" t="n">
-        <v>0.9964</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="379">

--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$379</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$393</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F379"/>
+  <dimension ref="A1:F393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9433,8 +9433,316 @@
       </c>
       <c r="F379" s="2" t="n"/>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>0</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0</v>
+      </c>
+      <c r="E380" t="n">
+        <v>0</v>
+      </c>
+      <c r="F380" s="2" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>0</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0</v>
+      </c>
+      <c r="E381" t="n">
+        <v>0</v>
+      </c>
+      <c r="F381" s="2" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>0</v>
+      </c>
+      <c r="D382" t="n">
+        <v>0</v>
+      </c>
+      <c r="E382" t="n">
+        <v>0</v>
+      </c>
+      <c r="F382" s="2" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>0</v>
+      </c>
+      <c r="D383" t="n">
+        <v>0</v>
+      </c>
+      <c r="E383" t="n">
+        <v>0</v>
+      </c>
+      <c r="F383" s="2" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>0</v>
+      </c>
+      <c r="D384" t="n">
+        <v>0</v>
+      </c>
+      <c r="E384" t="n">
+        <v>0</v>
+      </c>
+      <c r="F384" s="2" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>0</v>
+      </c>
+      <c r="D385" t="n">
+        <v>0</v>
+      </c>
+      <c r="E385" t="n">
+        <v>0</v>
+      </c>
+      <c r="F385" s="2" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>0</v>
+      </c>
+      <c r="D386" t="n">
+        <v>0</v>
+      </c>
+      <c r="E386" t="n">
+        <v>0</v>
+      </c>
+      <c r="F386" s="2" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>0</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0</v>
+      </c>
+      <c r="E387" t="n">
+        <v>0</v>
+      </c>
+      <c r="F387" s="2" t="n"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>0</v>
+      </c>
+      <c r="D388" t="n">
+        <v>0</v>
+      </c>
+      <c r="E388" t="n">
+        <v>0</v>
+      </c>
+      <c r="F388" s="2" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>0</v>
+      </c>
+      <c r="D389" t="n">
+        <v>0</v>
+      </c>
+      <c r="E389" t="n">
+        <v>0</v>
+      </c>
+      <c r="F389" s="2" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>0</v>
+      </c>
+      <c r="D390" t="n">
+        <v>0</v>
+      </c>
+      <c r="E390" t="n">
+        <v>0</v>
+      </c>
+      <c r="F390" s="2" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>0</v>
+      </c>
+      <c r="D391" t="n">
+        <v>0</v>
+      </c>
+      <c r="E391" t="n">
+        <v>0</v>
+      </c>
+      <c r="F391" s="2" t="n"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>0</v>
+      </c>
+      <c r="D392" t="n">
+        <v>0</v>
+      </c>
+      <c r="E392" t="n">
+        <v>0</v>
+      </c>
+      <c r="F392" s="2" t="n"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>0</v>
+      </c>
+      <c r="D393" t="n">
+        <v>0</v>
+      </c>
+      <c r="E393" t="n">
+        <v>0</v>
+      </c>
+      <c r="F393" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F379"/>
+  <autoFilter ref="A1:F393"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Geral Diário" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geral Diário" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$393</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$421</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>644</v>
       </c>
       <c r="C3" t="n">
-        <v>28046</v>
+        <v>29463</v>
       </c>
       <c r="D3" t="n">
-        <v>28690</v>
+        <v>30107</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9776</v>
+        <v>0.9786</v>
       </c>
     </row>
     <row r="4">
@@ -514,13 +514,13 @@
         <v>687</v>
       </c>
       <c r="C4" t="n">
-        <v>51495</v>
+        <v>54743</v>
       </c>
       <c r="D4" t="n">
-        <v>52182</v>
+        <v>55430</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9868000000000001</v>
+        <v>0.9876</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="C6" t="n">
-        <v>32780</v>
+        <v>35123</v>
       </c>
       <c r="D6" t="n">
-        <v>32891</v>
+        <v>35312</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9965999999999999</v>
+        <v>0.9945999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -566,15 +566,17 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -583,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>293</v>
+        <v>715</v>
       </c>
       <c r="C8" t="n">
-        <v>1352</v>
+        <v>1906</v>
       </c>
       <c r="D8" t="n">
-        <v>1645</v>
+        <v>2621</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8219</v>
+        <v>0.7272</v>
       </c>
     </row>
     <row r="9">
@@ -602,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.0462</v>
+        <v>0.0805</v>
       </c>
     </row>
     <row r="10">
@@ -621,16 +623,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C10" t="n">
-        <v>16053</v>
+        <v>18294</v>
       </c>
       <c r="D10" t="n">
-        <v>16155</v>
+        <v>18402</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9937</v>
+        <v>0.9941</v>
       </c>
     </row>
     <row r="11">
@@ -643,13 +645,13 @@
         <v>473</v>
       </c>
       <c r="C11" t="n">
-        <v>14590</v>
+        <v>14736</v>
       </c>
       <c r="D11" t="n">
-        <v>15063</v>
+        <v>15209</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9686</v>
+        <v>0.9689</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +680,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C13" t="n">
-        <v>40280</v>
+        <v>42303</v>
       </c>
       <c r="D13" t="n">
-        <v>40645</v>
+        <v>42672</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.991</v>
+        <v>0.9914000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +699,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2717</v>
+        <v>3070</v>
       </c>
       <c r="C14" t="n">
-        <v>104232</v>
+        <v>111359</v>
       </c>
       <c r="D14" t="n">
-        <v>106949</v>
+        <v>114429</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9745999999999999</v>
+        <v>0.9732</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F393"/>
+  <dimension ref="A1:F421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9436,7 +9438,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -9458,7 +9460,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -9470,17 +9472,19 @@
         <v>0</v>
       </c>
       <c r="D381" t="n">
-        <v>0</v>
+        <v>1061</v>
       </c>
       <c r="E381" t="n">
-        <v>0</v>
-      </c>
-      <c r="F381" s="2" t="n"/>
+        <v>1061</v>
+      </c>
+      <c r="F381" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -9492,17 +9496,19 @@
         <v>0</v>
       </c>
       <c r="D382" t="n">
-        <v>0</v>
+        <v>2721</v>
       </c>
       <c r="E382" t="n">
-        <v>0</v>
-      </c>
-      <c r="F382" s="2" t="n"/>
+        <v>2721</v>
+      </c>
+      <c r="F382" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -9524,7 +9530,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -9533,20 +9539,22 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="D384" t="n">
-        <v>0</v>
+        <v>1901</v>
       </c>
       <c r="E384" t="n">
-        <v>0</v>
-      </c>
-      <c r="F384" s="2" t="n"/>
+        <v>1978</v>
+      </c>
+      <c r="F384" s="2" t="n">
+        <v>0.9611</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -9558,17 +9566,19 @@
         <v>0</v>
       </c>
       <c r="D385" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E385" t="n">
-        <v>0</v>
-      </c>
-      <c r="F385" s="2" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="F385" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -9577,20 +9587,22 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D386" t="n">
-        <v>0</v>
+        <v>554</v>
       </c>
       <c r="E386" t="n">
-        <v>0</v>
-      </c>
-      <c r="F386" s="2" t="n"/>
+        <v>594</v>
+      </c>
+      <c r="F386" s="2" t="n">
+        <v>0.9327</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -9599,20 +9611,22 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D387" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E387" t="n">
-        <v>0</v>
-      </c>
-      <c r="F387" s="2" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="F387" s="2" t="n">
+        <v>0.2667</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -9621,20 +9635,22 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D388" t="n">
-        <v>0</v>
+        <v>1744</v>
       </c>
       <c r="E388" t="n">
-        <v>0</v>
-      </c>
-      <c r="F388" s="2" t="n"/>
+        <v>1746</v>
+      </c>
+      <c r="F388" s="2" t="n">
+        <v>0.9989</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -9646,17 +9662,19 @@
         <v>0</v>
       </c>
       <c r="D389" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="E389" t="n">
-        <v>0</v>
-      </c>
-      <c r="F389" s="2" t="n"/>
+        <v>132</v>
+      </c>
+      <c r="F389" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -9678,7 +9696,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -9687,20 +9705,22 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D391" t="n">
-        <v>0</v>
+        <v>1488</v>
       </c>
       <c r="E391" t="n">
-        <v>0</v>
-      </c>
-      <c r="F391" s="2" t="n"/>
+        <v>1489</v>
+      </c>
+      <c r="F391" s="2" t="n">
+        <v>0.9993000000000001</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -9709,40 +9729,678 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="D392" t="n">
-        <v>0</v>
+        <v>5925</v>
       </c>
       <c r="E392" t="n">
-        <v>0</v>
-      </c>
-      <c r="F392" s="2" t="n"/>
+        <v>6009</v>
+      </c>
+      <c r="F392" s="2" t="n">
+        <v>0.986</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>0</v>
+      </c>
+      <c r="D393" t="n">
+        <v>0</v>
+      </c>
+      <c r="E393" t="n">
+        <v>0</v>
+      </c>
+      <c r="F393" s="2" t="n"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>0</v>
+      </c>
+      <c r="D394" t="n">
+        <v>0</v>
+      </c>
+      <c r="E394" t="n">
+        <v>0</v>
+      </c>
+      <c r="F394" s="2" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>0</v>
+      </c>
+      <c r="D395" t="n">
+        <v>356</v>
+      </c>
+      <c r="E395" t="n">
+        <v>356</v>
+      </c>
+      <c r="F395" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>0</v>
+      </c>
+      <c r="D396" t="n">
+        <v>527</v>
+      </c>
+      <c r="E396" t="n">
+        <v>527</v>
+      </c>
+      <c r="F396" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>0</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0</v>
+      </c>
+      <c r="E397" t="n">
+        <v>0</v>
+      </c>
+      <c r="F397" s="2" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>1</v>
+      </c>
+      <c r="D398" t="n">
+        <v>442</v>
+      </c>
+      <c r="E398" t="n">
+        <v>443</v>
+      </c>
+      <c r="F398" s="2" t="n">
+        <v>0.9976999999999999</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>7</v>
+      </c>
+      <c r="D399" t="n">
+        <v>0</v>
+      </c>
+      <c r="E399" t="n">
+        <v>7</v>
+      </c>
+      <c r="F399" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>382</v>
+      </c>
+      <c r="D400" t="n">
+        <v>0</v>
+      </c>
+      <c r="E400" t="n">
+        <v>382</v>
+      </c>
+      <c r="F400" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>7</v>
+      </c>
+      <c r="D401" t="n">
+        <v>0</v>
+      </c>
+      <c r="E401" t="n">
+        <v>7</v>
+      </c>
+      <c r="F401" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>4</v>
+      </c>
+      <c r="D402" t="n">
+        <v>497</v>
+      </c>
+      <c r="E402" t="n">
+        <v>501</v>
+      </c>
+      <c r="F402" s="2" t="n">
+        <v>0.992</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>0</v>
+      </c>
+      <c r="D403" t="n">
+        <v>14</v>
+      </c>
+      <c r="E403" t="n">
+        <v>14</v>
+      </c>
+      <c r="F403" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>0</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0</v>
+      </c>
+      <c r="E404" t="n">
+        <v>0</v>
+      </c>
+      <c r="F404" s="2" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>3</v>
+      </c>
+      <c r="D405" t="n">
+        <v>535</v>
+      </c>
+      <c r="E405" t="n">
+        <v>538</v>
+      </c>
+      <c r="F405" s="2" t="n">
+        <v>0.9944</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>269</v>
+      </c>
+      <c r="D406" t="n">
+        <v>1202</v>
+      </c>
+      <c r="E406" t="n">
+        <v>1471</v>
+      </c>
+      <c r="F406" s="2" t="n">
+        <v>0.8170999999999999</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>0</v>
+      </c>
+      <c r="D407" t="n">
+        <v>0</v>
+      </c>
+      <c r="E407" t="n">
+        <v>0</v>
+      </c>
+      <c r="F407" s="2" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr">
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>0</v>
+      </c>
+      <c r="D408" t="n">
+        <v>0</v>
+      </c>
+      <c r="E408" t="n">
+        <v>0</v>
+      </c>
+      <c r="F408" s="2" t="n"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>0</v>
+      </c>
+      <c r="D409" t="n">
+        <v>0</v>
+      </c>
+      <c r="E409" t="n">
+        <v>0</v>
+      </c>
+      <c r="F409" s="2" t="n"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>0</v>
+      </c>
+      <c r="D410" t="n">
+        <v>0</v>
+      </c>
+      <c r="E410" t="n">
+        <v>0</v>
+      </c>
+      <c r="F410" s="2" t="n"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>0</v>
+      </c>
+      <c r="D411" t="n">
+        <v>0</v>
+      </c>
+      <c r="E411" t="n">
+        <v>0</v>
+      </c>
+      <c r="F411" s="2" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>0</v>
+      </c>
+      <c r="D412" t="n">
+        <v>0</v>
+      </c>
+      <c r="E412" t="n">
+        <v>0</v>
+      </c>
+      <c r="F412" s="2" t="n"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>0</v>
+      </c>
+      <c r="D413" t="n">
+        <v>0</v>
+      </c>
+      <c r="E413" t="n">
+        <v>0</v>
+      </c>
+      <c r="F413" s="2" t="n"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>0</v>
+      </c>
+      <c r="D414" t="n">
+        <v>0</v>
+      </c>
+      <c r="E414" t="n">
+        <v>0</v>
+      </c>
+      <c r="F414" s="2" t="n"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>0</v>
+      </c>
+      <c r="D415" t="n">
+        <v>0</v>
+      </c>
+      <c r="E415" t="n">
+        <v>0</v>
+      </c>
+      <c r="F415" s="2" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>0</v>
+      </c>
+      <c r="D416" t="n">
+        <v>0</v>
+      </c>
+      <c r="E416" t="n">
+        <v>0</v>
+      </c>
+      <c r="F416" s="2" t="n"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>0</v>
+      </c>
+      <c r="D417" t="n">
+        <v>0</v>
+      </c>
+      <c r="E417" t="n">
+        <v>0</v>
+      </c>
+      <c r="F417" s="2" t="n"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>0</v>
+      </c>
+      <c r="D418" t="n">
+        <v>0</v>
+      </c>
+      <c r="E418" t="n">
+        <v>0</v>
+      </c>
+      <c r="F418" s="2" t="n"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>0</v>
+      </c>
+      <c r="D419" t="n">
+        <v>0</v>
+      </c>
+      <c r="E419" t="n">
+        <v>0</v>
+      </c>
+      <c r="F419" s="2" t="n"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>0</v>
+      </c>
+      <c r="D420" t="n">
+        <v>0</v>
+      </c>
+      <c r="E420" t="n">
+        <v>0</v>
+      </c>
+      <c r="F420" s="2" t="n"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
         <is>
           <t>S-FREG-SP</t>
         </is>
       </c>
-      <c r="C393" t="n">
-        <v>0</v>
-      </c>
-      <c r="D393" t="n">
-        <v>0</v>
-      </c>
-      <c r="E393" t="n">
-        <v>0</v>
-      </c>
-      <c r="F393" s="2" t="n"/>
+      <c r="C421" t="n">
+        <v>0</v>
+      </c>
+      <c r="D421" t="n">
+        <v>0</v>
+      </c>
+      <c r="E421" t="n">
+        <v>0</v>
+      </c>
+      <c r="F421" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F393"/>
+  <autoFilter ref="A1:F421"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$393</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$407</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>644</v>
       </c>
       <c r="C3" t="n">
-        <v>28046</v>
+        <v>30117</v>
       </c>
       <c r="D3" t="n">
-        <v>28690</v>
+        <v>30761</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9776</v>
+        <v>0.9791</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>687</v>
+        <v>861</v>
       </c>
       <c r="C4" t="n">
-        <v>51495</v>
+        <v>55814</v>
       </c>
       <c r="D4" t="n">
-        <v>52182</v>
+        <v>56675</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9868000000000001</v>
+        <v>0.9848</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111</v>
+        <v>201</v>
       </c>
       <c r="C6" t="n">
-        <v>32780</v>
+        <v>36866</v>
       </c>
       <c r="D6" t="n">
-        <v>32891</v>
+        <v>37067</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9965999999999999</v>
+        <v>0.9945999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -569,12 +569,14 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -583,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>293</v>
+        <v>363</v>
       </c>
       <c r="C8" t="n">
-        <v>1352</v>
+        <v>2417</v>
       </c>
       <c r="D8" t="n">
-        <v>1645</v>
+        <v>2780</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8219</v>
+        <v>0.8694</v>
       </c>
     </row>
     <row r="9">
@@ -602,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>65</v>
+        <v>115</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.0462</v>
+        <v>0.0261</v>
       </c>
     </row>
     <row r="10">
@@ -621,16 +623,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="C10" t="n">
-        <v>16053</v>
+        <v>18937</v>
       </c>
       <c r="D10" t="n">
-        <v>16155</v>
+        <v>19105</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9937</v>
+        <v>0.9912000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -643,13 +645,13 @@
         <v>473</v>
       </c>
       <c r="C11" t="n">
-        <v>14590</v>
+        <v>14927</v>
       </c>
       <c r="D11" t="n">
-        <v>15063</v>
+        <v>15400</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9686</v>
+        <v>0.9693000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +680,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="C13" t="n">
-        <v>40280</v>
+        <v>44094</v>
       </c>
       <c r="D13" t="n">
-        <v>40645</v>
+        <v>44481</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.991</v>
+        <v>0.9913</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +699,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2717</v>
+        <v>3213</v>
       </c>
       <c r="C14" t="n">
-        <v>104232</v>
+        <v>114629</v>
       </c>
       <c r="D14" t="n">
-        <v>106949</v>
+        <v>117842</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9745999999999999</v>
+        <v>0.9727</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F393"/>
+  <dimension ref="A1:F407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9741,8 +9743,336 @@
       </c>
       <c r="F393" s="2" t="n"/>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>0</v>
+      </c>
+      <c r="D394" t="n">
+        <v>0</v>
+      </c>
+      <c r="E394" t="n">
+        <v>0</v>
+      </c>
+      <c r="F394" s="2" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>0</v>
+      </c>
+      <c r="D395" t="n">
+        <v>2071</v>
+      </c>
+      <c r="E395" t="n">
+        <v>2071</v>
+      </c>
+      <c r="F395" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>174</v>
+      </c>
+      <c r="D396" t="n">
+        <v>4319</v>
+      </c>
+      <c r="E396" t="n">
+        <v>4493</v>
+      </c>
+      <c r="F396" s="2" t="n">
+        <v>0.9612999999999999</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>0</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0</v>
+      </c>
+      <c r="E397" t="n">
+        <v>0</v>
+      </c>
+      <c r="F397" s="2" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>90</v>
+      </c>
+      <c r="D398" t="n">
+        <v>4086</v>
+      </c>
+      <c r="E398" t="n">
+        <v>4176</v>
+      </c>
+      <c r="F398" s="2" t="n">
+        <v>0.9784</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>0</v>
+      </c>
+      <c r="D399" t="n">
+        <v>4</v>
+      </c>
+      <c r="E399" t="n">
+        <v>4</v>
+      </c>
+      <c r="F399" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>70</v>
+      </c>
+      <c r="D400" t="n">
+        <v>1065</v>
+      </c>
+      <c r="E400" t="n">
+        <v>1135</v>
+      </c>
+      <c r="F400" s="2" t="n">
+        <v>0.9383</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>50</v>
+      </c>
+      <c r="D401" t="n">
+        <v>0</v>
+      </c>
+      <c r="E401" t="n">
+        <v>50</v>
+      </c>
+      <c r="F401" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>66</v>
+      </c>
+      <c r="D402" t="n">
+        <v>2884</v>
+      </c>
+      <c r="E402" t="n">
+        <v>2950</v>
+      </c>
+      <c r="F402" s="2" t="n">
+        <v>0.9776</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>0</v>
+      </c>
+      <c r="D403" t="n">
+        <v>337</v>
+      </c>
+      <c r="E403" t="n">
+        <v>337</v>
+      </c>
+      <c r="F403" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>0</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0</v>
+      </c>
+      <c r="E404" t="n">
+        <v>0</v>
+      </c>
+      <c r="F404" s="2" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>22</v>
+      </c>
+      <c r="D405" t="n">
+        <v>3814</v>
+      </c>
+      <c r="E405" t="n">
+        <v>3836</v>
+      </c>
+      <c r="F405" s="2" t="n">
+        <v>0.9943000000000001</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>496</v>
+      </c>
+      <c r="D406" t="n">
+        <v>10397</v>
+      </c>
+      <c r="E406" t="n">
+        <v>10893</v>
+      </c>
+      <c r="F406" s="2" t="n">
+        <v>0.9545</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>0</v>
+      </c>
+      <c r="D407" t="n">
+        <v>0</v>
+      </c>
+      <c r="E407" t="n">
+        <v>0</v>
+      </c>
+      <c r="F407" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F393"/>
+  <autoFilter ref="A1:F407"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C4" t="n">
         <v>55814</v>
       </c>
       <c r="D4" t="n">
-        <v>56675</v>
+        <v>56674</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.9848</v>
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3213</v>
+        <v>3217</v>
       </c>
       <c r="C14" t="n">
         <v>114629</v>
       </c>
       <c r="D14" t="n">
-        <v>117842</v>
+        <v>117846</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0.9727</v>
@@ -9801,16 +9801,16 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D396" t="n">
         <v>4319</v>
       </c>
       <c r="E396" t="n">
-        <v>4493</v>
+        <v>4492</v>
       </c>
       <c r="F396" s="2" t="n">
-        <v>0.9612999999999999</v>
+        <v>0.9615</v>
       </c>
     </row>
     <row r="397">
@@ -10037,16 +10037,16 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D406" t="n">
         <v>10397</v>
       </c>
       <c r="E406" t="n">
-        <v>10893</v>
+        <v>10897</v>
       </c>
       <c r="F406" s="2" t="n">
-        <v>0.9545</v>
+        <v>0.9540999999999999</v>
       </c>
     </row>
     <row r="407">

--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>57</v>
       </c>
       <c r="C3" t="n">
-        <v>1386</v>
+        <v>2664</v>
       </c>
       <c r="D3" t="n">
-        <v>1443</v>
+        <v>2721</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9605</v>
+        <v>0.9791</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="C4" t="n">
-        <v>4503</v>
+        <v>6917</v>
       </c>
       <c r="D4" t="n">
-        <v>4506</v>
+        <v>6988</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9993000000000001</v>
+        <v>0.9898</v>
       </c>
     </row>
     <row r="5">
@@ -550,13 +550,13 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>2762</v>
+        <v>5241</v>
       </c>
       <c r="D6" t="n">
-        <v>2786</v>
+        <v>5265</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9914000000000001</v>
+        <v>0.9954000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="C7" t="n">
-        <v>91</v>
+        <v>285</v>
       </c>
       <c r="D7" t="n">
-        <v>91</v>
+        <v>496</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0.5746</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C8" t="n">
-        <v>1493</v>
+        <v>3526</v>
       </c>
       <c r="D8" t="n">
-        <v>1519</v>
+        <v>3645</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9829000000000001</v>
+        <v>0.9673999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -607,10 +607,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>2221</v>
+        <v>4494</v>
       </c>
       <c r="D10" t="n">
-        <v>2223</v>
+        <v>4502</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9991</v>
+        <v>0.9982</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>1012</v>
+        <v>1560</v>
       </c>
       <c r="D11" t="n">
-        <v>1043</v>
+        <v>1591</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9804999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>2212</v>
+        <v>3842</v>
       </c>
       <c r="D13" t="n">
-        <v>2215</v>
+        <v>3846</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9986</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>295</v>
+        <v>442</v>
       </c>
       <c r="C14" t="n">
-        <v>6647</v>
+        <v>12632</v>
       </c>
       <c r="D14" t="n">
-        <v>6942</v>
+        <v>13074</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9575</v>
+        <v>0.9662000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1109,8 +1109,336 @@
       </c>
       <c r="F15" s="2" t="n"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1278</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1278</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>68</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2414</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2482</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0.9726</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2479</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2479</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>211</v>
+      </c>
+      <c r="D21" t="n">
+        <v>194</v>
+      </c>
+      <c r="E21" t="n">
+        <v>405</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0.479</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>93</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2033</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2126</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.9562999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>34</v>
+      </c>
+      <c r="E23" t="n">
+        <v>34</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2273</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2279</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0.9974</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>548</v>
+      </c>
+      <c r="E25" t="n">
+        <v>548</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1630</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1631</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0.9994</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>147</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5985</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6132</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0.976</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F15"/>
+  <autoFilter ref="A1:F29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="C3" t="n">
-        <v>2664</v>
+        <v>4006</v>
       </c>
       <c r="D3" t="n">
-        <v>2721</v>
+        <v>4104</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9791</v>
+        <v>0.9761</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71</v>
+        <v>148</v>
       </c>
       <c r="C4" t="n">
-        <v>6917</v>
+        <v>9624</v>
       </c>
       <c r="D4" t="n">
-        <v>6988</v>
+        <v>9772</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9898</v>
+        <v>0.9849</v>
       </c>
     </row>
     <row r="5">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C6" t="n">
-        <v>5241</v>
+        <v>8038</v>
       </c>
       <c r="D6" t="n">
-        <v>5265</v>
+        <v>8075</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0.9954000000000001</v>
@@ -569,13 +569,13 @@
         <v>211</v>
       </c>
       <c r="C7" t="n">
-        <v>285</v>
+        <v>386</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>597</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.5746</v>
+        <v>0.6466</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>190</v>
       </c>
       <c r="C8" t="n">
-        <v>3526</v>
+        <v>3829</v>
       </c>
       <c r="D8" t="n">
-        <v>3645</v>
+        <v>4019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9673999999999999</v>
+        <v>0.9527</v>
       </c>
     </row>
     <row r="9">
@@ -607,10 +607,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D9" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>4494</v>
+        <v>5911</v>
       </c>
       <c r="D10" t="n">
-        <v>4502</v>
+        <v>5936</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9982</v>
+        <v>0.9958</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>1560</v>
+        <v>1651</v>
       </c>
       <c r="D11" t="n">
-        <v>1591</v>
+        <v>1682</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9804999999999999</v>
+        <v>0.9815999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -681,13 +681,13 @@
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>3842</v>
+        <v>5406</v>
       </c>
       <c r="D13" t="n">
-        <v>3846</v>
+        <v>5410</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.9993000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>442</v>
+        <v>564</v>
       </c>
       <c r="C14" t="n">
-        <v>12632</v>
+        <v>18098</v>
       </c>
       <c r="D14" t="n">
-        <v>13074</v>
+        <v>18662</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9662000000000001</v>
+        <v>0.9698</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1437,8 +1437,336 @@
       </c>
       <c r="F29" s="2" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>41</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1342</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1383</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0.9704</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>77</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2707</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2784</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>13</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2797</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0.9954000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>101</v>
+      </c>
+      <c r="E35" t="n">
+        <v>101</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>71</v>
+      </c>
+      <c r="D36" t="n">
+        <v>303</v>
+      </c>
+      <c r="E36" t="n">
+        <v>374</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0.8101999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>30</v>
+      </c>
+      <c r="E37" t="n">
+        <v>30</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>17</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1417</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1434</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0.9881</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>91</v>
+      </c>
+      <c r="E39" t="n">
+        <v>91</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1564</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1564</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>122</v>
+      </c>
+      <c r="D42" t="n">
+        <v>5466</v>
+      </c>
+      <c r="E42" t="n">
+        <v>5588</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0.9782</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F29"/>
+  <autoFilter ref="A1:F43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C14" t="n">
-        <v>18098</v>
+        <v>18099</v>
       </c>
       <c r="D14" t="n">
         <v>18662</v>
@@ -1731,16 +1731,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D42" t="n">
-        <v>5466</v>
+        <v>5467</v>
       </c>
       <c r="E42" t="n">
         <v>5588</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.9782</v>
+        <v>0.9782999999999999</v>
       </c>
     </row>
     <row r="43">

--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>98</v>
       </c>
       <c r="C3" t="n">
-        <v>4006</v>
+        <v>5001</v>
       </c>
       <c r="D3" t="n">
-        <v>4104</v>
+        <v>5099</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9761</v>
+        <v>0.9808</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C4" t="n">
-        <v>9624</v>
+        <v>14140</v>
       </c>
       <c r="D4" t="n">
-        <v>9772</v>
+        <v>14290</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9849</v>
+        <v>0.9895</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="C6" t="n">
-        <v>8038</v>
+        <v>11186</v>
       </c>
       <c r="D6" t="n">
-        <v>8075</v>
+        <v>11320</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9954000000000001</v>
+        <v>0.9882</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>211</v>
       </c>
       <c r="C7" t="n">
-        <v>386</v>
+        <v>569</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>780</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6466</v>
+        <v>0.7295</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C8" t="n">
-        <v>3829</v>
+        <v>4253</v>
       </c>
       <c r="D8" t="n">
-        <v>4019</v>
+        <v>4460</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9527</v>
+        <v>0.9536</v>
       </c>
     </row>
     <row r="9">
@@ -607,10 +607,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>5911</v>
+        <v>7094</v>
       </c>
       <c r="D10" t="n">
-        <v>5936</v>
+        <v>7127</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9958</v>
+        <v>0.9954000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>1651</v>
+        <v>1766</v>
       </c>
       <c r="D11" t="n">
-        <v>1682</v>
+        <v>1806</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9815999999999999</v>
+        <v>0.9779000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>5406</v>
+        <v>6882</v>
       </c>
       <c r="D13" t="n">
-        <v>5410</v>
+        <v>6890</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9993000000000001</v>
+        <v>0.9987999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>563</v>
+        <v>921</v>
       </c>
       <c r="C14" t="n">
-        <v>18099</v>
+        <v>22829</v>
       </c>
       <c r="D14" t="n">
-        <v>18662</v>
+        <v>23750</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9698</v>
+        <v>0.9612000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1765,8 +1765,336 @@
       </c>
       <c r="F43" s="2" t="n"/>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>995</v>
+      </c>
+      <c r="E45" t="n">
+        <v>995</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4516</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4518</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0.9995999999999999</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>97</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3148</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3245</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0.9701000000000001</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>183</v>
+      </c>
+      <c r="E49" t="n">
+        <v>183</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>17</v>
+      </c>
+      <c r="D50" t="n">
+        <v>424</v>
+      </c>
+      <c r="E50" t="n">
+        <v>441</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>0.9615</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>25</v>
+      </c>
+      <c r="E51" t="n">
+        <v>25</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1183</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1191</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0.9933</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>9</v>
+      </c>
+      <c r="D53" t="n">
+        <v>115</v>
+      </c>
+      <c r="E53" t="n">
+        <v>124</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>0.9274</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1476</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1480</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>0.9973000000000001</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>358</v>
+      </c>
+      <c r="D56" t="n">
+        <v>4730</v>
+      </c>
+      <c r="E56" t="n">
+        <v>5088</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>0.9296</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F43"/>
+  <autoFilter ref="A1:F57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C6" t="n">
-        <v>11186</v>
+        <v>11188</v>
       </c>
       <c r="D6" t="n">
         <v>11320</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9882</v>
+        <v>0.9883</v>
       </c>
     </row>
     <row r="7">
@@ -1869,16 +1869,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D48" t="n">
-        <v>3148</v>
+        <v>3150</v>
       </c>
       <c r="E48" t="n">
         <v>3245</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.9701000000000001</v>
+        <v>0.9706999999999999</v>
       </c>
     </row>
     <row r="49">

--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C3" t="n">
-        <v>5001</v>
+        <v>5097</v>
       </c>
       <c r="D3" t="n">
-        <v>5099</v>
+        <v>5199</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9808</v>
+        <v>0.9804</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="C4" t="n">
-        <v>14140</v>
+        <v>14575</v>
       </c>
       <c r="D4" t="n">
-        <v>14290</v>
+        <v>14774</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9895</v>
+        <v>0.9865</v>
       </c>
     </row>
     <row r="5">
@@ -550,13 +550,13 @@
         <v>132</v>
       </c>
       <c r="C6" t="n">
-        <v>11188</v>
+        <v>12887</v>
       </c>
       <c r="D6" t="n">
-        <v>11320</v>
+        <v>13019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9883</v>
+        <v>0.9899</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>211</v>
       </c>
       <c r="C7" t="n">
-        <v>569</v>
+        <v>602</v>
       </c>
       <c r="D7" t="n">
-        <v>780</v>
+        <v>813</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7295</v>
+        <v>0.7404999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C8" t="n">
-        <v>4253</v>
+        <v>4255</v>
       </c>
       <c r="D8" t="n">
-        <v>4460</v>
+        <v>4482</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9536</v>
+        <v>0.9494</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D9" t="n">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>0.9556999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -626,13 +626,13 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>7094</v>
+        <v>7417</v>
       </c>
       <c r="D10" t="n">
-        <v>7127</v>
+        <v>7450</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9954000000000001</v>
+        <v>0.9956</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>1766</v>
+        <v>1796</v>
       </c>
       <c r="D11" t="n">
-        <v>1806</v>
+        <v>1836</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9779000000000001</v>
+        <v>0.9782</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>6882</v>
+        <v>7193</v>
       </c>
       <c r="D13" t="n">
-        <v>6890</v>
+        <v>7211</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9987999999999999</v>
+        <v>0.9975000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>921</v>
+        <v>1273</v>
       </c>
       <c r="C14" t="n">
-        <v>22829</v>
+        <v>24569</v>
       </c>
       <c r="D14" t="n">
-        <v>23750</v>
+        <v>25842</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.9506999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2093,8 +2093,336 @@
       </c>
       <c r="F57" s="2" t="n"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" t="n">
+        <v>96</v>
+      </c>
+      <c r="E59" t="n">
+        <v>100</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>49</v>
+      </c>
+      <c r="D60" t="n">
+        <v>435</v>
+      </c>
+      <c r="E60" t="n">
+        <v>484</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>0.8987999999999999</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1699</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1699</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>33</v>
+      </c>
+      <c r="E63" t="n">
+        <v>33</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>20</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" t="n">
+        <v>22</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>7</v>
+      </c>
+      <c r="D65" t="n">
+        <v>6</v>
+      </c>
+      <c r="E65" t="n">
+        <v>13</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>0.4615</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>323</v>
+      </c>
+      <c r="E66" t="n">
+        <v>323</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>30</v>
+      </c>
+      <c r="E67" t="n">
+        <v>30</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>10</v>
+      </c>
+      <c r="D69" t="n">
+        <v>311</v>
+      </c>
+      <c r="E69" t="n">
+        <v>321</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>0.9688</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>352</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1740</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2092</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0.8317</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F57"/>
+  <autoFilter ref="A1:F71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2421,8 +2421,316 @@
       </c>
       <c r="F71" s="2" t="n"/>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F71"/>
+  <autoFilter ref="A1:F85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>761</v>
       </c>
       <c r="C3" t="n">
         <v>5097</v>
       </c>
       <c r="D3" t="n">
-        <v>5199</v>
+        <v>5858</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9804</v>
+        <v>0.8701000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="C4" t="n">
         <v>14575</v>
       </c>
       <c r="D4" t="n">
-        <v>14774</v>
+        <v>14804</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9865</v>
+        <v>0.9845</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>132</v>
+        <v>386</v>
       </c>
       <c r="C6" t="n">
         <v>12887</v>
       </c>
       <c r="D6" t="n">
-        <v>13019</v>
+        <v>13273</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9899</v>
+        <v>0.9709</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="C7" t="n">
         <v>602</v>
       </c>
       <c r="D7" t="n">
-        <v>813</v>
+        <v>839</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7404999999999999</v>
+        <v>0.7175</v>
       </c>
     </row>
     <row r="8">
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
         <v>7417</v>
       </c>
       <c r="D10" t="n">
-        <v>7450</v>
+        <v>7456</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9956</v>
+        <v>0.9948</v>
       </c>
     </row>
     <row r="11">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1273</v>
+        <v>2295</v>
       </c>
       <c r="C14" t="n">
         <v>24569</v>
       </c>
       <c r="D14" t="n">
-        <v>25842</v>
+        <v>26864</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9506999999999999</v>
+        <v>0.9146</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2729,8 +2729,328 @@
       </c>
       <c r="F85" s="2" t="n"/>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>659</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>659</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>30</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>30</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>254</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>254</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>26</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>26</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>6</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>6</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1022</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1022</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F85"/>
+  <autoFilter ref="A1:F99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>761</v>
       </c>
       <c r="C3" t="n">
-        <v>5097</v>
+        <v>8708</v>
       </c>
       <c r="D3" t="n">
-        <v>5858</v>
+        <v>9469</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.8701000000000001</v>
+        <v>0.9196</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="C4" t="n">
-        <v>14575</v>
+        <v>22465</v>
       </c>
       <c r="D4" t="n">
-        <v>14804</v>
+        <v>22711</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9845</v>
+        <v>0.9892</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>386</v>
+        <v>1283</v>
       </c>
       <c r="C6" t="n">
-        <v>12887</v>
+        <v>18525</v>
       </c>
       <c r="D6" t="n">
-        <v>13273</v>
+        <v>19808</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9709</v>
+        <v>0.9351999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>237</v>
+        <v>350</v>
       </c>
       <c r="C7" t="n">
-        <v>602</v>
+        <v>998</v>
       </c>
       <c r="D7" t="n">
-        <v>839</v>
+        <v>1348</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7175</v>
+        <v>0.7404000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>227</v>
+        <v>1290</v>
       </c>
       <c r="C8" t="n">
-        <v>4255</v>
+        <v>4597</v>
       </c>
       <c r="D8" t="n">
-        <v>4482</v>
+        <v>5887</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9494</v>
+        <v>0.7809</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>151</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
-        <v>158</v>
+        <v>278</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9556999999999999</v>
+        <v>0.9748</v>
       </c>
     </row>
     <row r="10">
@@ -626,13 +626,13 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>7417</v>
+        <v>10747</v>
       </c>
       <c r="D10" t="n">
-        <v>7456</v>
+        <v>10786</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9948</v>
+        <v>0.9964</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>1796</v>
+        <v>2062</v>
       </c>
       <c r="D11" t="n">
-        <v>1836</v>
+        <v>2102</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9782</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>7193</v>
+        <v>11810</v>
       </c>
       <c r="D13" t="n">
-        <v>7211</v>
+        <v>11830</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2295</v>
+        <v>3890</v>
       </c>
       <c r="C14" t="n">
-        <v>24569</v>
+        <v>39020</v>
       </c>
       <c r="D14" t="n">
-        <v>26864</v>
+        <v>42910</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9146</v>
+        <v>0.9093000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3049,8 +3049,336 @@
       </c>
       <c r="F99" s="2" t="n"/>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>3611</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3611</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>17</v>
+      </c>
+      <c r="D102" t="n">
+        <v>7890</v>
+      </c>
+      <c r="E102" t="n">
+        <v>7907</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>0.9979</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>897</v>
+      </c>
+      <c r="D104" t="n">
+        <v>5638</v>
+      </c>
+      <c r="E104" t="n">
+        <v>6535</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>0.8626999999999999</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>113</v>
+      </c>
+      <c r="D105" t="n">
+        <v>396</v>
+      </c>
+      <c r="E105" t="n">
+        <v>509</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>0.778</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1063</v>
+      </c>
+      <c r="D106" t="n">
+        <v>342</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>0.2434</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>120</v>
+      </c>
+      <c r="E107" t="n">
+        <v>120</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3330</v>
+      </c>
+      <c r="E108" t="n">
+        <v>3330</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>266</v>
+      </c>
+      <c r="E109" t="n">
+        <v>266</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2</v>
+      </c>
+      <c r="D111" t="n">
+        <v>4617</v>
+      </c>
+      <c r="E111" t="n">
+        <v>4619</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>0.9995999999999999</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1595</v>
+      </c>
+      <c r="D112" t="n">
+        <v>14451</v>
+      </c>
+      <c r="E112" t="n">
+        <v>16046</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>0.9006000000000001</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F99"/>
+  <autoFilter ref="A1:F113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C4" t="n">
-        <v>22465</v>
+        <v>22467</v>
       </c>
       <c r="D4" t="n">
         <v>22711</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9892</v>
+        <v>0.9893000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3890</v>
+        <v>3887</v>
       </c>
       <c r="C14" t="n">
-        <v>39020</v>
+        <v>39023</v>
       </c>
       <c r="D14" t="n">
         <v>42910</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9093000000000001</v>
+        <v>0.9094</v>
       </c>
     </row>
     <row r="15">
@@ -3107,16 +3107,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D102" t="n">
-        <v>7890</v>
+        <v>7892</v>
       </c>
       <c r="E102" t="n">
         <v>7907</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>0.9979</v>
+        <v>0.9981</v>
       </c>
     </row>
     <row r="103">
@@ -3343,16 +3343,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="D112" t="n">
-        <v>14451</v>
+        <v>14454</v>
       </c>
       <c r="E112" t="n">
         <v>16046</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>0.9006000000000001</v>
+        <v>0.9007999999999999</v>
       </c>
     </row>
     <row r="113">

--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>761</v>
       </c>
       <c r="C3" t="n">
-        <v>8708</v>
+        <v>10030</v>
       </c>
       <c r="D3" t="n">
-        <v>9469</v>
+        <v>10791</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9196</v>
+        <v>0.9295</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>244</v>
+        <v>349</v>
       </c>
       <c r="C4" t="n">
-        <v>22467</v>
+        <v>30277</v>
       </c>
       <c r="D4" t="n">
-        <v>22711</v>
+        <v>30626</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9893000000000001</v>
+        <v>0.9886</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1283</v>
+        <v>1457</v>
       </c>
       <c r="C6" t="n">
-        <v>18525</v>
+        <v>23751</v>
       </c>
       <c r="D6" t="n">
-        <v>19808</v>
+        <v>25208</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9351999999999999</v>
+        <v>0.9422</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>350</v>
       </c>
       <c r="C7" t="n">
-        <v>998</v>
+        <v>1114</v>
       </c>
       <c r="D7" t="n">
-        <v>1348</v>
+        <v>1464</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7404000000000001</v>
+        <v>0.7609</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1290</v>
+        <v>1345</v>
       </c>
       <c r="C8" t="n">
-        <v>4597</v>
+        <v>5152</v>
       </c>
       <c r="D8" t="n">
-        <v>5887</v>
+        <v>6497</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7809</v>
+        <v>0.7929999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>271</v>
+        <v>344</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>351</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9748</v>
+        <v>0.9801000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -626,13 +626,13 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>10747</v>
+        <v>13111</v>
       </c>
       <c r="D10" t="n">
-        <v>10786</v>
+        <v>13150</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9964</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>2062</v>
+        <v>2240</v>
       </c>
       <c r="D11" t="n">
-        <v>2102</v>
+        <v>2280</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.981</v>
+        <v>0.9825</v>
       </c>
     </row>
     <row r="12">
@@ -681,13 +681,13 @@
         <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>11810</v>
+        <v>14412</v>
       </c>
       <c r="D13" t="n">
-        <v>11830</v>
+        <v>14432</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9983</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3887</v>
+        <v>4101</v>
       </c>
       <c r="C14" t="n">
-        <v>39023</v>
+        <v>47333</v>
       </c>
       <c r="D14" t="n">
-        <v>42910</v>
+        <v>51434</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9094</v>
+        <v>0.9203</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3377,8 +3377,336 @@
       </c>
       <c r="F113" s="2" t="n"/>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1322</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1322</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>105</v>
+      </c>
+      <c r="D116" t="n">
+        <v>7810</v>
+      </c>
+      <c r="E116" t="n">
+        <v>7915</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>0.9867</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>174</v>
+      </c>
+      <c r="D118" t="n">
+        <v>5226</v>
+      </c>
+      <c r="E118" t="n">
+        <v>5400</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>0.9678</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>116</v>
+      </c>
+      <c r="E119" t="n">
+        <v>116</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>55</v>
+      </c>
+      <c r="D120" t="n">
+        <v>555</v>
+      </c>
+      <c r="E120" t="n">
+        <v>610</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>0.9098000000000001</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>73</v>
+      </c>
+      <c r="E121" t="n">
+        <v>73</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" t="n">
+        <v>2364</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2364</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>178</v>
+      </c>
+      <c r="E123" t="n">
+        <v>178</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2602</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2602</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>214</v>
+      </c>
+      <c r="D126" t="n">
+        <v>8310</v>
+      </c>
+      <c r="E126" t="n">
+        <v>8524</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>0.9749</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F113"/>
+  <autoFilter ref="A1:F127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C4" t="n">
-        <v>30277</v>
+        <v>30279</v>
       </c>
       <c r="D4" t="n">
         <v>30626</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9886</v>
+        <v>0.9887</v>
       </c>
     </row>
     <row r="5">
@@ -3435,16 +3435,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D116" t="n">
-        <v>7810</v>
+        <v>7812</v>
       </c>
       <c r="E116" t="n">
         <v>7915</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>0.9867</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="117">

--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>761</v>
       </c>
       <c r="C3" t="n">
-        <v>10030</v>
+        <v>11653</v>
       </c>
       <c r="D3" t="n">
-        <v>10791</v>
+        <v>12414</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9295</v>
+        <v>0.9387000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="C4" t="n">
-        <v>30279</v>
+        <v>36234</v>
       </c>
       <c r="D4" t="n">
-        <v>30626</v>
+        <v>36643</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9887</v>
+        <v>0.9887999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1457</v>
+        <v>1486</v>
       </c>
       <c r="C6" t="n">
-        <v>23751</v>
+        <v>28035</v>
       </c>
       <c r="D6" t="n">
-        <v>25208</v>
+        <v>29521</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9422</v>
+        <v>0.9497</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>350</v>
       </c>
       <c r="C7" t="n">
-        <v>1114</v>
+        <v>1252</v>
       </c>
       <c r="D7" t="n">
-        <v>1464</v>
+        <v>1602</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7609</v>
+        <v>0.7815000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1345</v>
+        <v>1400</v>
       </c>
       <c r="C8" t="n">
-        <v>5152</v>
+        <v>5480</v>
       </c>
       <c r="D8" t="n">
-        <v>6497</v>
+        <v>6880</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7929999999999999</v>
+        <v>0.7965000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>344</v>
+        <v>405</v>
       </c>
       <c r="D9" t="n">
-        <v>351</v>
+        <v>412</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9801000000000001</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="10">
@@ -626,13 +626,13 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>13111</v>
+        <v>14962</v>
       </c>
       <c r="D10" t="n">
-        <v>13150</v>
+        <v>15001</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.997</v>
+        <v>0.9974</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>2240</v>
+        <v>2329</v>
       </c>
       <c r="D11" t="n">
-        <v>2280</v>
+        <v>2369</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9825</v>
+        <v>0.9831</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>14412</v>
+        <v>16832</v>
       </c>
       <c r="D13" t="n">
-        <v>14432</v>
+        <v>16860</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9986</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4101</v>
+        <v>4437</v>
       </c>
       <c r="C14" t="n">
-        <v>47333</v>
+        <v>52921</v>
       </c>
       <c r="D14" t="n">
-        <v>51434</v>
+        <v>57358</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9203</v>
+        <v>0.9226000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3705,8 +3705,336 @@
       </c>
       <c r="F127" s="2" t="n"/>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1623</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1623</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>62</v>
+      </c>
+      <c r="D130" t="n">
+        <v>5955</v>
+      </c>
+      <c r="E130" t="n">
+        <v>6017</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>0.9897</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>29</v>
+      </c>
+      <c r="D132" t="n">
+        <v>4284</v>
+      </c>
+      <c r="E132" t="n">
+        <v>4313</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>0.9933</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>138</v>
+      </c>
+      <c r="E133" t="n">
+        <v>138</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>55</v>
+      </c>
+      <c r="D134" t="n">
+        <v>328</v>
+      </c>
+      <c r="E134" t="n">
+        <v>383</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>0.8564000000000001</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>61</v>
+      </c>
+      <c r="E135" t="n">
+        <v>61</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1851</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1851</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>89</v>
+      </c>
+      <c r="E137" t="n">
+        <v>89</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>8</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2420</v>
+      </c>
+      <c r="E139" t="n">
+        <v>2428</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>0.9967</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>336</v>
+      </c>
+      <c r="D140" t="n">
+        <v>5588</v>
+      </c>
+      <c r="E140" t="n">
+        <v>5924</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>0.9433</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F127"/>
+  <autoFilter ref="A1:F141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C6" t="n">
-        <v>28035</v>
+        <v>28036</v>
       </c>
       <c r="D6" t="n">
         <v>29521</v>
@@ -3809,16 +3809,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D132" t="n">
-        <v>4284</v>
+        <v>4285</v>
       </c>
       <c r="E132" t="n">
         <v>4313</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>0.9933</v>
+        <v>0.9934999999999999</v>
       </c>
     </row>
     <row r="133">

--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$155</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C3" t="n">
-        <v>11653</v>
+        <v>12568</v>
       </c>
       <c r="D3" t="n">
-        <v>12414</v>
+        <v>13330</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9387000000000001</v>
+        <v>0.9428</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="C4" t="n">
-        <v>36234</v>
+        <v>38910</v>
       </c>
       <c r="D4" t="n">
-        <v>36643</v>
+        <v>39339</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9887999999999999</v>
+        <v>0.9891</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1485</v>
+        <v>1500</v>
       </c>
       <c r="C6" t="n">
-        <v>28036</v>
+        <v>30193</v>
       </c>
       <c r="D6" t="n">
-        <v>29521</v>
+        <v>31693</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9497</v>
+        <v>0.9527</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C7" t="n">
-        <v>1252</v>
+        <v>1404</v>
       </c>
       <c r="D7" t="n">
-        <v>1602</v>
+        <v>1756</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7815000000000001</v>
+        <v>0.7995</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1400</v>
+        <v>1445</v>
       </c>
       <c r="C8" t="n">
-        <v>5480</v>
+        <v>5926</v>
       </c>
       <c r="D8" t="n">
-        <v>6880</v>
+        <v>7371</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7965000000000001</v>
+        <v>0.804</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>405</v>
+        <v>483</v>
       </c>
       <c r="D9" t="n">
-        <v>412</v>
+        <v>490</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.983</v>
+        <v>0.9856999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>190</v>
       </c>
       <c r="C10" t="n">
-        <v>14962</v>
+        <v>16407</v>
       </c>
       <c r="D10" t="n">
-        <v>15001</v>
+        <v>16597</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9974</v>
+        <v>0.9886</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>2329</v>
+        <v>2390</v>
       </c>
       <c r="D11" t="n">
-        <v>2369</v>
+        <v>2430</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9831</v>
+        <v>0.9834999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="C13" t="n">
-        <v>16832</v>
+        <v>18816</v>
       </c>
       <c r="D13" t="n">
-        <v>16860</v>
+        <v>18915</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9983</v>
+        <v>0.9948</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4437</v>
+        <v>4594</v>
       </c>
       <c r="C14" t="n">
-        <v>52921</v>
+        <v>58162</v>
       </c>
       <c r="D14" t="n">
-        <v>57358</v>
+        <v>62756</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9226000000000001</v>
+        <v>0.9268000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4033,8 +4033,336 @@
       </c>
       <c r="F141" s="2" t="n"/>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="n">
+        <v>915</v>
+      </c>
+      <c r="E143" t="n">
+        <v>916</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>0.9989</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>20</v>
+      </c>
+      <c r="D144" t="n">
+        <v>2676</v>
+      </c>
+      <c r="E144" t="n">
+        <v>2696</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>0.9926</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>15</v>
+      </c>
+      <c r="D146" t="n">
+        <v>2157</v>
+      </c>
+      <c r="E146" t="n">
+        <v>2172</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>0.9931</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" t="n">
+        <v>152</v>
+      </c>
+      <c r="E147" t="n">
+        <v>154</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>0.987</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>45</v>
+      </c>
+      <c r="D148" t="n">
+        <v>446</v>
+      </c>
+      <c r="E148" t="n">
+        <v>491</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>0.9084</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>78</v>
+      </c>
+      <c r="E149" t="n">
+        <v>78</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>151</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1445</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1596</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>0.9054000000000001</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="n">
+        <v>61</v>
+      </c>
+      <c r="E151" t="n">
+        <v>61</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>71</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1984</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2055</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>0.9655</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>157</v>
+      </c>
+      <c r="D154" t="n">
+        <v>5241</v>
+      </c>
+      <c r="E154" t="n">
+        <v>5398</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>0.9709</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F141"/>
+  <autoFilter ref="A1:F155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>762</v>
       </c>
       <c r="C3" t="n">
-        <v>12568</v>
+        <v>12800</v>
       </c>
       <c r="D3" t="n">
-        <v>13330</v>
+        <v>13562</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9428</v>
+        <v>0.9438</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>429</v>
+        <v>484</v>
       </c>
       <c r="C4" t="n">
-        <v>38910</v>
+        <v>39181</v>
       </c>
       <c r="D4" t="n">
-        <v>39339</v>
+        <v>39665</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9891</v>
+        <v>0.9878</v>
       </c>
     </row>
     <row r="5">
@@ -550,13 +550,13 @@
         <v>1500</v>
       </c>
       <c r="C6" t="n">
-        <v>30193</v>
+        <v>30472</v>
       </c>
       <c r="D6" t="n">
-        <v>31693</v>
+        <v>31972</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9527</v>
+        <v>0.9531000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>352</v>
       </c>
       <c r="C7" t="n">
-        <v>1404</v>
+        <v>1473</v>
       </c>
       <c r="D7" t="n">
-        <v>1756</v>
+        <v>1825</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7995</v>
+        <v>0.8070999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1445</v>
+        <v>1452</v>
       </c>
       <c r="C8" t="n">
         <v>5926</v>
       </c>
       <c r="D8" t="n">
-        <v>7371</v>
+        <v>7378</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.804</v>
+        <v>0.8031999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="D9" t="n">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9856999999999999</v>
+        <v>0.9859</v>
       </c>
     </row>
     <row r="10">
@@ -626,13 +626,13 @@
         <v>190</v>
       </c>
       <c r="C10" t="n">
-        <v>16407</v>
+        <v>16763</v>
       </c>
       <c r="D10" t="n">
-        <v>16597</v>
+        <v>16953</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9886</v>
+        <v>0.9887999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>2390</v>
+        <v>2435</v>
       </c>
       <c r="D11" t="n">
-        <v>2430</v>
+        <v>2475</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9834999999999999</v>
+        <v>0.9838</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>99</v>
+        <v>178</v>
       </c>
       <c r="C13" t="n">
-        <v>18816</v>
+        <v>19247</v>
       </c>
       <c r="D13" t="n">
-        <v>18915</v>
+        <v>19425</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9948</v>
+        <v>0.9908</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4594</v>
+        <v>4678</v>
       </c>
       <c r="C14" t="n">
-        <v>58162</v>
+        <v>59496</v>
       </c>
       <c r="D14" t="n">
-        <v>62756</v>
+        <v>64174</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9268000000000001</v>
+        <v>0.9270999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4361,8 +4361,336 @@
       </c>
       <c r="F155" s="2" t="n"/>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>232</v>
+      </c>
+      <c r="E157" t="n">
+        <v>232</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>55</v>
+      </c>
+      <c r="D158" t="n">
+        <v>271</v>
+      </c>
+      <c r="E158" t="n">
+        <v>326</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>0.8312999999999999</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" t="n">
+        <v>279</v>
+      </c>
+      <c r="E160" t="n">
+        <v>279</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>69</v>
+      </c>
+      <c r="E161" t="n">
+        <v>69</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>7</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
+        <v>7</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="n">
+        <v>7</v>
+      </c>
+      <c r="E163" t="n">
+        <v>7</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" t="n">
+        <v>356</v>
+      </c>
+      <c r="E164" t="n">
+        <v>356</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" t="n">
+        <v>45</v>
+      </c>
+      <c r="E165" t="n">
+        <v>45</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>79</v>
+      </c>
+      <c r="D167" t="n">
+        <v>431</v>
+      </c>
+      <c r="E167" t="n">
+        <v>510</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>0.8451000000000001</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>84</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1334</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1418</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>0.9408</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F155"/>
+  <autoFilter ref="A1:F169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F169"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4689,8 +4689,316 @@
       </c>
       <c r="F169" s="2" t="n"/>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F169"/>
+  <autoFilter ref="A1:F183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>762</v>
       </c>
       <c r="C3" t="n">
-        <v>12800</v>
+        <v>14469</v>
       </c>
       <c r="D3" t="n">
-        <v>13562</v>
+        <v>15231</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9438</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>484</v>
+        <v>1271</v>
       </c>
       <c r="C4" t="n">
-        <v>39181</v>
+        <v>43522</v>
       </c>
       <c r="D4" t="n">
-        <v>39665</v>
+        <v>44793</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9878</v>
+        <v>0.9716</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1500</v>
+        <v>1826</v>
       </c>
       <c r="C6" t="n">
-        <v>30472</v>
+        <v>33857</v>
       </c>
       <c r="D6" t="n">
-        <v>31972</v>
+        <v>35683</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9531000000000001</v>
+        <v>0.9488</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>352</v>
       </c>
       <c r="C7" t="n">
-        <v>1473</v>
+        <v>1811</v>
       </c>
       <c r="D7" t="n">
-        <v>1825</v>
+        <v>2163</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8070999999999999</v>
+        <v>0.8373</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1452</v>
+        <v>1599</v>
       </c>
       <c r="C8" t="n">
-        <v>5926</v>
+        <v>6587</v>
       </c>
       <c r="D8" t="n">
-        <v>7378</v>
+        <v>8186</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8031999999999999</v>
+        <v>0.8047</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>490</v>
+        <v>645</v>
       </c>
       <c r="D9" t="n">
-        <v>497</v>
+        <v>652</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9859</v>
+        <v>0.9893000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>190</v>
+        <v>344</v>
       </c>
       <c r="C10" t="n">
-        <v>16763</v>
+        <v>19485</v>
       </c>
       <c r="D10" t="n">
-        <v>16953</v>
+        <v>19829</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9887999999999999</v>
+        <v>0.9826999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>2435</v>
+        <v>2551</v>
       </c>
       <c r="D11" t="n">
-        <v>2475</v>
+        <v>2591</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9838</v>
+        <v>0.9845999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="C13" t="n">
-        <v>19247</v>
+        <v>22875</v>
       </c>
       <c r="D13" t="n">
-        <v>19425</v>
+        <v>23073</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9908</v>
+        <v>0.9914000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4678</v>
+        <v>5106</v>
       </c>
       <c r="C14" t="n">
-        <v>59496</v>
+        <v>71012</v>
       </c>
       <c r="D14" t="n">
-        <v>64174</v>
+        <v>76118</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9270999999999999</v>
+        <v>0.9329000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4997,8 +4997,336 @@
       </c>
       <c r="F183" s="2" t="n"/>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1669</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1669</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>787</v>
+      </c>
+      <c r="D186" t="n">
+        <v>4341</v>
+      </c>
+      <c r="E186" t="n">
+        <v>5128</v>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>0.8465</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>326</v>
+      </c>
+      <c r="D188" t="n">
+        <v>3385</v>
+      </c>
+      <c r="E188" t="n">
+        <v>3711</v>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>0.9122</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" t="n">
+        <v>338</v>
+      </c>
+      <c r="E189" t="n">
+        <v>338</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>147</v>
+      </c>
+      <c r="D190" t="n">
+        <v>661</v>
+      </c>
+      <c r="E190" t="n">
+        <v>808</v>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>0.8181</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>155</v>
+      </c>
+      <c r="E191" t="n">
+        <v>155</v>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>154</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2722</v>
+      </c>
+      <c r="E192" t="n">
+        <v>2876</v>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>0.9465</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" t="n">
+        <v>116</v>
+      </c>
+      <c r="E193" t="n">
+        <v>116</v>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>20</v>
+      </c>
+      <c r="D195" t="n">
+        <v>3628</v>
+      </c>
+      <c r="E195" t="n">
+        <v>3648</v>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>428</v>
+      </c>
+      <c r="D196" t="n">
+        <v>11516</v>
+      </c>
+      <c r="E196" t="n">
+        <v>11944</v>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v>0.9642000000000001</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F183"/>
+  <autoFilter ref="A1:F197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C4" t="n">
-        <v>43522</v>
+        <v>43524</v>
       </c>
       <c r="D4" t="n">
         <v>44793</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9716</v>
+        <v>0.9717</v>
       </c>
     </row>
     <row r="5">
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5106</v>
+        <v>5105</v>
       </c>
       <c r="C14" t="n">
-        <v>71012</v>
+        <v>71013</v>
       </c>
       <c r="D14" t="n">
         <v>76118</v>
@@ -5055,16 +5055,16 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D186" t="n">
-        <v>4341</v>
+        <v>4343</v>
       </c>
       <c r="E186" t="n">
         <v>5128</v>
       </c>
       <c r="F186" s="2" t="n">
-        <v>0.8465</v>
+        <v>0.8469</v>
       </c>
     </row>
     <row r="187">
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D196" t="n">
-        <v>11516</v>
+        <v>11517</v>
       </c>
       <c r="E196" t="n">
         <v>11944</v>

--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$211</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C3" t="n">
-        <v>14469</v>
+        <v>16250</v>
       </c>
       <c r="D3" t="n">
-        <v>15231</v>
+        <v>17014</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9551000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1269</v>
+        <v>1287</v>
       </c>
       <c r="C4" t="n">
-        <v>43524</v>
+        <v>49096</v>
       </c>
       <c r="D4" t="n">
-        <v>44793</v>
+        <v>50383</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9717</v>
+        <v>0.9745</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1826</v>
+        <v>1848</v>
       </c>
       <c r="C6" t="n">
-        <v>33857</v>
+        <v>36802</v>
       </c>
       <c r="D6" t="n">
-        <v>35683</v>
+        <v>38650</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9488</v>
+        <v>0.9521999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>352</v>
       </c>
       <c r="C7" t="n">
-        <v>1811</v>
+        <v>2026</v>
       </c>
       <c r="D7" t="n">
-        <v>2163</v>
+        <v>2378</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8373</v>
+        <v>0.852</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1599</v>
+        <v>1650</v>
       </c>
       <c r="C8" t="n">
-        <v>6587</v>
+        <v>7023</v>
       </c>
       <c r="D8" t="n">
-        <v>8186</v>
+        <v>8673</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8047</v>
+        <v>0.8098000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>645</v>
+        <v>760</v>
       </c>
       <c r="D9" t="n">
-        <v>652</v>
+        <v>767</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9893000000000001</v>
+        <v>0.9909</v>
       </c>
     </row>
     <row r="10">
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="C10" t="n">
-        <v>19485</v>
+        <v>21376</v>
       </c>
       <c r="D10" t="n">
-        <v>19829</v>
+        <v>21741</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9826999999999999</v>
+        <v>0.9832</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>2551</v>
+        <v>2883</v>
       </c>
       <c r="D11" t="n">
-        <v>2591</v>
+        <v>2923</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9845999999999999</v>
+        <v>0.9863</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C13" t="n">
-        <v>22875</v>
+        <v>25944</v>
       </c>
       <c r="D13" t="n">
-        <v>23073</v>
+        <v>26143</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9914000000000001</v>
+        <v>0.9923999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5105</v>
+        <v>5316</v>
       </c>
       <c r="C14" t="n">
-        <v>71013</v>
+        <v>78372</v>
       </c>
       <c r="D14" t="n">
-        <v>76118</v>
+        <v>83688</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9329000000000001</v>
+        <v>0.9365000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F197"/>
+  <dimension ref="A1:F211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5325,8 +5325,336 @@
       </c>
       <c r="F197" s="2" t="n"/>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>2</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1781</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1783</v>
+      </c>
+      <c r="F199" s="2" t="n">
+        <v>0.9989</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>18</v>
+      </c>
+      <c r="D200" t="n">
+        <v>5572</v>
+      </c>
+      <c r="E200" t="n">
+        <v>5590</v>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>0.9968</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>22</v>
+      </c>
+      <c r="D202" t="n">
+        <v>2945</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2967</v>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>0.9926</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" t="n">
+        <v>215</v>
+      </c>
+      <c r="E203" t="n">
+        <v>215</v>
+      </c>
+      <c r="F203" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>51</v>
+      </c>
+      <c r="D204" t="n">
+        <v>436</v>
+      </c>
+      <c r="E204" t="n">
+        <v>487</v>
+      </c>
+      <c r="F204" s="2" t="n">
+        <v>0.8953</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>0</v>
+      </c>
+      <c r="D205" t="n">
+        <v>115</v>
+      </c>
+      <c r="E205" t="n">
+        <v>115</v>
+      </c>
+      <c r="F205" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>21</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1891</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1912</v>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v>0.9890000000000001</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" t="n">
+        <v>332</v>
+      </c>
+      <c r="E207" t="n">
+        <v>332</v>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>1</v>
+      </c>
+      <c r="D209" t="n">
+        <v>3069</v>
+      </c>
+      <c r="E209" t="n">
+        <v>3070</v>
+      </c>
+      <c r="F209" s="2" t="n">
+        <v>0.9997</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>211</v>
+      </c>
+      <c r="D210" t="n">
+        <v>7359</v>
+      </c>
+      <c r="E210" t="n">
+        <v>7570</v>
+      </c>
+      <c r="F210" s="2" t="n">
+        <v>0.9721</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>0</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F197"/>
+  <autoFilter ref="A1:F211"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$225</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>764</v>
       </c>
       <c r="C3" t="n">
-        <v>16250</v>
+        <v>17379</v>
       </c>
       <c r="D3" t="n">
-        <v>17014</v>
+        <v>18143</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9551000000000001</v>
+        <v>0.9579000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1287</v>
+        <v>1323</v>
       </c>
       <c r="C4" t="n">
-        <v>49096</v>
+        <v>51846</v>
       </c>
       <c r="D4" t="n">
-        <v>50383</v>
+        <v>53169</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9745</v>
+        <v>0.9751000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1848</v>
+        <v>1877</v>
       </c>
       <c r="C6" t="n">
-        <v>36802</v>
+        <v>38608</v>
       </c>
       <c r="D6" t="n">
-        <v>38650</v>
+        <v>40485</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9521999999999999</v>
+        <v>0.9536</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>352</v>
       </c>
       <c r="C7" t="n">
-        <v>2026</v>
+        <v>2118</v>
       </c>
       <c r="D7" t="n">
-        <v>2378</v>
+        <v>2470</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.852</v>
+        <v>0.8575</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1650</v>
+        <v>1657</v>
       </c>
       <c r="C8" t="n">
-        <v>7023</v>
+        <v>7530</v>
       </c>
       <c r="D8" t="n">
-        <v>8673</v>
+        <v>9187</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8098000000000001</v>
+        <v>0.8195999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>760</v>
+        <v>865</v>
       </c>
       <c r="D9" t="n">
-        <v>767</v>
+        <v>872</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9909</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="10">
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>365</v>
+        <v>729</v>
       </c>
       <c r="C10" t="n">
-        <v>21376</v>
+        <v>22511</v>
       </c>
       <c r="D10" t="n">
-        <v>21741</v>
+        <v>23240</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9832</v>
+        <v>0.9686</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>2883</v>
+        <v>2998</v>
       </c>
       <c r="D11" t="n">
-        <v>2923</v>
+        <v>3038</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9863</v>
+        <v>0.9868000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -681,13 +681,13 @@
         <v>199</v>
       </c>
       <c r="C13" t="n">
-        <v>25944</v>
+        <v>28131</v>
       </c>
       <c r="D13" t="n">
-        <v>26143</v>
+        <v>28330</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5316</v>
+        <v>5332</v>
       </c>
       <c r="C14" t="n">
-        <v>78372</v>
+        <v>84659</v>
       </c>
       <c r="D14" t="n">
-        <v>83688</v>
+        <v>89991</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9365000000000001</v>
+        <v>0.9407</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F211"/>
+  <dimension ref="A1:F225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5653,8 +5653,336 @@
       </c>
       <c r="F211" s="2" t="n"/>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" s="2" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>0</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1129</v>
+      </c>
+      <c r="E213" t="n">
+        <v>1129</v>
+      </c>
+      <c r="F213" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>36</v>
+      </c>
+      <c r="D214" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E214" t="n">
+        <v>2786</v>
+      </c>
+      <c r="F214" s="2" t="n">
+        <v>0.9871</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" s="2" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>29</v>
+      </c>
+      <c r="D216" t="n">
+        <v>1806</v>
+      </c>
+      <c r="E216" t="n">
+        <v>1835</v>
+      </c>
+      <c r="F216" s="2" t="n">
+        <v>0.9842</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" t="n">
+        <v>92</v>
+      </c>
+      <c r="E217" t="n">
+        <v>92</v>
+      </c>
+      <c r="F217" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>7</v>
+      </c>
+      <c r="D218" t="n">
+        <v>507</v>
+      </c>
+      <c r="E218" t="n">
+        <v>514</v>
+      </c>
+      <c r="F218" s="2" t="n">
+        <v>0.9864000000000001</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>0</v>
+      </c>
+      <c r="D219" t="n">
+        <v>105</v>
+      </c>
+      <c r="E219" t="n">
+        <v>105</v>
+      </c>
+      <c r="F219" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>364</v>
+      </c>
+      <c r="D220" t="n">
+        <v>1135</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1499</v>
+      </c>
+      <c r="F220" s="2" t="n">
+        <v>0.7572</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>0</v>
+      </c>
+      <c r="D221" t="n">
+        <v>115</v>
+      </c>
+      <c r="E221" t="n">
+        <v>115</v>
+      </c>
+      <c r="F221" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" s="2" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>0</v>
+      </c>
+      <c r="D223" t="n">
+        <v>2187</v>
+      </c>
+      <c r="E223" t="n">
+        <v>2187</v>
+      </c>
+      <c r="F223" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>16</v>
+      </c>
+      <c r="D224" t="n">
+        <v>6287</v>
+      </c>
+      <c r="E224" t="n">
+        <v>6303</v>
+      </c>
+      <c r="F224" s="2" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>0</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F211"/>
+  <autoFilter ref="A1:F225"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$239</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>764</v>
       </c>
       <c r="C3" t="n">
-        <v>17379</v>
+        <v>18933</v>
       </c>
       <c r="D3" t="n">
-        <v>18143</v>
+        <v>19697</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9579000000000001</v>
+        <v>0.9612000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1323</v>
+        <v>1365</v>
       </c>
       <c r="C4" t="n">
-        <v>51846</v>
+        <v>54408</v>
       </c>
       <c r="D4" t="n">
-        <v>53169</v>
+        <v>55773</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9751000000000001</v>
+        <v>0.9754999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1877</v>
+        <v>1904</v>
       </c>
       <c r="C6" t="n">
-        <v>38608</v>
+        <v>40191</v>
       </c>
       <c r="D6" t="n">
-        <v>40485</v>
+        <v>42095</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9536</v>
+        <v>0.9548000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>352</v>
       </c>
       <c r="C7" t="n">
-        <v>2118</v>
+        <v>2260</v>
       </c>
       <c r="D7" t="n">
-        <v>2470</v>
+        <v>2612</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8575</v>
+        <v>0.8652</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1657</v>
+        <v>1678</v>
       </c>
       <c r="C8" t="n">
-        <v>7530</v>
+        <v>7992</v>
       </c>
       <c r="D8" t="n">
-        <v>9187</v>
+        <v>9670</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8195999999999999</v>
+        <v>0.8265</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>865</v>
+        <v>939</v>
       </c>
       <c r="D9" t="n">
-        <v>872</v>
+        <v>946</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.992</v>
+        <v>0.9926</v>
       </c>
     </row>
     <row r="10">
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C10" t="n">
-        <v>22511</v>
+        <v>23938</v>
       </c>
       <c r="D10" t="n">
-        <v>23240</v>
+        <v>24668</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9686</v>
+        <v>0.9704</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>2998</v>
+        <v>3194</v>
       </c>
       <c r="D11" t="n">
-        <v>3038</v>
+        <v>3234</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9868000000000001</v>
+        <v>0.9876</v>
       </c>
     </row>
     <row r="12">
@@ -681,13 +681,13 @@
         <v>199</v>
       </c>
       <c r="C13" t="n">
-        <v>28131</v>
+        <v>30086</v>
       </c>
       <c r="D13" t="n">
-        <v>28330</v>
+        <v>30285</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.993</v>
+        <v>0.9934000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5332</v>
+        <v>5530</v>
       </c>
       <c r="C14" t="n">
-        <v>84659</v>
+        <v>91773</v>
       </c>
       <c r="D14" t="n">
-        <v>89991</v>
+        <v>97303</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9407</v>
+        <v>0.9431999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F225"/>
+  <dimension ref="A1:F239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5981,8 +5981,336 @@
       </c>
       <c r="F225" s="2" t="n"/>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" s="2" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>0</v>
+      </c>
+      <c r="D227" t="n">
+        <v>1554</v>
+      </c>
+      <c r="E227" t="n">
+        <v>1554</v>
+      </c>
+      <c r="F227" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>42</v>
+      </c>
+      <c r="D228" t="n">
+        <v>2562</v>
+      </c>
+      <c r="E228" t="n">
+        <v>2604</v>
+      </c>
+      <c r="F228" s="2" t="n">
+        <v>0.9839</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>0</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" s="2" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>27</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1583</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1610</v>
+      </c>
+      <c r="F230" s="2" t="n">
+        <v>0.9832</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>0</v>
+      </c>
+      <c r="D231" t="n">
+        <v>142</v>
+      </c>
+      <c r="E231" t="n">
+        <v>142</v>
+      </c>
+      <c r="F231" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>21</v>
+      </c>
+      <c r="D232" t="n">
+        <v>462</v>
+      </c>
+      <c r="E232" t="n">
+        <v>483</v>
+      </c>
+      <c r="F232" s="2" t="n">
+        <v>0.9565</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>0</v>
+      </c>
+      <c r="D233" t="n">
+        <v>74</v>
+      </c>
+      <c r="E233" t="n">
+        <v>74</v>
+      </c>
+      <c r="F233" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1</v>
+      </c>
+      <c r="D234" t="n">
+        <v>1427</v>
+      </c>
+      <c r="E234" t="n">
+        <v>1428</v>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>0.9993000000000001</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" t="n">
+        <v>196</v>
+      </c>
+      <c r="E235" t="n">
+        <v>196</v>
+      </c>
+      <c r="F235" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>0</v>
+      </c>
+      <c r="D237" t="n">
+        <v>1955</v>
+      </c>
+      <c r="E237" t="n">
+        <v>1955</v>
+      </c>
+      <c r="F237" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>198</v>
+      </c>
+      <c r="D238" t="n">
+        <v>7114</v>
+      </c>
+      <c r="E238" t="n">
+        <v>7312</v>
+      </c>
+      <c r="F238" s="2" t="n">
+        <v>0.9729000000000001</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>0</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F225"/>
+  <autoFilter ref="A1:F239"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$239</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$253</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>764</v>
       </c>
       <c r="C3" t="n">
-        <v>18933</v>
+        <v>20299</v>
       </c>
       <c r="D3" t="n">
-        <v>19697</v>
+        <v>21063</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.9637</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1365</v>
+        <v>1464</v>
       </c>
       <c r="C4" t="n">
-        <v>54408</v>
+        <v>56622</v>
       </c>
       <c r="D4" t="n">
-        <v>55773</v>
+        <v>58086</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9754999999999999</v>
+        <v>0.9748</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1904</v>
+        <v>1950</v>
       </c>
       <c r="C6" t="n">
-        <v>40191</v>
+        <v>41955</v>
       </c>
       <c r="D6" t="n">
-        <v>42095</v>
+        <v>43905</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9548000000000001</v>
+        <v>0.9556</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>352</v>
       </c>
       <c r="C7" t="n">
-        <v>2260</v>
+        <v>2274</v>
       </c>
       <c r="D7" t="n">
-        <v>2612</v>
+        <v>2626</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8652</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1678</v>
+        <v>1734</v>
       </c>
       <c r="C8" t="n">
-        <v>7992</v>
+        <v>8328</v>
       </c>
       <c r="D8" t="n">
-        <v>9670</v>
+        <v>10062</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8265</v>
+        <v>0.8277</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>939</v>
+        <v>1084</v>
       </c>
       <c r="D9" t="n">
-        <v>946</v>
+        <v>1091</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9926</v>
+        <v>0.9936</v>
       </c>
     </row>
     <row r="10">
@@ -626,13 +626,13 @@
         <v>730</v>
       </c>
       <c r="C10" t="n">
-        <v>23938</v>
+        <v>25721</v>
       </c>
       <c r="D10" t="n">
-        <v>24668</v>
+        <v>26451</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9704</v>
+        <v>0.9723999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>3194</v>
+        <v>3258</v>
       </c>
       <c r="D11" t="n">
-        <v>3234</v>
+        <v>3298</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9876</v>
+        <v>0.9879000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -681,13 +681,13 @@
         <v>199</v>
       </c>
       <c r="C13" t="n">
-        <v>30086</v>
+        <v>31921</v>
       </c>
       <c r="D13" t="n">
-        <v>30285</v>
+        <v>32120</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9934000000000001</v>
+        <v>0.9937999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5530</v>
+        <v>5568</v>
       </c>
       <c r="C14" t="n">
-        <v>91773</v>
+        <v>99277</v>
       </c>
       <c r="D14" t="n">
-        <v>97303</v>
+        <v>104845</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9431999999999999</v>
+        <v>0.9469</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F239"/>
+  <dimension ref="A1:F253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6309,8 +6309,336 @@
       </c>
       <c r="F239" s="2" t="n"/>
     </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" s="2" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>0</v>
+      </c>
+      <c r="D241" t="n">
+        <v>1366</v>
+      </c>
+      <c r="E241" t="n">
+        <v>1366</v>
+      </c>
+      <c r="F241" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>99</v>
+      </c>
+      <c r="D242" t="n">
+        <v>2214</v>
+      </c>
+      <c r="E242" t="n">
+        <v>2313</v>
+      </c>
+      <c r="F242" s="2" t="n">
+        <v>0.9571999999999999</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>0</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" s="2" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>46</v>
+      </c>
+      <c r="D244" t="n">
+        <v>1764</v>
+      </c>
+      <c r="E244" t="n">
+        <v>1810</v>
+      </c>
+      <c r="F244" s="2" t="n">
+        <v>0.9745999999999999</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>0</v>
+      </c>
+      <c r="D245" t="n">
+        <v>14</v>
+      </c>
+      <c r="E245" t="n">
+        <v>14</v>
+      </c>
+      <c r="F245" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>56</v>
+      </c>
+      <c r="D246" t="n">
+        <v>336</v>
+      </c>
+      <c r="E246" t="n">
+        <v>392</v>
+      </c>
+      <c r="F246" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" t="n">
+        <v>145</v>
+      </c>
+      <c r="E247" t="n">
+        <v>145</v>
+      </c>
+      <c r="F247" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>0</v>
+      </c>
+      <c r="D248" t="n">
+        <v>1783</v>
+      </c>
+      <c r="E248" t="n">
+        <v>1783</v>
+      </c>
+      <c r="F248" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>0</v>
+      </c>
+      <c r="D249" t="n">
+        <v>64</v>
+      </c>
+      <c r="E249" t="n">
+        <v>64</v>
+      </c>
+      <c r="F249" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>0</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" s="2" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>0</v>
+      </c>
+      <c r="D251" t="n">
+        <v>1835</v>
+      </c>
+      <c r="E251" t="n">
+        <v>1835</v>
+      </c>
+      <c r="F251" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>38</v>
+      </c>
+      <c r="D252" t="n">
+        <v>7504</v>
+      </c>
+      <c r="E252" t="n">
+        <v>7542</v>
+      </c>
+      <c r="F252" s="2" t="n">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>0</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F239"/>
+  <autoFilter ref="A1:F253"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$253</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$267</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>764</v>
       </c>
       <c r="C3" t="n">
-        <v>20299</v>
+        <v>20677</v>
       </c>
       <c r="D3" t="n">
-        <v>21063</v>
+        <v>21441</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9637</v>
+        <v>0.9643999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1464</v>
+        <v>1526</v>
       </c>
       <c r="C4" t="n">
-        <v>56622</v>
+        <v>57236</v>
       </c>
       <c r="D4" t="n">
-        <v>58086</v>
+        <v>58762</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9748</v>
+        <v>0.9740000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -550,13 +550,13 @@
         <v>1950</v>
       </c>
       <c r="C6" t="n">
-        <v>41955</v>
+        <v>42096</v>
       </c>
       <c r="D6" t="n">
-        <v>43905</v>
+        <v>44046</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9556</v>
+        <v>0.9556999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1734</v>
+        <v>1771</v>
       </c>
       <c r="C8" t="n">
         <v>8328</v>
       </c>
       <c r="D8" t="n">
-        <v>10062</v>
+        <v>10099</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8277</v>
+        <v>0.8245999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>1084</v>
+        <v>1137</v>
       </c>
       <c r="D9" t="n">
-        <v>1091</v>
+        <v>1144</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9936</v>
+        <v>0.9939</v>
       </c>
     </row>
     <row r="10">
@@ -626,13 +626,13 @@
         <v>730</v>
       </c>
       <c r="C10" t="n">
-        <v>25721</v>
+        <v>26337</v>
       </c>
       <c r="D10" t="n">
-        <v>26451</v>
+        <v>27067</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9723999999999999</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="11">
@@ -645,10 +645,10 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>3258</v>
+        <v>3269</v>
       </c>
       <c r="D11" t="n">
-        <v>3298</v>
+        <v>3309</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0.9879000000000001</v>
@@ -678,13 +678,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C13" t="n">
-        <v>31921</v>
+        <v>32363</v>
       </c>
       <c r="D13" t="n">
-        <v>32120</v>
+        <v>32565</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0.9937999999999999</v>
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5568</v>
+        <v>5717</v>
       </c>
       <c r="C14" t="n">
-        <v>99277</v>
+        <v>101830</v>
       </c>
       <c r="D14" t="n">
-        <v>104845</v>
+        <v>107547</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9469</v>
+        <v>0.9468000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F253"/>
+  <dimension ref="A1:F267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6637,8 +6637,334 @@
       </c>
       <c r="F253" s="2" t="n"/>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>0</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" s="2" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>0</v>
+      </c>
+      <c r="D255" t="n">
+        <v>378</v>
+      </c>
+      <c r="E255" t="n">
+        <v>378</v>
+      </c>
+      <c r="F255" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>62</v>
+      </c>
+      <c r="D256" t="n">
+        <v>614</v>
+      </c>
+      <c r="E256" t="n">
+        <v>676</v>
+      </c>
+      <c r="F256" s="2" t="n">
+        <v>0.9083</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>0</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" s="2" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>0</v>
+      </c>
+      <c r="D258" t="n">
+        <v>141</v>
+      </c>
+      <c r="E258" t="n">
+        <v>141</v>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>0</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" s="2" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>37</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
+        <v>37</v>
+      </c>
+      <c r="F260" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>0</v>
+      </c>
+      <c r="D261" t="n">
+        <v>53</v>
+      </c>
+      <c r="E261" t="n">
+        <v>53</v>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>0</v>
+      </c>
+      <c r="D262" t="n">
+        <v>616</v>
+      </c>
+      <c r="E262" t="n">
+        <v>616</v>
+      </c>
+      <c r="F262" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>0</v>
+      </c>
+      <c r="D263" t="n">
+        <v>11</v>
+      </c>
+      <c r="E263" t="n">
+        <v>11</v>
+      </c>
+      <c r="F263" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>0</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" s="2" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>3</v>
+      </c>
+      <c r="D265" t="n">
+        <v>442</v>
+      </c>
+      <c r="E265" t="n">
+        <v>445</v>
+      </c>
+      <c r="F265" s="2" t="n">
+        <v>0.9933</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>149</v>
+      </c>
+      <c r="D266" t="n">
+        <v>2553</v>
+      </c>
+      <c r="E266" t="n">
+        <v>2702</v>
+      </c>
+      <c r="F266" s="2" t="n">
+        <v>0.9449</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+      <c r="F267" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F253"/>
+  <autoFilter ref="A1:F267"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$281</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F267"/>
+  <dimension ref="A1:F281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6963,8 +6963,316 @@
       </c>
       <c r="F267" s="2" t="n"/>
     </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>0</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" s="2" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>0</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0</v>
+      </c>
+      <c r="F269" s="2" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>0</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" t="n">
+        <v>0</v>
+      </c>
+      <c r="F270" s="2" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>0</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" s="2" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>0</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" s="2" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>0</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" s="2" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>0</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" s="2" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>0</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+      <c r="F275" s="2" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>0</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" s="2" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>0</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" s="2" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>0</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" s="2" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>0</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" s="2" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>0</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" s="2" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>0</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F267"/>
+  <autoFilter ref="A1:F281"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$295</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>764</v>
+        <v>778</v>
       </c>
       <c r="C3" t="n">
-        <v>20677</v>
+        <v>23475</v>
       </c>
       <c r="D3" t="n">
-        <v>21441</v>
+        <v>24253</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9643999999999999</v>
+        <v>0.9679000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1526</v>
+        <v>1808</v>
       </c>
       <c r="C4" t="n">
-        <v>57236</v>
+        <v>61668</v>
       </c>
       <c r="D4" t="n">
-        <v>58762</v>
+        <v>63476</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9740000000000001</v>
+        <v>0.9715</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1950</v>
+        <v>2081</v>
       </c>
       <c r="C6" t="n">
-        <v>42096</v>
+        <v>47959</v>
       </c>
       <c r="D6" t="n">
-        <v>44046</v>
+        <v>50040</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9556999999999999</v>
+        <v>0.9584</v>
       </c>
     </row>
     <row r="7">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1771</v>
+        <v>2153</v>
       </c>
       <c r="C8" t="n">
-        <v>8328</v>
+        <v>8633</v>
       </c>
       <c r="D8" t="n">
-        <v>10099</v>
+        <v>10786</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8245999999999999</v>
+        <v>0.8004000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>1137</v>
+        <v>1488</v>
       </c>
       <c r="D9" t="n">
-        <v>1144</v>
+        <v>1495</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9939</v>
+        <v>0.9953</v>
       </c>
     </row>
     <row r="10">
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>730</v>
+        <v>1345</v>
       </c>
       <c r="C10" t="n">
-        <v>26337</v>
+        <v>29682</v>
       </c>
       <c r="D10" t="n">
-        <v>27067</v>
+        <v>31027</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.973</v>
+        <v>0.9567</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>3269</v>
+        <v>3335</v>
       </c>
       <c r="D11" t="n">
-        <v>3309</v>
+        <v>3375</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9879000000000001</v>
+        <v>0.9881</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="C13" t="n">
-        <v>32363</v>
+        <v>36138</v>
       </c>
       <c r="D13" t="n">
-        <v>32565</v>
+        <v>36373</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9937999999999999</v>
+        <v>0.9934999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5717</v>
+        <v>6225</v>
       </c>
       <c r="C14" t="n">
-        <v>101830</v>
+        <v>115802</v>
       </c>
       <c r="D14" t="n">
-        <v>107547</v>
+        <v>122027</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9468000000000001</v>
+        <v>0.9490000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F281"/>
+  <dimension ref="A1:F295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7271,8 +7271,334 @@
       </c>
       <c r="F281" s="2" t="n"/>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>0</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" s="2" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>14</v>
+      </c>
+      <c r="D283" t="n">
+        <v>2798</v>
+      </c>
+      <c r="E283" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F283" s="2" t="n">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>282</v>
+      </c>
+      <c r="D284" t="n">
+        <v>4432</v>
+      </c>
+      <c r="E284" t="n">
+        <v>4714</v>
+      </c>
+      <c r="F284" s="2" t="n">
+        <v>0.9401999999999999</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>0</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" s="2" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>131</v>
+      </c>
+      <c r="D286" t="n">
+        <v>5863</v>
+      </c>
+      <c r="E286" t="n">
+        <v>5994</v>
+      </c>
+      <c r="F286" s="2" t="n">
+        <v>0.9781</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>0</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" t="n">
+        <v>0</v>
+      </c>
+      <c r="F287" s="2" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>382</v>
+      </c>
+      <c r="D288" t="n">
+        <v>305</v>
+      </c>
+      <c r="E288" t="n">
+        <v>687</v>
+      </c>
+      <c r="F288" s="2" t="n">
+        <v>0.444</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>0</v>
+      </c>
+      <c r="D289" t="n">
+        <v>351</v>
+      </c>
+      <c r="E289" t="n">
+        <v>351</v>
+      </c>
+      <c r="F289" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>615</v>
+      </c>
+      <c r="D290" t="n">
+        <v>3345</v>
+      </c>
+      <c r="E290" t="n">
+        <v>3960</v>
+      </c>
+      <c r="F290" s="2" t="n">
+        <v>0.8447</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>0</v>
+      </c>
+      <c r="D291" t="n">
+        <v>66</v>
+      </c>
+      <c r="E291" t="n">
+        <v>66</v>
+      </c>
+      <c r="F291" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>0</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" t="n">
+        <v>0</v>
+      </c>
+      <c r="F292" s="2" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>33</v>
+      </c>
+      <c r="D293" t="n">
+        <v>3775</v>
+      </c>
+      <c r="E293" t="n">
+        <v>3808</v>
+      </c>
+      <c r="F293" s="2" t="n">
+        <v>0.9913</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>508</v>
+      </c>
+      <c r="D294" t="n">
+        <v>13972</v>
+      </c>
+      <c r="E294" t="n">
+        <v>14480</v>
+      </c>
+      <c r="F294" s="2" t="n">
+        <v>0.9649</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>0</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0</v>
+      </c>
+      <c r="F295" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F281"/>
+  <autoFilter ref="A1:F295"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$309</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>778</v>
       </c>
       <c r="C3" t="n">
-        <v>23475</v>
+        <v>25112</v>
       </c>
       <c r="D3" t="n">
-        <v>24253</v>
+        <v>25890</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9679000000000001</v>
+        <v>0.9699</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1808</v>
+        <v>1904</v>
       </c>
       <c r="C4" t="n">
-        <v>61668</v>
+        <v>66052</v>
       </c>
       <c r="D4" t="n">
-        <v>63476</v>
+        <v>67956</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9715</v>
+        <v>0.972</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2081</v>
+        <v>2420</v>
       </c>
       <c r="C6" t="n">
-        <v>47959</v>
+        <v>53716</v>
       </c>
       <c r="D6" t="n">
-        <v>50040</v>
+        <v>56136</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9584</v>
+        <v>0.9569</v>
       </c>
     </row>
     <row r="7">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2153</v>
+        <v>2167</v>
       </c>
       <c r="C8" t="n">
-        <v>8633</v>
+        <v>9270</v>
       </c>
       <c r="D8" t="n">
-        <v>10786</v>
+        <v>11437</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8004000000000001</v>
+        <v>0.8105</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>1488</v>
+        <v>1623</v>
       </c>
       <c r="D9" t="n">
-        <v>1495</v>
+        <v>1630</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9953</v>
+        <v>0.9956999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1345</v>
+        <v>1454</v>
       </c>
       <c r="C10" t="n">
-        <v>29682</v>
+        <v>32633</v>
       </c>
       <c r="D10" t="n">
-        <v>31027</v>
+        <v>34087</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9567</v>
+        <v>0.9573</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>3335</v>
+        <v>3380</v>
       </c>
       <c r="D11" t="n">
-        <v>3375</v>
+        <v>3420</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9881</v>
+        <v>0.9883</v>
       </c>
     </row>
     <row r="12">
@@ -681,13 +681,13 @@
         <v>235</v>
       </c>
       <c r="C13" t="n">
-        <v>36138</v>
+        <v>39032</v>
       </c>
       <c r="D13" t="n">
-        <v>36373</v>
+        <v>39267</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9934999999999999</v>
+        <v>0.9940000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6225</v>
+        <v>6528</v>
       </c>
       <c r="C14" t="n">
-        <v>115802</v>
+        <v>126250</v>
       </c>
       <c r="D14" t="n">
-        <v>122027</v>
+        <v>132778</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9490000000000001</v>
+        <v>0.9508</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F295"/>
+  <dimension ref="A1:F309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7597,8 +7597,334 @@
       </c>
       <c r="F295" s="2" t="n"/>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>0</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0</v>
+      </c>
+      <c r="F296" s="2" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>0</v>
+      </c>
+      <c r="D297" t="n">
+        <v>1637</v>
+      </c>
+      <c r="E297" t="n">
+        <v>1637</v>
+      </c>
+      <c r="F297" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>96</v>
+      </c>
+      <c r="D298" t="n">
+        <v>4384</v>
+      </c>
+      <c r="E298" t="n">
+        <v>4480</v>
+      </c>
+      <c r="F298" s="2" t="n">
+        <v>0.9786</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>0</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0</v>
+      </c>
+      <c r="F299" s="2" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>339</v>
+      </c>
+      <c r="D300" t="n">
+        <v>5757</v>
+      </c>
+      <c r="E300" t="n">
+        <v>6096</v>
+      </c>
+      <c r="F300" s="2" t="n">
+        <v>0.9444</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>0</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" t="n">
+        <v>0</v>
+      </c>
+      <c r="F301" s="2" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>14</v>
+      </c>
+      <c r="D302" t="n">
+        <v>637</v>
+      </c>
+      <c r="E302" t="n">
+        <v>651</v>
+      </c>
+      <c r="F302" s="2" t="n">
+        <v>0.9784999999999999</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>0</v>
+      </c>
+      <c r="D303" t="n">
+        <v>135</v>
+      </c>
+      <c r="E303" t="n">
+        <v>135</v>
+      </c>
+      <c r="F303" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>109</v>
+      </c>
+      <c r="D304" t="n">
+        <v>2951</v>
+      </c>
+      <c r="E304" t="n">
+        <v>3060</v>
+      </c>
+      <c r="F304" s="2" t="n">
+        <v>0.9643999999999999</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>0</v>
+      </c>
+      <c r="D305" t="n">
+        <v>45</v>
+      </c>
+      <c r="E305" t="n">
+        <v>45</v>
+      </c>
+      <c r="F305" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>0</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="n">
+        <v>0</v>
+      </c>
+      <c r="F306" s="2" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>0</v>
+      </c>
+      <c r="D307" t="n">
+        <v>2894</v>
+      </c>
+      <c r="E307" t="n">
+        <v>2894</v>
+      </c>
+      <c r="F307" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>303</v>
+      </c>
+      <c r="D308" t="n">
+        <v>10448</v>
+      </c>
+      <c r="E308" t="n">
+        <v>10751</v>
+      </c>
+      <c r="F308" s="2" t="n">
+        <v>0.9718000000000001</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>0</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0</v>
+      </c>
+      <c r="F309" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F295"/>
+  <autoFilter ref="A1:F309"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$309</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$323</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,13 +495,13 @@
         <v>778</v>
       </c>
       <c r="C3" t="n">
-        <v>25112</v>
+        <v>26706</v>
       </c>
       <c r="D3" t="n">
-        <v>25890</v>
+        <v>27484</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9699</v>
+        <v>0.9717</v>
       </c>
     </row>
     <row r="4">
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1904</v>
+        <v>1964</v>
       </c>
       <c r="C4" t="n">
-        <v>66052</v>
+        <v>68261</v>
       </c>
       <c r="D4" t="n">
-        <v>67956</v>
+        <v>70225</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.972</v>
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2420</v>
+        <v>2441</v>
       </c>
       <c r="C6" t="n">
-        <v>53716</v>
+        <v>55924</v>
       </c>
       <c r="D6" t="n">
-        <v>56136</v>
+        <v>58365</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9569</v>
+        <v>0.9581999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2167</v>
+        <v>2171</v>
       </c>
       <c r="C8" t="n">
-        <v>9270</v>
+        <v>9621</v>
       </c>
       <c r="D8" t="n">
-        <v>11437</v>
+        <v>11792</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8105</v>
+        <v>0.8159000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1623</v>
+        <v>1807</v>
       </c>
       <c r="D9" t="n">
-        <v>1630</v>
+        <v>1819</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9956999999999999</v>
+        <v>0.9934000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -626,13 +626,13 @@
         <v>1454</v>
       </c>
       <c r="C10" t="n">
-        <v>32633</v>
+        <v>34195</v>
       </c>
       <c r="D10" t="n">
-        <v>34087</v>
+        <v>35649</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9573</v>
+        <v>0.9592000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>3380</v>
+        <v>3476</v>
       </c>
       <c r="D11" t="n">
-        <v>3420</v>
+        <v>3516</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9883</v>
+        <v>0.9886</v>
       </c>
     </row>
     <row r="12">
@@ -681,13 +681,13 @@
         <v>235</v>
       </c>
       <c r="C13" t="n">
-        <v>39032</v>
+        <v>41448</v>
       </c>
       <c r="D13" t="n">
-        <v>39267</v>
+        <v>41683</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9940000000000001</v>
+        <v>0.9944</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6528</v>
+        <v>6662</v>
       </c>
       <c r="C14" t="n">
-        <v>126250</v>
+        <v>133290</v>
       </c>
       <c r="D14" t="n">
-        <v>132778</v>
+        <v>139952</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9508</v>
+        <v>0.9523999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F309"/>
+  <dimension ref="A1:F323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7923,8 +7923,334 @@
       </c>
       <c r="F309" s="2" t="n"/>
     </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>0</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" t="n">
+        <v>0</v>
+      </c>
+      <c r="F310" s="2" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>0</v>
+      </c>
+      <c r="D311" t="n">
+        <v>1594</v>
+      </c>
+      <c r="E311" t="n">
+        <v>1594</v>
+      </c>
+      <c r="F311" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>60</v>
+      </c>
+      <c r="D312" t="n">
+        <v>2209</v>
+      </c>
+      <c r="E312" t="n">
+        <v>2269</v>
+      </c>
+      <c r="F312" s="2" t="n">
+        <v>0.9736</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>0</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" t="n">
+        <v>0</v>
+      </c>
+      <c r="F313" s="2" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>21</v>
+      </c>
+      <c r="D314" t="n">
+        <v>2208</v>
+      </c>
+      <c r="E314" t="n">
+        <v>2229</v>
+      </c>
+      <c r="F314" s="2" t="n">
+        <v>0.9906</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>0</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0</v>
+      </c>
+      <c r="E315" t="n">
+        <v>0</v>
+      </c>
+      <c r="F315" s="2" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>4</v>
+      </c>
+      <c r="D316" t="n">
+        <v>351</v>
+      </c>
+      <c r="E316" t="n">
+        <v>355</v>
+      </c>
+      <c r="F316" s="2" t="n">
+        <v>0.9887</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>5</v>
+      </c>
+      <c r="D317" t="n">
+        <v>184</v>
+      </c>
+      <c r="E317" t="n">
+        <v>189</v>
+      </c>
+      <c r="F317" s="2" t="n">
+        <v>0.9734999999999999</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>0</v>
+      </c>
+      <c r="D318" t="n">
+        <v>1562</v>
+      </c>
+      <c r="E318" t="n">
+        <v>1562</v>
+      </c>
+      <c r="F318" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>0</v>
+      </c>
+      <c r="D319" t="n">
+        <v>96</v>
+      </c>
+      <c r="E319" t="n">
+        <v>96</v>
+      </c>
+      <c r="F319" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>0</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" t="n">
+        <v>0</v>
+      </c>
+      <c r="F320" s="2" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>0</v>
+      </c>
+      <c r="D321" t="n">
+        <v>2416</v>
+      </c>
+      <c r="E321" t="n">
+        <v>2416</v>
+      </c>
+      <c r="F321" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>134</v>
+      </c>
+      <c r="D322" t="n">
+        <v>7040</v>
+      </c>
+      <c r="E322" t="n">
+        <v>7174</v>
+      </c>
+      <c r="F322" s="2" t="n">
+        <v>0.9813</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>0</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>0</v>
+      </c>
+      <c r="F323" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F309"/>
+  <autoFilter ref="A1:F323"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$323</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$337</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="C3" t="n">
-        <v>26706</v>
+        <v>28014</v>
       </c>
       <c r="D3" t="n">
-        <v>27484</v>
+        <v>28796</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9717</v>
+        <v>0.9728</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1964</v>
+        <v>1976</v>
       </c>
       <c r="C4" t="n">
-        <v>68261</v>
+        <v>70352</v>
       </c>
       <c r="D4" t="n">
-        <v>70225</v>
+        <v>72328</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.972</v>
+        <v>0.9727</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2441</v>
+        <v>2470</v>
       </c>
       <c r="C6" t="n">
-        <v>55924</v>
+        <v>57759</v>
       </c>
       <c r="D6" t="n">
-        <v>58365</v>
+        <v>60229</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9581999999999999</v>
+        <v>0.9590000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2171</v>
+        <v>2201</v>
       </c>
       <c r="C8" t="n">
-        <v>9621</v>
+        <v>9972</v>
       </c>
       <c r="D8" t="n">
-        <v>11792</v>
+        <v>12173</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8159000000000001</v>
+        <v>0.8192</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1807</v>
+        <v>2127</v>
       </c>
       <c r="D9" t="n">
-        <v>1819</v>
+        <v>2139</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9934000000000001</v>
+        <v>0.9944</v>
       </c>
     </row>
     <row r="10">
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1454</v>
+        <v>1496</v>
       </c>
       <c r="C10" t="n">
-        <v>34195</v>
+        <v>36482</v>
       </c>
       <c r="D10" t="n">
-        <v>35649</v>
+        <v>37978</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9606</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>3476</v>
+        <v>3528</v>
       </c>
       <c r="D11" t="n">
-        <v>3516</v>
+        <v>3568</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9886</v>
+        <v>0.9887999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -681,13 +681,13 @@
         <v>235</v>
       </c>
       <c r="C13" t="n">
-        <v>41448</v>
+        <v>43246</v>
       </c>
       <c r="D13" t="n">
-        <v>41683</v>
+        <v>43481</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9944</v>
+        <v>0.9945999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6662</v>
+        <v>7338</v>
       </c>
       <c r="C14" t="n">
-        <v>133290</v>
+        <v>140136</v>
       </c>
       <c r="D14" t="n">
-        <v>139952</v>
+        <v>147474</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9523999999999999</v>
+        <v>0.9501999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F323"/>
+  <dimension ref="A1:F337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8249,8 +8249,334 @@
       </c>
       <c r="F323" s="2" t="n"/>
     </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>0</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" t="n">
+        <v>0</v>
+      </c>
+      <c r="F324" s="2" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>4</v>
+      </c>
+      <c r="D325" t="n">
+        <v>1308</v>
+      </c>
+      <c r="E325" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F325" s="2" t="n">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>12</v>
+      </c>
+      <c r="D326" t="n">
+        <v>2091</v>
+      </c>
+      <c r="E326" t="n">
+        <v>2103</v>
+      </c>
+      <c r="F326" s="2" t="n">
+        <v>0.9943000000000001</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>0</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0</v>
+      </c>
+      <c r="E327" t="n">
+        <v>0</v>
+      </c>
+      <c r="F327" s="2" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>29</v>
+      </c>
+      <c r="D328" t="n">
+        <v>1835</v>
+      </c>
+      <c r="E328" t="n">
+        <v>1864</v>
+      </c>
+      <c r="F328" s="2" t="n">
+        <v>0.9843999999999999</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>0</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0</v>
+      </c>
+      <c r="E329" t="n">
+        <v>0</v>
+      </c>
+      <c r="F329" s="2" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>30</v>
+      </c>
+      <c r="D330" t="n">
+        <v>351</v>
+      </c>
+      <c r="E330" t="n">
+        <v>381</v>
+      </c>
+      <c r="F330" s="2" t="n">
+        <v>0.9213</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>0</v>
+      </c>
+      <c r="D331" t="n">
+        <v>320</v>
+      </c>
+      <c r="E331" t="n">
+        <v>320</v>
+      </c>
+      <c r="F331" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>42</v>
+      </c>
+      <c r="D332" t="n">
+        <v>2287</v>
+      </c>
+      <c r="E332" t="n">
+        <v>2329</v>
+      </c>
+      <c r="F332" s="2" t="n">
+        <v>0.982</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>0</v>
+      </c>
+      <c r="D333" t="n">
+        <v>52</v>
+      </c>
+      <c r="E333" t="n">
+        <v>52</v>
+      </c>
+      <c r="F333" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>0</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" t="n">
+        <v>0</v>
+      </c>
+      <c r="F334" s="2" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>0</v>
+      </c>
+      <c r="D335" t="n">
+        <v>1798</v>
+      </c>
+      <c r="E335" t="n">
+        <v>1798</v>
+      </c>
+      <c r="F335" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>676</v>
+      </c>
+      <c r="D336" t="n">
+        <v>6846</v>
+      </c>
+      <c r="E336" t="n">
+        <v>7522</v>
+      </c>
+      <c r="F336" s="2" t="n">
+        <v>0.9101</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>0</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0</v>
+      </c>
+      <c r="E337" t="n">
+        <v>0</v>
+      </c>
+      <c r="F337" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F323"/>
+  <autoFilter ref="A1:F337"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$337</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$351</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F337"/>
+  <dimension ref="A1:F351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8575,8 +8575,316 @@
       </c>
       <c r="F337" s="2" t="n"/>
     </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>0</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" t="n">
+        <v>0</v>
+      </c>
+      <c r="F338" s="2" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>0</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0</v>
+      </c>
+      <c r="E339" t="n">
+        <v>0</v>
+      </c>
+      <c r="F339" s="2" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>0</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0</v>
+      </c>
+      <c r="E340" t="n">
+        <v>0</v>
+      </c>
+      <c r="F340" s="2" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>0</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" t="n">
+        <v>0</v>
+      </c>
+      <c r="F341" s="2" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>0</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" t="n">
+        <v>0</v>
+      </c>
+      <c r="F342" s="2" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>0</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0</v>
+      </c>
+      <c r="E343" t="n">
+        <v>0</v>
+      </c>
+      <c r="F343" s="2" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>0</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0</v>
+      </c>
+      <c r="E344" t="n">
+        <v>0</v>
+      </c>
+      <c r="F344" s="2" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>0</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0</v>
+      </c>
+      <c r="E345" t="n">
+        <v>0</v>
+      </c>
+      <c r="F345" s="2" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>0</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0</v>
+      </c>
+      <c r="E346" t="n">
+        <v>0</v>
+      </c>
+      <c r="F346" s="2" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>0</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0</v>
+      </c>
+      <c r="E347" t="n">
+        <v>0</v>
+      </c>
+      <c r="F347" s="2" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>0</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0</v>
+      </c>
+      <c r="E348" t="n">
+        <v>0</v>
+      </c>
+      <c r="F348" s="2" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>0</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0</v>
+      </c>
+      <c r="E349" t="n">
+        <v>0</v>
+      </c>
+      <c r="F349" s="2" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>0</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0</v>
+      </c>
+      <c r="E350" t="n">
+        <v>0</v>
+      </c>
+      <c r="F350" s="2" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>0</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" t="n">
+        <v>0</v>
+      </c>
+      <c r="F351" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F337"/>
+  <autoFilter ref="A1:F351"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$351</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$365</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>782</v>
+        <v>807</v>
       </c>
       <c r="C3" t="n">
-        <v>28014</v>
+        <v>31591</v>
       </c>
       <c r="D3" t="n">
-        <v>28796</v>
+        <v>32398</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9728</v>
+        <v>0.9751000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1976</v>
+        <v>2138</v>
       </c>
       <c r="C4" t="n">
-        <v>70352</v>
+        <v>74950</v>
       </c>
       <c r="D4" t="n">
-        <v>72328</v>
+        <v>77088</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9727</v>
+        <v>0.9723000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2470</v>
+        <v>2575</v>
       </c>
       <c r="C6" t="n">
-        <v>57759</v>
+        <v>61875</v>
       </c>
       <c r="D6" t="n">
-        <v>60229</v>
+        <v>64450</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9590000000000001</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="7">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2201</v>
+        <v>2277</v>
       </c>
       <c r="C8" t="n">
-        <v>9972</v>
+        <v>10822</v>
       </c>
       <c r="D8" t="n">
-        <v>12173</v>
+        <v>13099</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8192</v>
+        <v>0.8262</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>2127</v>
+        <v>2504</v>
       </c>
       <c r="D9" t="n">
-        <v>2139</v>
+        <v>2517</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9944</v>
+        <v>0.9948</v>
       </c>
     </row>
     <row r="10">
@@ -626,13 +626,13 @@
         <v>1496</v>
       </c>
       <c r="C10" t="n">
-        <v>36482</v>
+        <v>40040</v>
       </c>
       <c r="D10" t="n">
-        <v>37978</v>
+        <v>41536</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9606</v>
+        <v>0.9640000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>3528</v>
+        <v>3722</v>
       </c>
       <c r="D11" t="n">
-        <v>3568</v>
+        <v>3762</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9887999999999999</v>
+        <v>0.9893999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -681,13 +681,13 @@
         <v>235</v>
       </c>
       <c r="C13" t="n">
-        <v>43246</v>
+        <v>47000</v>
       </c>
       <c r="D13" t="n">
-        <v>43481</v>
+        <v>47235</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9945999999999999</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7338</v>
+        <v>8118</v>
       </c>
       <c r="C14" t="n">
-        <v>140136</v>
+        <v>151910</v>
       </c>
       <c r="D14" t="n">
-        <v>147474</v>
+        <v>160028</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9501999999999999</v>
+        <v>0.9493</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F351"/>
+  <dimension ref="A1:F365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8883,8 +8883,334 @@
       </c>
       <c r="F351" s="2" t="n"/>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>0</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" t="n">
+        <v>0</v>
+      </c>
+      <c r="F352" s="2" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>25</v>
+      </c>
+      <c r="D353" t="n">
+        <v>3577</v>
+      </c>
+      <c r="E353" t="n">
+        <v>3602</v>
+      </c>
+      <c r="F353" s="2" t="n">
+        <v>0.9931</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>162</v>
+      </c>
+      <c r="D354" t="n">
+        <v>4598</v>
+      </c>
+      <c r="E354" t="n">
+        <v>4760</v>
+      </c>
+      <c r="F354" s="2" t="n">
+        <v>0.966</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>0</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" t="n">
+        <v>0</v>
+      </c>
+      <c r="F355" s="2" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>105</v>
+      </c>
+      <c r="D356" t="n">
+        <v>4116</v>
+      </c>
+      <c r="E356" t="n">
+        <v>4221</v>
+      </c>
+      <c r="F356" s="2" t="n">
+        <v>0.9751000000000001</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>0</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0</v>
+      </c>
+      <c r="E357" t="n">
+        <v>0</v>
+      </c>
+      <c r="F357" s="2" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>76</v>
+      </c>
+      <c r="D358" t="n">
+        <v>850</v>
+      </c>
+      <c r="E358" t="n">
+        <v>926</v>
+      </c>
+      <c r="F358" s="2" t="n">
+        <v>0.9179</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>1</v>
+      </c>
+      <c r="D359" t="n">
+        <v>377</v>
+      </c>
+      <c r="E359" t="n">
+        <v>378</v>
+      </c>
+      <c r="F359" s="2" t="n">
+        <v>0.9974</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>0</v>
+      </c>
+      <c r="D360" t="n">
+        <v>3558</v>
+      </c>
+      <c r="E360" t="n">
+        <v>3558</v>
+      </c>
+      <c r="F360" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>0</v>
+      </c>
+      <c r="D361" t="n">
+        <v>194</v>
+      </c>
+      <c r="E361" t="n">
+        <v>194</v>
+      </c>
+      <c r="F361" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>0</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0</v>
+      </c>
+      <c r="E362" t="n">
+        <v>0</v>
+      </c>
+      <c r="F362" s="2" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>0</v>
+      </c>
+      <c r="D363" t="n">
+        <v>3754</v>
+      </c>
+      <c r="E363" t="n">
+        <v>3754</v>
+      </c>
+      <c r="F363" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>780</v>
+      </c>
+      <c r="D364" t="n">
+        <v>11774</v>
+      </c>
+      <c r="E364" t="n">
+        <v>12554</v>
+      </c>
+      <c r="F364" s="2" t="n">
+        <v>0.9379000000000001</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>0</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0</v>
+      </c>
+      <c r="E365" t="n">
+        <v>0</v>
+      </c>
+      <c r="F365" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F351"/>
+  <autoFilter ref="A1:F365"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$365</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$379</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>807</v>
+        <v>829</v>
       </c>
       <c r="C3" t="n">
-        <v>31591</v>
+        <v>33479</v>
       </c>
       <c r="D3" t="n">
-        <v>32398</v>
+        <v>34308</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9751000000000001</v>
+        <v>0.9758</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2138</v>
+        <v>2491</v>
       </c>
       <c r="C4" t="n">
-        <v>74950</v>
+        <v>78631</v>
       </c>
       <c r="D4" t="n">
-        <v>77088</v>
+        <v>81122</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9693000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2575</v>
+        <v>2652</v>
       </c>
       <c r="C6" t="n">
-        <v>61875</v>
+        <v>64084</v>
       </c>
       <c r="D6" t="n">
-        <v>64450</v>
+        <v>66736</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.96</v>
+        <v>0.9603</v>
       </c>
     </row>
     <row r="7">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2277</v>
+        <v>2627</v>
       </c>
       <c r="C8" t="n">
-        <v>10822</v>
+        <v>11399</v>
       </c>
       <c r="D8" t="n">
-        <v>13099</v>
+        <v>14026</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8262</v>
+        <v>0.8127</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>2504</v>
+        <v>2721</v>
       </c>
       <c r="D9" t="n">
-        <v>2517</v>
+        <v>2735</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9948</v>
+        <v>0.9948999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="C10" t="n">
-        <v>40040</v>
+        <v>43389</v>
       </c>
       <c r="D10" t="n">
-        <v>41536</v>
+        <v>44887</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9640000000000001</v>
+        <v>0.9666</v>
       </c>
     </row>
     <row r="11">
@@ -645,13 +645,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>3722</v>
+        <v>3784</v>
       </c>
       <c r="D11" t="n">
-        <v>3762</v>
+        <v>3824</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9895</v>
       </c>
     </row>
     <row r="12">
@@ -678,16 +678,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C13" t="n">
-        <v>47000</v>
+        <v>48940</v>
       </c>
       <c r="D13" t="n">
-        <v>47235</v>
+        <v>49176</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.995</v>
+        <v>0.9952</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8118</v>
+        <v>8321</v>
       </c>
       <c r="C14" t="n">
-        <v>151910</v>
+        <v>161386</v>
       </c>
       <c r="D14" t="n">
-        <v>160028</v>
+        <v>169707</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9493</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="15">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F365"/>
+  <dimension ref="A1:F379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9209,8 +9209,334 @@
       </c>
       <c r="F365" s="2" t="n"/>
     </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>0</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0</v>
+      </c>
+      <c r="E366" t="n">
+        <v>0</v>
+      </c>
+      <c r="F366" s="2" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>22</v>
+      </c>
+      <c r="D367" t="n">
+        <v>1888</v>
+      </c>
+      <c r="E367" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F367" s="2" t="n">
+        <v>0.9884999999999999</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>353</v>
+      </c>
+      <c r="D368" t="n">
+        <v>3681</v>
+      </c>
+      <c r="E368" t="n">
+        <v>4034</v>
+      </c>
+      <c r="F368" s="2" t="n">
+        <v>0.9125</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>0</v>
+      </c>
+      <c r="D369" t="n">
+        <v>0</v>
+      </c>
+      <c r="E369" t="n">
+        <v>0</v>
+      </c>
+      <c r="F369" s="2" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>77</v>
+      </c>
+      <c r="D370" t="n">
+        <v>2209</v>
+      </c>
+      <c r="E370" t="n">
+        <v>2286</v>
+      </c>
+      <c r="F370" s="2" t="n">
+        <v>0.9662999999999999</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>0</v>
+      </c>
+      <c r="D371" t="n">
+        <v>0</v>
+      </c>
+      <c r="E371" t="n">
+        <v>0</v>
+      </c>
+      <c r="F371" s="2" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>350</v>
+      </c>
+      <c r="D372" t="n">
+        <v>577</v>
+      </c>
+      <c r="E372" t="n">
+        <v>927</v>
+      </c>
+      <c r="F372" s="2" t="n">
+        <v>0.6224000000000001</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>1</v>
+      </c>
+      <c r="D373" t="n">
+        <v>217</v>
+      </c>
+      <c r="E373" t="n">
+        <v>218</v>
+      </c>
+      <c r="F373" s="2" t="n">
+        <v>0.9954000000000001</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>2</v>
+      </c>
+      <c r="D374" t="n">
+        <v>3349</v>
+      </c>
+      <c r="E374" t="n">
+        <v>3351</v>
+      </c>
+      <c r="F374" s="2" t="n">
+        <v>0.9994</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>0</v>
+      </c>
+      <c r="D375" t="n">
+        <v>62</v>
+      </c>
+      <c r="E375" t="n">
+        <v>62</v>
+      </c>
+      <c r="F375" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>0</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0</v>
+      </c>
+      <c r="E376" t="n">
+        <v>0</v>
+      </c>
+      <c r="F376" s="2" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>1</v>
+      </c>
+      <c r="D377" t="n">
+        <v>1940</v>
+      </c>
+      <c r="E377" t="n">
+        <v>1941</v>
+      </c>
+      <c r="F377" s="2" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>203</v>
+      </c>
+      <c r="D378" t="n">
+        <v>9476</v>
+      </c>
+      <c r="E378" t="n">
+        <v>9679</v>
+      </c>
+      <c r="F378" s="2" t="n">
+        <v>0.9790000000000001</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>0</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0</v>
+      </c>
+      <c r="E379" t="n">
+        <v>0</v>
+      </c>
+      <c r="F379" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F365"/>
+  <autoFilter ref="A1:F379"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1783</v>
+        <v>3775</v>
       </c>
       <c r="D3" t="n">
-        <v>1783</v>
+        <v>3777</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>319</v>
       </c>
       <c r="C4" t="n">
-        <v>2775</v>
+        <v>5321</v>
       </c>
       <c r="D4" t="n">
-        <v>2802</v>
+        <v>5640</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9904000000000001</v>
+        <v>0.9434</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C6" t="n">
-        <v>2466</v>
+        <v>4911</v>
       </c>
       <c r="D6" t="n">
-        <v>2501</v>
+        <v>4960</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.986</v>
+        <v>0.9901000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="C8" t="n">
-        <v>2157</v>
+        <v>2947</v>
       </c>
       <c r="D8" t="n">
-        <v>2281</v>
+        <v>3171</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9456</v>
+        <v>0.9294</v>
       </c>
     </row>
     <row r="9">
@@ -605,13 +605,13 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>132</v>
+        <v>447</v>
       </c>
       <c r="D9" t="n">
-        <v>135</v>
+        <v>450</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9778</v>
+        <v>0.9933</v>
       </c>
     </row>
     <row r="10">
@@ -624,13 +624,13 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>2245</v>
+        <v>4919</v>
       </c>
       <c r="D10" t="n">
-        <v>2258</v>
+        <v>4932</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9942</v>
+        <v>0.9974</v>
       </c>
     </row>
     <row r="11">
@@ -643,10 +643,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -676,16 +676,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>1776</v>
+        <v>3705</v>
       </c>
       <c r="D13" t="n">
-        <v>1779</v>
+        <v>3713</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9983</v>
+        <v>0.9978</v>
       </c>
     </row>
     <row r="14">
@@ -695,16 +695,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>121</v>
+        <v>734</v>
       </c>
       <c r="C14" t="n">
-        <v>8775</v>
+        <v>17063</v>
       </c>
       <c r="D14" t="n">
-        <v>8896</v>
+        <v>17797</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9588</v>
       </c>
     </row>
     <row r="15">
@@ -736,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1105,8 +1105,334 @@
       </c>
       <c r="F15" s="2" t="n"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1992</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1994</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0.9990000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>292</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2546</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2838</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0.8970999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>14</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2445</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2459</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0.9943000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>100</v>
+      </c>
+      <c r="D22" t="n">
+        <v>790</v>
+      </c>
+      <c r="E22" t="n">
+        <v>890</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.8876000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>315</v>
+      </c>
+      <c r="E23" t="n">
+        <v>315</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2674</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>55</v>
+      </c>
+      <c r="E25" t="n">
+        <v>55</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1929</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1934</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0.9974</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>613</v>
+      </c>
+      <c r="D28" t="n">
+        <v>8288</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8901</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0.9311</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F15"/>
+  <autoFilter ref="A1:F29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>3775</v>
+        <v>4641</v>
       </c>
       <c r="D3" t="n">
-        <v>3777</v>
+        <v>4664</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9951000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C4" t="n">
-        <v>5321</v>
+        <v>5851</v>
       </c>
       <c r="D4" t="n">
-        <v>5640</v>
+        <v>6176</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9434</v>
+        <v>0.9473999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>4911</v>
+        <v>5372</v>
       </c>
       <c r="D6" t="n">
-        <v>4960</v>
+        <v>5452</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9901000000000001</v>
+        <v>0.9853000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -583,16 +583,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="C8" t="n">
         <v>2947</v>
       </c>
       <c r="D8" t="n">
-        <v>3171</v>
+        <v>3199</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9294</v>
+        <v>0.9212</v>
       </c>
     </row>
     <row r="9">
@@ -605,13 +605,13 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>447</v>
+        <v>538</v>
       </c>
       <c r="D9" t="n">
-        <v>450</v>
+        <v>541</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9933</v>
+        <v>0.9945000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -624,13 +624,13 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>4919</v>
+        <v>5752</v>
       </c>
       <c r="D10" t="n">
-        <v>4932</v>
+        <v>5765</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9974</v>
+        <v>0.9976999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -643,10 +643,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
@@ -679,13 +679,13 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>3705</v>
+        <v>4316</v>
       </c>
       <c r="D13" t="n">
-        <v>3713</v>
+        <v>4324</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9978</v>
+        <v>0.9981</v>
       </c>
     </row>
     <row r="14">
@@ -695,16 +695,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>734</v>
+        <v>815</v>
       </c>
       <c r="C14" t="n">
-        <v>17063</v>
+        <v>20020</v>
       </c>
       <c r="D14" t="n">
-        <v>17797</v>
+        <v>20835</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9588</v>
+        <v>0.9609000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -736,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1431,8 +1431,334 @@
       </c>
       <c r="F29" s="2" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CARAP 02-SP</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CARAP-SP</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>21</v>
+      </c>
+      <c r="D31" t="n">
+        <v>866</v>
+      </c>
+      <c r="E31" t="n">
+        <v>887</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0.9762999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" t="n">
+        <v>530</v>
+      </c>
+      <c r="E32" t="n">
+        <v>536</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.9887999999999999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>COT-SP</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>31</v>
+      </c>
+      <c r="D34" t="n">
+        <v>461</v>
+      </c>
+      <c r="E34" t="n">
+        <v>492</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>28</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>28</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>91</v>
+      </c>
+      <c r="E37" t="n">
+        <v>91</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>833</v>
+      </c>
+      <c r="E38" t="n">
+        <v>833</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>611</v>
+      </c>
+      <c r="E41" t="n">
+        <v>611</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>81</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2957</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3038</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0.9732999999999999</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F29"/>
+  <autoFilter ref="A1:F43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Geral Diário" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -471,261 +471,187 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CARAP 02-SP</t>
+          <t>CHM-SP</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>5851</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n"/>
+        <v>6176</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.9473999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CARAP-SP</t>
+          <t>CLP-SP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>4641</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4664</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.9951000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHM-SP</t>
+          <t>F JND-SP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>5851</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>6176</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.9473999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CLP-SP</t>
+          <t>F S-JRG-SP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2947</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="n"/>
+        <v>3199</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.9212</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COT-SP</t>
+          <t>ITUP-SP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>5372</v>
+        <v>538</v>
       </c>
       <c r="D6" t="n">
-        <v>5452</v>
+        <v>541</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9853000000000001</v>
+        <v>0.9945000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F JND-SP</t>
+          <t>JND 02-SP</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>5752</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2" t="n"/>
+        <v>5765</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.9976999999999999</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F S-JRG-SP</t>
+          <t>JND-SP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2947</v>
+        <v>124</v>
       </c>
       <c r="D8" t="n">
-        <v>3199</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9212</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ITUP-SP</t>
+          <t>OSC 02-SP</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>538</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>541</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.9945000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JND 02-SP</t>
+          <t>OSC-SP</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>5752</v>
+        <v>4316</v>
       </c>
       <c r="D10" t="n">
-        <v>5765</v>
+        <v>4324</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9976999999999999</v>
+        <v>0.9981</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JND-SP</t>
+          <t>S-FREG-SP</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>124</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>OSC 02-SP</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>OSC-SP</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4316</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4324</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0.9981</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>S-CSVD-SP</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>815</v>
-      </c>
-      <c r="C14" t="n">
-        <v>20020</v>
-      </c>
-      <c r="D14" t="n">
-        <v>20835</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0.9609000000000001</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>S-FREG-SP</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E15"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -736,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1757,8 +1683,228 @@
       </c>
       <c r="F43" s="2" t="n"/>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>OSC 02-SP</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>OSC-SP</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F43"/>
+  <autoFilter ref="A1:F53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Geral Diário" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>325</v>
+        <v>727</v>
       </c>
       <c r="C2" t="n">
-        <v>5851</v>
+        <v>13221</v>
       </c>
       <c r="D2" t="n">
-        <v>6176</v>
+        <v>13948</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9473999999999999</v>
+        <v>0.9479000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>252</v>
+        <v>364</v>
       </c>
       <c r="C5" t="n">
-        <v>2947</v>
+        <v>13018</v>
       </c>
       <c r="D5" t="n">
-        <v>3199</v>
+        <v>13382</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9212</v>
+        <v>0.9728</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="C6" t="n">
-        <v>538</v>
+        <v>1310</v>
       </c>
       <c r="D6" t="n">
-        <v>541</v>
+        <v>1393</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9404</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>711</v>
       </c>
       <c r="C7" t="n">
-        <v>5752</v>
+        <v>9645</v>
       </c>
       <c r="D7" t="n">
-        <v>5765</v>
+        <v>10356</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9976999999999999</v>
+        <v>0.9312999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>124</v>
+        <v>209</v>
       </c>
       <c r="D8" t="n">
-        <v>124</v>
+        <v>209</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -600,58 +600,41 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OSC 02-SP</t>
+          <t>S-CSVD-SP</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>2523</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>32599</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="n"/>
+        <v>35122</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.9281999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OSC-SP</t>
+          <t>S-FREG-SP</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>4316</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>4324</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0.9981</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>S-FREG-SP</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -662,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1903,8 +1886,218 @@
       </c>
       <c r="F53" s="2" t="n"/>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>402</v>
+      </c>
+      <c r="D54" t="n">
+        <v>7370</v>
+      </c>
+      <c r="E54" t="n">
+        <v>7772</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>0.9483</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>112</v>
+      </c>
+      <c r="D57" t="n">
+        <v>10071</v>
+      </c>
+      <c r="E57" t="n">
+        <v>10183</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>0.9890000000000001</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>80</v>
+      </c>
+      <c r="D58" t="n">
+        <v>772</v>
+      </c>
+      <c r="E58" t="n">
+        <v>852</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>0.9061</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>698</v>
+      </c>
+      <c r="D59" t="n">
+        <v>3893</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4591</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>0.848</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>85</v>
+      </c>
+      <c r="E60" t="n">
+        <v>85</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1708</v>
+      </c>
+      <c r="D61" t="n">
+        <v>12579</v>
+      </c>
+      <c r="E61" t="n">
+        <v>14287</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>0.8804999999999999</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F53"/>
+  <autoFilter ref="A1:F62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>727</v>
+        <v>1370</v>
       </c>
       <c r="C2" t="n">
-        <v>13221</v>
+        <v>21804</v>
       </c>
       <c r="D2" t="n">
-        <v>13948</v>
+        <v>23174</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9479000000000001</v>
+        <v>0.9409000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>364</v>
+        <v>661</v>
       </c>
       <c r="C5" t="n">
-        <v>13018</v>
+        <v>13377</v>
       </c>
       <c r="D5" t="n">
-        <v>13382</v>
+        <v>14038</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9728</v>
+        <v>0.9529000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -550,13 +550,13 @@
         <v>83</v>
       </c>
       <c r="C6" t="n">
-        <v>1310</v>
+        <v>1645</v>
       </c>
       <c r="D6" t="n">
-        <v>1393</v>
+        <v>1728</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9404</v>
+        <v>0.9520000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>711</v>
+        <v>1109</v>
       </c>
       <c r="C7" t="n">
-        <v>9645</v>
+        <v>12925</v>
       </c>
       <c r="D7" t="n">
-        <v>10356</v>
+        <v>14034</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9312999999999999</v>
+        <v>0.9209999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2523</v>
+        <v>2819</v>
       </c>
       <c r="C9" t="n">
-        <v>32599</v>
+        <v>42579</v>
       </c>
       <c r="D9" t="n">
-        <v>35122</v>
+        <v>45398</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9281999999999999</v>
+        <v>0.9379000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2096,8 +2096,218 @@
       </c>
       <c r="F62" s="2" t="n"/>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>643</v>
+      </c>
+      <c r="D63" t="n">
+        <v>8583</v>
+      </c>
+      <c r="E63" t="n">
+        <v>9226</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>0.9303</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>297</v>
+      </c>
+      <c r="D66" t="n">
+        <v>359</v>
+      </c>
+      <c r="E66" t="n">
+        <v>656</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>0.5473</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>335</v>
+      </c>
+      <c r="E67" t="n">
+        <v>335</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>398</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3280</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3678</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>0.8918</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>78</v>
+      </c>
+      <c r="E69" t="n">
+        <v>78</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>296</v>
+      </c>
+      <c r="D70" t="n">
+        <v>9980</v>
+      </c>
+      <c r="E70" t="n">
+        <v>10276</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0.9712000000000001</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F62"/>
+  <autoFilter ref="A1:F71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1370</v>
+        <v>1427</v>
       </c>
       <c r="C2" t="n">
-        <v>21804</v>
+        <v>27518</v>
       </c>
       <c r="D2" t="n">
-        <v>23174</v>
+        <v>28945</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9409000000000001</v>
+        <v>0.9506999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C5" t="n">
-        <v>13377</v>
+        <v>14344</v>
       </c>
       <c r="D5" t="n">
-        <v>14038</v>
+        <v>15007</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9529000000000001</v>
+        <v>0.9558</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83</v>
+        <v>188</v>
       </c>
       <c r="C6" t="n">
-        <v>1645</v>
+        <v>1958</v>
       </c>
       <c r="D6" t="n">
-        <v>1728</v>
+        <v>2146</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9520000000000001</v>
+        <v>0.9124</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1109</v>
+        <v>1682</v>
       </c>
       <c r="C7" t="n">
-        <v>12925</v>
+        <v>15387</v>
       </c>
       <c r="D7" t="n">
-        <v>14034</v>
+        <v>17069</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9209999999999999</v>
+        <v>0.9015000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>287</v>
+        <v>365</v>
       </c>
       <c r="D8" t="n">
-        <v>287</v>
+        <v>365</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2819</v>
+        <v>3373</v>
       </c>
       <c r="C9" t="n">
-        <v>42579</v>
+        <v>50320</v>
       </c>
       <c r="D9" t="n">
-        <v>45398</v>
+        <v>53693</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9379000000000001</v>
+        <v>0.9372</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2306,8 +2306,218 @@
       </c>
       <c r="F71" s="2" t="n"/>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>57</v>
+      </c>
+      <c r="D72" t="n">
+        <v>5714</v>
+      </c>
+      <c r="E72" t="n">
+        <v>5771</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>0.9901000000000001</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="n">
+        <v>967</v>
+      </c>
+      <c r="E75" t="n">
+        <v>969</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>0.9979</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>105</v>
+      </c>
+      <c r="D76" t="n">
+        <v>313</v>
+      </c>
+      <c r="E76" t="n">
+        <v>418</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>0.7487999999999999</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>573</v>
+      </c>
+      <c r="D77" t="n">
+        <v>2462</v>
+      </c>
+      <c r="E77" t="n">
+        <v>3035</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>0.8112</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>78</v>
+      </c>
+      <c r="E78" t="n">
+        <v>78</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>554</v>
+      </c>
+      <c r="D79" t="n">
+        <v>7741</v>
+      </c>
+      <c r="E79" t="n">
+        <v>8295</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>0.9331999999999999</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F71"/>
+  <autoFilter ref="A1:F80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1427</v>
+        <v>1489</v>
       </c>
       <c r="C2" t="n">
-        <v>27518</v>
+        <v>30281</v>
       </c>
       <c r="D2" t="n">
-        <v>28945</v>
+        <v>31770</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9506999999999999</v>
+        <v>0.9531000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>663</v>
+        <v>809</v>
       </c>
       <c r="C5" t="n">
-        <v>14344</v>
+        <v>15245</v>
       </c>
       <c r="D5" t="n">
-        <v>15007</v>
+        <v>16054</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9558</v>
+        <v>0.9495999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -550,13 +550,13 @@
         <v>188</v>
       </c>
       <c r="C6" t="n">
-        <v>1958</v>
+        <v>2442</v>
       </c>
       <c r="D6" t="n">
-        <v>2146</v>
+        <v>2630</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9124</v>
+        <v>0.9285</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1682</v>
+        <v>1750</v>
       </c>
       <c r="C7" t="n">
-        <v>15387</v>
+        <v>18477</v>
       </c>
       <c r="D7" t="n">
-        <v>17069</v>
+        <v>20227</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9015000000000001</v>
+        <v>0.9135</v>
       </c>
     </row>
     <row r="8">
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>365</v>
+        <v>517</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>517</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3373</v>
+        <v>4333</v>
       </c>
       <c r="C9" t="n">
-        <v>50320</v>
+        <v>57485</v>
       </c>
       <c r="D9" t="n">
-        <v>53693</v>
+        <v>61818</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9372</v>
+        <v>0.9298999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2516,8 +2516,218 @@
       </c>
       <c r="F80" s="2" t="n"/>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>62</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2763</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2825</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>0.9781</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>146</v>
+      </c>
+      <c r="D84" t="n">
+        <v>901</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1047</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>0.8606</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>484</v>
+      </c>
+      <c r="E85" t="n">
+        <v>484</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>68</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3090</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3158</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>0.9784999999999999</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>152</v>
+      </c>
+      <c r="E87" t="n">
+        <v>152</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>960</v>
+      </c>
+      <c r="D88" t="n">
+        <v>7165</v>
+      </c>
+      <c r="E88" t="n">
+        <v>8125</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0.8818</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F80"/>
+  <autoFilter ref="A1:F89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,13 +478,13 @@
         <v>1489</v>
       </c>
       <c r="C2" t="n">
-        <v>30281</v>
+        <v>30981</v>
       </c>
       <c r="D2" t="n">
-        <v>31770</v>
+        <v>32470</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9531000000000001</v>
+        <v>0.9540999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>809</v>
+        <v>836</v>
       </c>
       <c r="C5" t="n">
-        <v>15245</v>
+        <v>15255</v>
       </c>
       <c r="D5" t="n">
-        <v>16054</v>
+        <v>16091</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9495999999999999</v>
+        <v>0.948</v>
       </c>
     </row>
     <row r="6">
@@ -550,13 +550,13 @@
         <v>188</v>
       </c>
       <c r="C6" t="n">
-        <v>2442</v>
+        <v>2524</v>
       </c>
       <c r="D6" t="n">
-        <v>2630</v>
+        <v>2712</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9285</v>
+        <v>0.9307</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1750</v>
+        <v>2067</v>
       </c>
       <c r="C7" t="n">
-        <v>18477</v>
+        <v>19187</v>
       </c>
       <c r="D7" t="n">
-        <v>20227</v>
+        <v>21254</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9135</v>
+        <v>0.9026999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>517</v>
+        <v>657</v>
       </c>
       <c r="D8" t="n">
-        <v>517</v>
+        <v>657</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4333</v>
+        <v>4447</v>
       </c>
       <c r="C9" t="n">
-        <v>57485</v>
+        <v>60073</v>
       </c>
       <c r="D9" t="n">
-        <v>61818</v>
+        <v>64520</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.9311</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2726,8 +2726,218 @@
       </c>
       <c r="F89" s="2" t="n"/>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>700</v>
+      </c>
+      <c r="E90" t="n">
+        <v>700</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>27</v>
+      </c>
+      <c r="D93" t="n">
+        <v>10</v>
+      </c>
+      <c r="E93" t="n">
+        <v>37</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>0.2703</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>82</v>
+      </c>
+      <c r="E94" t="n">
+        <v>82</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>317</v>
+      </c>
+      <c r="D95" t="n">
+        <v>710</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1027</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>0.6912999999999999</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>140</v>
+      </c>
+      <c r="E96" t="n">
+        <v>140</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>114</v>
+      </c>
+      <c r="D97" t="n">
+        <v>2588</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2702</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>0.9578</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F89"/>
+  <autoFilter ref="A1:F98"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2936,8 +2936,206 @@
       </c>
       <c r="F98" s="2" t="n"/>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F98"/>
+  <autoFilter ref="A1:F107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$116</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1489</v>
+        <v>1634</v>
       </c>
       <c r="C2" t="n">
         <v>30981</v>
       </c>
       <c r="D2" t="n">
-        <v>32470</v>
+        <v>32615</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9499</v>
       </c>
     </row>
     <row r="3">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="C5" t="n">
         <v>15255</v>
       </c>
       <c r="D5" t="n">
-        <v>16091</v>
+        <v>16094</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.948</v>
+        <v>0.9479000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>188</v>
+        <v>280</v>
       </c>
       <c r="C6" t="n">
         <v>2524</v>
       </c>
       <c r="D6" t="n">
-        <v>2712</v>
+        <v>2804</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9307</v>
+        <v>0.9001</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2067</v>
+        <v>2306</v>
       </c>
       <c r="C7" t="n">
         <v>19187</v>
       </c>
       <c r="D7" t="n">
-        <v>21254</v>
+        <v>21493</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.8926999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
         <v>657</v>
       </c>
       <c r="D8" t="n">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>0.9834999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4447</v>
+        <v>4762</v>
       </c>
       <c r="C9" t="n">
-        <v>60073</v>
+        <v>61158</v>
       </c>
       <c r="D9" t="n">
-        <v>64520</v>
+        <v>65920</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9311</v>
+        <v>0.9278</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3134,8 +3134,218 @@
       </c>
       <c r="F107" s="2" t="n"/>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>145</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>145</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>3</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>3</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>92</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>92</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>239</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>239</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>11</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>11</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>315</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1085</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>0.775</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F107"/>
+  <autoFilter ref="A1:F116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1634</v>
+        <v>2286</v>
       </c>
       <c r="C2" t="n">
-        <v>30981</v>
+        <v>39440</v>
       </c>
       <c r="D2" t="n">
-        <v>32615</v>
+        <v>41726</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9499</v>
+        <v>0.9451999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>839</v>
+        <v>1450</v>
       </c>
       <c r="C5" t="n">
-        <v>15255</v>
+        <v>16407</v>
       </c>
       <c r="D5" t="n">
-        <v>16094</v>
+        <v>17857</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9479000000000001</v>
+        <v>0.9188</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>280</v>
+        <v>422</v>
       </c>
       <c r="C6" t="n">
-        <v>2524</v>
+        <v>3394</v>
       </c>
       <c r="D6" t="n">
-        <v>2804</v>
+        <v>3816</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9001</v>
+        <v>0.8894</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2306</v>
+        <v>3392</v>
       </c>
       <c r="C7" t="n">
-        <v>19187</v>
+        <v>24787</v>
       </c>
       <c r="D7" t="n">
-        <v>21493</v>
+        <v>28179</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8926999999999999</v>
+        <v>0.8795999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>657</v>
+        <v>1015</v>
       </c>
       <c r="D8" t="n">
-        <v>668</v>
+        <v>1027</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9834999999999999</v>
+        <v>0.9883</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4762</v>
+        <v>8414</v>
       </c>
       <c r="C9" t="n">
-        <v>61158</v>
+        <v>78375</v>
       </c>
       <c r="D9" t="n">
-        <v>65920</v>
+        <v>86789</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9278</v>
+        <v>0.9031</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3344,8 +3344,218 @@
       </c>
       <c r="F116" s="2" t="n"/>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>652</v>
+      </c>
+      <c r="D117" t="n">
+        <v>8459</v>
+      </c>
+      <c r="E117" t="n">
+        <v>9111</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>0.9284</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>611</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1152</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1763</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>0.6534</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>142</v>
+      </c>
+      <c r="D121" t="n">
+        <v>870</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1012</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>0.8597</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1086</v>
+      </c>
+      <c r="D122" t="n">
+        <v>5600</v>
+      </c>
+      <c r="E122" t="n">
+        <v>6686</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>0.8376</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="n">
+        <v>358</v>
+      </c>
+      <c r="E123" t="n">
+        <v>359</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>0.9972</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>3652</v>
+      </c>
+      <c r="D124" t="n">
+        <v>17217</v>
+      </c>
+      <c r="E124" t="n">
+        <v>20869</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>0.825</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F116"/>
+  <autoFilter ref="A1:F125"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2286</v>
+        <v>3083</v>
       </c>
       <c r="C2" t="n">
-        <v>39440</v>
+        <v>46516</v>
       </c>
       <c r="D2" t="n">
-        <v>41726</v>
+        <v>49599</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9451999999999999</v>
+        <v>0.9378</v>
       </c>
     </row>
     <row r="3">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1450</v>
+        <v>1566</v>
       </c>
       <c r="C5" t="n">
-        <v>16407</v>
+        <v>17192</v>
       </c>
       <c r="D5" t="n">
-        <v>17857</v>
+        <v>18758</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9188</v>
+        <v>0.9165000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -550,13 +550,13 @@
         <v>422</v>
       </c>
       <c r="C6" t="n">
-        <v>3394</v>
+        <v>4387</v>
       </c>
       <c r="D6" t="n">
-        <v>3816</v>
+        <v>4809</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8894</v>
+        <v>0.9122</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3392</v>
+        <v>4304</v>
       </c>
       <c r="C7" t="n">
-        <v>24787</v>
+        <v>28537</v>
       </c>
       <c r="D7" t="n">
-        <v>28179</v>
+        <v>32841</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8795999999999999</v>
+        <v>0.8689</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1015</v>
+        <v>1290</v>
       </c>
       <c r="D8" t="n">
-        <v>1027</v>
+        <v>1302</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9883</v>
+        <v>0.9908</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8414</v>
+        <v>9672</v>
       </c>
       <c r="C9" t="n">
-        <v>78375</v>
+        <v>89271</v>
       </c>
       <c r="D9" t="n">
-        <v>86789</v>
+        <v>98943</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9031</v>
+        <v>0.9022</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3554,8 +3554,218 @@
       </c>
       <c r="F125" s="2" t="n"/>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>797</v>
+      </c>
+      <c r="D126" t="n">
+        <v>7076</v>
+      </c>
+      <c r="E126" t="n">
+        <v>7873</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>0.8987999999999999</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>116</v>
+      </c>
+      <c r="D129" t="n">
+        <v>785</v>
+      </c>
+      <c r="E129" t="n">
+        <v>901</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>0.8713</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>993</v>
+      </c>
+      <c r="E130" t="n">
+        <v>993</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>912</v>
+      </c>
+      <c r="D131" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E131" t="n">
+        <v>4662</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>0.8044</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="n">
+        <v>275</v>
+      </c>
+      <c r="E132" t="n">
+        <v>275</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1258</v>
+      </c>
+      <c r="D133" t="n">
+        <v>10896</v>
+      </c>
+      <c r="E133" t="n">
+        <v>12154</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>0.8965000000000001</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F125"/>
+  <autoFilter ref="A1:F134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$143</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3083</v>
+        <v>3490</v>
       </c>
       <c r="C2" t="n">
-        <v>46516</v>
+        <v>50333</v>
       </c>
       <c r="D2" t="n">
-        <v>49599</v>
+        <v>53823</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9378</v>
+        <v>0.9351999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1566</v>
+        <v>1638</v>
       </c>
       <c r="C5" t="n">
-        <v>17192</v>
+        <v>17813</v>
       </c>
       <c r="D5" t="n">
-        <v>18758</v>
+        <v>19451</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9165000000000001</v>
+        <v>0.9157999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C6" t="n">
-        <v>4387</v>
+        <v>4944</v>
       </c>
       <c r="D6" t="n">
-        <v>4809</v>
+        <v>5367</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9122</v>
+        <v>0.9212</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4304</v>
+        <v>4306</v>
       </c>
       <c r="C7" t="n">
-        <v>28537</v>
+        <v>31677</v>
       </c>
       <c r="D7" t="n">
-        <v>32841</v>
+        <v>35983</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8689</v>
+        <v>0.8803</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1290</v>
+        <v>1419</v>
       </c>
       <c r="D8" t="n">
-        <v>1302</v>
+        <v>1431</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9908</v>
+        <v>0.9915999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9672</v>
+        <v>10070</v>
       </c>
       <c r="C9" t="n">
-        <v>89271</v>
+        <v>96369</v>
       </c>
       <c r="D9" t="n">
-        <v>98943</v>
+        <v>106439</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9022</v>
+        <v>0.9054000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3764,8 +3764,218 @@
       </c>
       <c r="F134" s="2" t="n"/>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>407</v>
+      </c>
+      <c r="D135" t="n">
+        <v>3817</v>
+      </c>
+      <c r="E135" t="n">
+        <v>4224</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>0.9036</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>72</v>
+      </c>
+      <c r="D138" t="n">
+        <v>621</v>
+      </c>
+      <c r="E138" t="n">
+        <v>693</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>0.8961</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>557</v>
+      </c>
+      <c r="E139" t="n">
+        <v>558</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>0.9982</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3140</v>
+      </c>
+      <c r="E140" t="n">
+        <v>3142</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>0.9994</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>129</v>
+      </c>
+      <c r="E141" t="n">
+        <v>129</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>398</v>
+      </c>
+      <c r="D142" t="n">
+        <v>7098</v>
+      </c>
+      <c r="E142" t="n">
+        <v>7496</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>0.9469</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F134"/>
+  <autoFilter ref="A1:F143"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3490</v>
+        <v>3588</v>
       </c>
       <c r="C2" t="n">
-        <v>50333</v>
+        <v>53918</v>
       </c>
       <c r="D2" t="n">
-        <v>53823</v>
+        <v>57506</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9351999999999999</v>
+        <v>0.9376000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1638</v>
+        <v>1676</v>
       </c>
       <c r="C5" t="n">
-        <v>17813</v>
+        <v>17941</v>
       </c>
       <c r="D5" t="n">
-        <v>19451</v>
+        <v>19617</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.9146</v>
       </c>
     </row>
     <row r="6">
@@ -550,13 +550,13 @@
         <v>423</v>
       </c>
       <c r="C6" t="n">
-        <v>4944</v>
+        <v>5379</v>
       </c>
       <c r="D6" t="n">
-        <v>5367</v>
+        <v>5802</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9212</v>
+        <v>0.9270999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4306</v>
+        <v>4313</v>
       </c>
       <c r="C7" t="n">
-        <v>31677</v>
+        <v>34176</v>
       </c>
       <c r="D7" t="n">
-        <v>35983</v>
+        <v>38489</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8803</v>
+        <v>0.8879</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1419</v>
+        <v>1526</v>
       </c>
       <c r="D8" t="n">
-        <v>1431</v>
+        <v>1538</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9915999999999999</v>
+        <v>0.9922</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10070</v>
+        <v>10421</v>
       </c>
       <c r="C9" t="n">
-        <v>96369</v>
+        <v>103152</v>
       </c>
       <c r="D9" t="n">
-        <v>106439</v>
+        <v>113573</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9054000000000001</v>
+        <v>0.9081999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3974,8 +3974,218 @@
       </c>
       <c r="F143" s="2" t="n"/>
     </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>98</v>
+      </c>
+      <c r="D144" t="n">
+        <v>3585</v>
+      </c>
+      <c r="E144" t="n">
+        <v>3683</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>0.9734</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>38</v>
+      </c>
+      <c r="D147" t="n">
+        <v>128</v>
+      </c>
+      <c r="E147" t="n">
+        <v>166</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>0.7711</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>435</v>
+      </c>
+      <c r="E148" t="n">
+        <v>435</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>7</v>
+      </c>
+      <c r="D149" t="n">
+        <v>2499</v>
+      </c>
+      <c r="E149" t="n">
+        <v>2506</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>0.9972</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>107</v>
+      </c>
+      <c r="E150" t="n">
+        <v>107</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>351</v>
+      </c>
+      <c r="D151" t="n">
+        <v>6783</v>
+      </c>
+      <c r="E151" t="n">
+        <v>7134</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>0.9508</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F143"/>
+  <autoFilter ref="A1:F152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$161</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3588</v>
+        <v>3600</v>
       </c>
       <c r="C2" t="n">
-        <v>53918</v>
+        <v>54272</v>
       </c>
       <c r="D2" t="n">
-        <v>57506</v>
+        <v>57872</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9376000000000001</v>
+        <v>0.9378</v>
       </c>
     </row>
     <row r="3">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1676</v>
+        <v>1689</v>
       </c>
       <c r="C5" t="n">
-        <v>17941</v>
+        <v>17946</v>
       </c>
       <c r="D5" t="n">
-        <v>19617</v>
+        <v>19635</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9146</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="6">
@@ -550,13 +550,13 @@
         <v>423</v>
       </c>
       <c r="C6" t="n">
-        <v>5379</v>
+        <v>5416</v>
       </c>
       <c r="D6" t="n">
-        <v>5802</v>
+        <v>5839</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9270999999999999</v>
+        <v>0.9276000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4313</v>
+        <v>4418</v>
       </c>
       <c r="C7" t="n">
-        <v>34176</v>
+        <v>34532</v>
       </c>
       <c r="D7" t="n">
-        <v>38489</v>
+        <v>38950</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8879</v>
+        <v>0.8865999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1526</v>
+        <v>1595</v>
       </c>
       <c r="D8" t="n">
-        <v>1538</v>
+        <v>1607</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9922</v>
+        <v>0.9925</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10421</v>
+        <v>10944</v>
       </c>
       <c r="C9" t="n">
-        <v>103152</v>
+        <v>105320</v>
       </c>
       <c r="D9" t="n">
-        <v>113573</v>
+        <v>116264</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9081999999999999</v>
+        <v>0.9059</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4184,8 +4184,218 @@
       </c>
       <c r="F152" s="2" t="n"/>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>12</v>
+      </c>
+      <c r="D153" t="n">
+        <v>354</v>
+      </c>
+      <c r="E153" t="n">
+        <v>366</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>0.9671999999999999</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>13</v>
+      </c>
+      <c r="D156" t="n">
+        <v>5</v>
+      </c>
+      <c r="E156" t="n">
+        <v>18</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>0.2778</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>37</v>
+      </c>
+      <c r="E157" t="n">
+        <v>37</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>105</v>
+      </c>
+      <c r="D158" t="n">
+        <v>356</v>
+      </c>
+      <c r="E158" t="n">
+        <v>461</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>0.7722</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>69</v>
+      </c>
+      <c r="E159" t="n">
+        <v>69</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>523</v>
+      </c>
+      <c r="D160" t="n">
+        <v>2168</v>
+      </c>
+      <c r="E160" t="n">
+        <v>2691</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>0.8056</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F152"/>
+  <autoFilter ref="A1:F161"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F161"/>
+  <dimension ref="A1:F170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4394,8 +4394,206 @@
       </c>
       <c r="F161" s="2" t="n"/>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F161"/>
+  <autoFilter ref="A1:F170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3600</v>
+        <v>3678</v>
       </c>
       <c r="C2" t="n">
-        <v>54272</v>
+        <v>59525</v>
       </c>
       <c r="D2" t="n">
-        <v>57872</v>
+        <v>63203</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9378</v>
+        <v>0.9418000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1689</v>
+        <v>1692</v>
       </c>
       <c r="C5" t="n">
-        <v>17946</v>
+        <v>18207</v>
       </c>
       <c r="D5" t="n">
-        <v>19635</v>
+        <v>19899</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.914</v>
+        <v>0.915</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>423</v>
+        <v>1052</v>
       </c>
       <c r="C6" t="n">
-        <v>5416</v>
+        <v>5752</v>
       </c>
       <c r="D6" t="n">
-        <v>5839</v>
+        <v>6804</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9276000000000001</v>
+        <v>0.8454</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4418</v>
+        <v>4577</v>
       </c>
       <c r="C7" t="n">
-        <v>34532</v>
+        <v>41046</v>
       </c>
       <c r="D7" t="n">
-        <v>38950</v>
+        <v>45623</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8865999999999999</v>
+        <v>0.8996999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1595</v>
+        <v>1726</v>
       </c>
       <c r="D8" t="n">
-        <v>1607</v>
+        <v>1738</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9925</v>
+        <v>0.9931</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10944</v>
+        <v>12957</v>
       </c>
       <c r="C9" t="n">
-        <v>105320</v>
+        <v>115515</v>
       </c>
       <c r="D9" t="n">
-        <v>116264</v>
+        <v>128472</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9059</v>
+        <v>0.8991</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F170"/>
+  <dimension ref="A1:F179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4592,8 +4592,218 @@
       </c>
       <c r="F170" s="2" t="n"/>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>78</v>
+      </c>
+      <c r="D171" t="n">
+        <v>5253</v>
+      </c>
+      <c r="E171" t="n">
+        <v>5331</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>0.9854000000000001</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>3</v>
+      </c>
+      <c r="D174" t="n">
+        <v>261</v>
+      </c>
+      <c r="E174" t="n">
+        <v>264</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>0.9886</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>629</v>
+      </c>
+      <c r="D175" t="n">
+        <v>336</v>
+      </c>
+      <c r="E175" t="n">
+        <v>965</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>0.3482</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>159</v>
+      </c>
+      <c r="D176" t="n">
+        <v>6514</v>
+      </c>
+      <c r="E176" t="n">
+        <v>6673</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>0.9762000000000001</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>131</v>
+      </c>
+      <c r="E177" t="n">
+        <v>131</v>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D178" t="n">
+        <v>10195</v>
+      </c>
+      <c r="E178" t="n">
+        <v>12208</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>0.8351000000000001</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F170"/>
+  <autoFilter ref="A1:F179"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$188</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3678</v>
+        <v>3722</v>
       </c>
       <c r="C2" t="n">
-        <v>59525</v>
+        <v>62352</v>
       </c>
       <c r="D2" t="n">
-        <v>63203</v>
+        <v>66074</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9418000000000001</v>
+        <v>0.9437000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1692</v>
+        <v>1705</v>
       </c>
       <c r="C5" t="n">
-        <v>18207</v>
+        <v>18260</v>
       </c>
       <c r="D5" t="n">
-        <v>19899</v>
+        <v>19965</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.915</v>
+        <v>0.9146</v>
       </c>
     </row>
     <row r="6">
@@ -550,13 +550,13 @@
         <v>1052</v>
       </c>
       <c r="C6" t="n">
-        <v>5752</v>
+        <v>6580</v>
       </c>
       <c r="D6" t="n">
-        <v>6804</v>
+        <v>7632</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8454</v>
+        <v>0.8622</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>4577</v>
       </c>
       <c r="C7" t="n">
-        <v>41046</v>
+        <v>44799</v>
       </c>
       <c r="D7" t="n">
-        <v>45623</v>
+        <v>49376</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8996999999999999</v>
+        <v>0.9073</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1726</v>
+        <v>1950</v>
       </c>
       <c r="D8" t="n">
-        <v>1738</v>
+        <v>1962</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9931</v>
+        <v>0.9939</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12957</v>
+        <v>13967</v>
       </c>
       <c r="C9" t="n">
-        <v>115515</v>
+        <v>123389</v>
       </c>
       <c r="D9" t="n">
-        <v>128472</v>
+        <v>137356</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8991</v>
+        <v>0.8983</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F179"/>
+  <dimension ref="A1:F188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4802,8 +4802,218 @@
       </c>
       <c r="F179" s="2" t="n"/>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>44</v>
+      </c>
+      <c r="D180" t="n">
+        <v>2827</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2871</v>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>0.9847</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>13</v>
+      </c>
+      <c r="D183" t="n">
+        <v>53</v>
+      </c>
+      <c r="E183" t="n">
+        <v>66</v>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>0.8029999999999999</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>828</v>
+      </c>
+      <c r="E184" t="n">
+        <v>828</v>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" t="n">
+        <v>3753</v>
+      </c>
+      <c r="E185" t="n">
+        <v>3753</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" t="n">
+        <v>224</v>
+      </c>
+      <c r="E186" t="n">
+        <v>224</v>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D187" t="n">
+        <v>7874</v>
+      </c>
+      <c r="E187" t="n">
+        <v>8884</v>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>0.8863</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F179"/>
+  <autoFilter ref="A1:F188"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3722</v>
+        <v>3752</v>
       </c>
       <c r="C2" t="n">
-        <v>62352</v>
+        <v>65386</v>
       </c>
       <c r="D2" t="n">
-        <v>66074</v>
+        <v>69138</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9437000000000001</v>
+        <v>0.9457</v>
       </c>
     </row>
     <row r="3">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1705</v>
+        <v>1779</v>
       </c>
       <c r="C5" t="n">
         <v>18260</v>
       </c>
       <c r="D5" t="n">
-        <v>19965</v>
+        <v>20039</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9146</v>
+        <v>0.9112</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="C6" t="n">
-        <v>6580</v>
+        <v>7445</v>
       </c>
       <c r="D6" t="n">
-        <v>7632</v>
+        <v>8502</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8622</v>
+        <v>0.8756999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4577</v>
+        <v>4582</v>
       </c>
       <c r="C7" t="n">
-        <v>44799</v>
+        <v>47633</v>
       </c>
       <c r="D7" t="n">
-        <v>49376</v>
+        <v>52215</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9073</v>
+        <v>0.9122</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1950</v>
+        <v>2008</v>
       </c>
       <c r="D8" t="n">
-        <v>1962</v>
+        <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9939</v>
+        <v>0.9941</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13967</v>
+        <v>14493</v>
       </c>
       <c r="C9" t="n">
-        <v>123389</v>
+        <v>130507</v>
       </c>
       <c r="D9" t="n">
-        <v>137356</v>
+        <v>145000</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8983</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F188"/>
+  <dimension ref="A1:F197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5012,8 +5012,218 @@
       </c>
       <c r="F188" s="2" t="n"/>
     </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>30</v>
+      </c>
+      <c r="D189" t="n">
+        <v>3034</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3064</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>0.9902</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>74</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="n">
+        <v>74</v>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>5</v>
+      </c>
+      <c r="D193" t="n">
+        <v>865</v>
+      </c>
+      <c r="E193" t="n">
+        <v>870</v>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>0.9943000000000001</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>5</v>
+      </c>
+      <c r="D194" t="n">
+        <v>2834</v>
+      </c>
+      <c r="E194" t="n">
+        <v>2839</v>
+      </c>
+      <c r="F194" s="2" t="n">
+        <v>0.9982</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" t="n">
+        <v>58</v>
+      </c>
+      <c r="E195" t="n">
+        <v>58</v>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>526</v>
+      </c>
+      <c r="D196" t="n">
+        <v>7118</v>
+      </c>
+      <c r="E196" t="n">
+        <v>7644</v>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v>0.9312</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F188"/>
+  <autoFilter ref="A1:F197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$206</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3752</v>
+        <v>3815</v>
       </c>
       <c r="C2" t="n">
-        <v>65386</v>
+        <v>68671</v>
       </c>
       <c r="D2" t="n">
-        <v>69138</v>
+        <v>72486</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9457</v>
+        <v>0.9473999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1057</v>
+        <v>1157</v>
       </c>
       <c r="C6" t="n">
-        <v>7445</v>
+        <v>8029</v>
       </c>
       <c r="D6" t="n">
-        <v>8502</v>
+        <v>9186</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8756999999999999</v>
+        <v>0.8740000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>4582</v>
       </c>
       <c r="C7" t="n">
-        <v>47633</v>
+        <v>51111</v>
       </c>
       <c r="D7" t="n">
-        <v>52215</v>
+        <v>55693</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9122</v>
+        <v>0.9177</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2008</v>
+        <v>2095</v>
       </c>
       <c r="D8" t="n">
-        <v>2020</v>
+        <v>2107</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9941</v>
+        <v>0.9943000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14493</v>
+        <v>15469</v>
       </c>
       <c r="C9" t="n">
-        <v>130507</v>
+        <v>136702</v>
       </c>
       <c r="D9" t="n">
-        <v>145000</v>
+        <v>152171</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8983</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F197"/>
+  <dimension ref="A1:F206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5222,8 +5222,216 @@
       </c>
       <c r="F197" s="2" t="n"/>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>63</v>
+      </c>
+      <c r="D198" t="n">
+        <v>3285</v>
+      </c>
+      <c r="E198" t="n">
+        <v>3348</v>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v>0.9812000000000001</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" s="2" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>100</v>
+      </c>
+      <c r="D202" t="n">
+        <v>584</v>
+      </c>
+      <c r="E202" t="n">
+        <v>684</v>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>0.8538</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" t="n">
+        <v>3478</v>
+      </c>
+      <c r="E203" t="n">
+        <v>3478</v>
+      </c>
+      <c r="F203" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" t="n">
+        <v>87</v>
+      </c>
+      <c r="E204" t="n">
+        <v>87</v>
+      </c>
+      <c r="F204" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>976</v>
+      </c>
+      <c r="D205" t="n">
+        <v>6195</v>
+      </c>
+      <c r="E205" t="n">
+        <v>7171</v>
+      </c>
+      <c r="F205" s="2" t="n">
+        <v>0.8639</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F197"/>
+  <autoFilter ref="A1:F206"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$215</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3815</v>
+        <v>3874</v>
       </c>
       <c r="C2" t="n">
-        <v>68671</v>
+        <v>71151</v>
       </c>
       <c r="D2" t="n">
-        <v>72486</v>
+        <v>75025</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9473999999999999</v>
+        <v>0.9484</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>1157</v>
       </c>
       <c r="C6" t="n">
-        <v>8029</v>
+        <v>8539</v>
       </c>
       <c r="D6" t="n">
-        <v>9186</v>
+        <v>9696</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8740000000000001</v>
+        <v>0.8806999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>4582</v>
       </c>
       <c r="C7" t="n">
-        <v>51111</v>
+        <v>54867</v>
       </c>
       <c r="D7" t="n">
-        <v>55693</v>
+        <v>59449</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9177</v>
+        <v>0.9229000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2095</v>
+        <v>2175</v>
       </c>
       <c r="D8" t="n">
-        <v>2107</v>
+        <v>2187</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9943000000000001</v>
+        <v>0.9945000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15469</v>
+        <v>15686</v>
       </c>
       <c r="C9" t="n">
-        <v>136702</v>
+        <v>143001</v>
       </c>
       <c r="D9" t="n">
-        <v>152171</v>
+        <v>158687</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8983</v>
+        <v>0.9012</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F206"/>
+  <dimension ref="A1:F215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5430,8 +5430,216 @@
       </c>
       <c r="F206" s="2" t="n"/>
     </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>59</v>
+      </c>
+      <c r="D207" t="n">
+        <v>2480</v>
+      </c>
+      <c r="E207" t="n">
+        <v>2539</v>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>0.9768000000000001</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" s="2" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>0</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" s="2" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>0</v>
+      </c>
+      <c r="D211" t="n">
+        <v>510</v>
+      </c>
+      <c r="E211" t="n">
+        <v>510</v>
+      </c>
+      <c r="F211" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" t="n">
+        <v>3756</v>
+      </c>
+      <c r="E212" t="n">
+        <v>3756</v>
+      </c>
+      <c r="F212" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>0</v>
+      </c>
+      <c r="D213" t="n">
+        <v>80</v>
+      </c>
+      <c r="E213" t="n">
+        <v>80</v>
+      </c>
+      <c r="F213" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>217</v>
+      </c>
+      <c r="D214" t="n">
+        <v>6299</v>
+      </c>
+      <c r="E214" t="n">
+        <v>6516</v>
+      </c>
+      <c r="F214" s="2" t="n">
+        <v>0.9667</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F206"/>
+  <autoFilter ref="A1:F215"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$215</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$224</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,13 +478,13 @@
         <v>3874</v>
       </c>
       <c r="C2" t="n">
-        <v>71151</v>
+        <v>71847</v>
       </c>
       <c r="D2" t="n">
-        <v>75025</v>
+        <v>75721</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9484</v>
+        <v>0.9488</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>1157</v>
       </c>
       <c r="C6" t="n">
-        <v>8539</v>
+        <v>8761</v>
       </c>
       <c r="D6" t="n">
-        <v>9696</v>
+        <v>9918</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8806999999999999</v>
+        <v>0.8833</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>4582</v>
       </c>
       <c r="C7" t="n">
-        <v>54867</v>
+        <v>55256</v>
       </c>
       <c r="D7" t="n">
-        <v>59449</v>
+        <v>59838</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.9234</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2175</v>
+        <v>2205</v>
       </c>
       <c r="D8" t="n">
-        <v>2187</v>
+        <v>2217</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9945999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15686</v>
+        <v>16443</v>
       </c>
       <c r="C9" t="n">
-        <v>143001</v>
+        <v>144868</v>
       </c>
       <c r="D9" t="n">
-        <v>158687</v>
+        <v>161311</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9012</v>
+        <v>0.8981</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F215"/>
+  <dimension ref="A1:F224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5638,8 +5638,216 @@
       </c>
       <c r="F215" s="2" t="n"/>
     </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>0</v>
+      </c>
+      <c r="D216" t="n">
+        <v>696</v>
+      </c>
+      <c r="E216" t="n">
+        <v>696</v>
+      </c>
+      <c r="F216" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" s="2" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>0</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" s="2" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>0</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" s="2" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>0</v>
+      </c>
+      <c r="D220" t="n">
+        <v>222</v>
+      </c>
+      <c r="E220" t="n">
+        <v>222</v>
+      </c>
+      <c r="F220" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>0</v>
+      </c>
+      <c r="D221" t="n">
+        <v>389</v>
+      </c>
+      <c r="E221" t="n">
+        <v>389</v>
+      </c>
+      <c r="F221" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" t="n">
+        <v>30</v>
+      </c>
+      <c r="E222" t="n">
+        <v>30</v>
+      </c>
+      <c r="F222" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>757</v>
+      </c>
+      <c r="D223" t="n">
+        <v>1867</v>
+      </c>
+      <c r="E223" t="n">
+        <v>2624</v>
+      </c>
+      <c r="F223" s="2" t="n">
+        <v>0.7115</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>0</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F215"/>
+  <autoFilter ref="A1:F224"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$224</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$233</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F224"/>
+  <dimension ref="A1:F233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5846,8 +5846,206 @@
       </c>
       <c r="F224" s="2" t="n"/>
     </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>0</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" s="2" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" s="2" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>0</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
+      <c r="F227" s="2" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>0</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
+      <c r="F228" s="2" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>0</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" s="2" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>0</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" s="2" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>0</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" s="2" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>0</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" s="2" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>0</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F224"/>
+  <autoFilter ref="A1:F233"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$233</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$242</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3874</v>
+        <v>3949</v>
       </c>
       <c r="C2" t="n">
-        <v>71847</v>
+        <v>76449</v>
       </c>
       <c r="D2" t="n">
-        <v>75721</v>
+        <v>80398</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9488</v>
+        <v>0.9509000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>1157</v>
       </c>
       <c r="C6" t="n">
-        <v>8761</v>
+        <v>9773</v>
       </c>
       <c r="D6" t="n">
-        <v>9918</v>
+        <v>10930</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8833</v>
+        <v>0.8941</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>4582</v>
       </c>
       <c r="C7" t="n">
-        <v>55256</v>
+        <v>61735</v>
       </c>
       <c r="D7" t="n">
-        <v>59838</v>
+        <v>66317</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9234</v>
+        <v>0.9309000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2205</v>
+        <v>2385</v>
       </c>
       <c r="D8" t="n">
-        <v>2217</v>
+        <v>2397</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9945999999999999</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16443</v>
+        <v>17301</v>
       </c>
       <c r="C9" t="n">
-        <v>144868</v>
+        <v>155566</v>
       </c>
       <c r="D9" t="n">
-        <v>161311</v>
+        <v>172867</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8981</v>
+        <v>0.8998999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F233"/>
+  <dimension ref="A1:F242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6044,8 +6044,216 @@
       </c>
       <c r="F233" s="2" t="n"/>
     </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>75</v>
+      </c>
+      <c r="D234" t="n">
+        <v>4602</v>
+      </c>
+      <c r="E234" t="n">
+        <v>4677</v>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>0.9840000000000001</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" s="2" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>0</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" s="2" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>0</v>
+      </c>
+      <c r="D238" t="n">
+        <v>1012</v>
+      </c>
+      <c r="E238" t="n">
+        <v>1012</v>
+      </c>
+      <c r="F238" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>0</v>
+      </c>
+      <c r="D239" t="n">
+        <v>6479</v>
+      </c>
+      <c r="E239" t="n">
+        <v>6479</v>
+      </c>
+      <c r="F239" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" t="n">
+        <v>180</v>
+      </c>
+      <c r="E240" t="n">
+        <v>180</v>
+      </c>
+      <c r="F240" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>858</v>
+      </c>
+      <c r="D241" t="n">
+        <v>10698</v>
+      </c>
+      <c r="E241" t="n">
+        <v>11556</v>
+      </c>
+      <c r="F241" s="2" t="n">
+        <v>0.9258</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>0</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+      <c r="F242" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F233"/>
+  <autoFilter ref="A1:F242"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$251</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3949</v>
+        <v>3955</v>
       </c>
       <c r="C2" t="n">
-        <v>76449</v>
+        <v>79733</v>
       </c>
       <c r="D2" t="n">
-        <v>80398</v>
+        <v>83688</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9509000000000001</v>
+        <v>0.9527</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>1157</v>
       </c>
       <c r="C6" t="n">
-        <v>9773</v>
+        <v>10343</v>
       </c>
       <c r="D6" t="n">
-        <v>10930</v>
+        <v>11500</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8941</v>
+        <v>0.8994</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>4582</v>
       </c>
       <c r="C7" t="n">
-        <v>61735</v>
+        <v>65717</v>
       </c>
       <c r="D7" t="n">
-        <v>66317</v>
+        <v>70299</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9309000000000001</v>
+        <v>0.9348000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2385</v>
+        <v>2433</v>
       </c>
       <c r="D8" t="n">
-        <v>2397</v>
+        <v>2445</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.995</v>
+        <v>0.9951000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17301</v>
+        <v>17708</v>
       </c>
       <c r="C9" t="n">
-        <v>155566</v>
+        <v>162672</v>
       </c>
       <c r="D9" t="n">
-        <v>172867</v>
+        <v>180380</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8998999999999999</v>
+        <v>0.9018</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F242"/>
+  <dimension ref="A1:F251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6252,8 +6252,216 @@
       </c>
       <c r="F242" s="2" t="n"/>
     </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>6</v>
+      </c>
+      <c r="D243" t="n">
+        <v>3284</v>
+      </c>
+      <c r="E243" t="n">
+        <v>3290</v>
+      </c>
+      <c r="F243" s="2" t="n">
+        <v>0.9982</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>0</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" t="n">
+        <v>0</v>
+      </c>
+      <c r="F244" s="2" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>0</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" s="2" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>0</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" s="2" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" t="n">
+        <v>570</v>
+      </c>
+      <c r="E247" t="n">
+        <v>570</v>
+      </c>
+      <c r="F247" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>0</v>
+      </c>
+      <c r="D248" t="n">
+        <v>3982</v>
+      </c>
+      <c r="E248" t="n">
+        <v>3982</v>
+      </c>
+      <c r="F248" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>0</v>
+      </c>
+      <c r="D249" t="n">
+        <v>48</v>
+      </c>
+      <c r="E249" t="n">
+        <v>48</v>
+      </c>
+      <c r="F249" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>407</v>
+      </c>
+      <c r="D250" t="n">
+        <v>7106</v>
+      </c>
+      <c r="E250" t="n">
+        <v>7513</v>
+      </c>
+      <c r="F250" s="2" t="n">
+        <v>0.9458</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>0</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F242"/>
+  <autoFilter ref="A1:F251"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$251</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$260</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3955</v>
+        <v>3961</v>
       </c>
       <c r="C2" t="n">
-        <v>79733</v>
+        <v>81911</v>
       </c>
       <c r="D2" t="n">
-        <v>83688</v>
+        <v>85872</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9527</v>
+        <v>0.9539</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>1157</v>
       </c>
       <c r="C6" t="n">
-        <v>10343</v>
+        <v>10734</v>
       </c>
       <c r="D6" t="n">
-        <v>11500</v>
+        <v>11891</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.8994</v>
+        <v>0.9026999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -569,13 +569,13 @@
         <v>4582</v>
       </c>
       <c r="C7" t="n">
-        <v>65717</v>
+        <v>69023</v>
       </c>
       <c r="D7" t="n">
-        <v>70299</v>
+        <v>73605</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9348000000000001</v>
+        <v>0.9377</v>
       </c>
     </row>
     <row r="8">
@@ -588,10 +588,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2433</v>
+        <v>2457</v>
       </c>
       <c r="D8" t="n">
-        <v>2445</v>
+        <v>2469</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0.9951000000000001</v>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17708</v>
+        <v>17942</v>
       </c>
       <c r="C9" t="n">
-        <v>162672</v>
+        <v>168494</v>
       </c>
       <c r="D9" t="n">
-        <v>180380</v>
+        <v>186436</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9018</v>
+        <v>0.9037999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F251"/>
+  <dimension ref="A1:F260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6460,8 +6460,216 @@
       </c>
       <c r="F251" s="2" t="n"/>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>6</v>
+      </c>
+      <c r="D252" t="n">
+        <v>2178</v>
+      </c>
+      <c r="E252" t="n">
+        <v>2184</v>
+      </c>
+      <c r="F252" s="2" t="n">
+        <v>0.9973000000000001</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>0</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" s="2" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>0</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" s="2" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>0</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" s="2" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>0</v>
+      </c>
+      <c r="D256" t="n">
+        <v>391</v>
+      </c>
+      <c r="E256" t="n">
+        <v>391</v>
+      </c>
+      <c r="F256" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>0</v>
+      </c>
+      <c r="D257" t="n">
+        <v>3306</v>
+      </c>
+      <c r="E257" t="n">
+        <v>3306</v>
+      </c>
+      <c r="F257" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>0</v>
+      </c>
+      <c r="D258" t="n">
+        <v>24</v>
+      </c>
+      <c r="E258" t="n">
+        <v>24</v>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>234</v>
+      </c>
+      <c r="D259" t="n">
+        <v>5822</v>
+      </c>
+      <c r="E259" t="n">
+        <v>6056</v>
+      </c>
+      <c r="F259" s="2" t="n">
+        <v>0.9614</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>0</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+      <c r="F260" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F251"/>
+  <autoFilter ref="A1:F260"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$260</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$269</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3961</v>
+        <v>4333</v>
       </c>
       <c r="C2" t="n">
-        <v>81911</v>
+        <v>83370</v>
       </c>
       <c r="D2" t="n">
-        <v>85872</v>
+        <v>87703</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9539</v>
+        <v>0.9506</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>1157</v>
       </c>
       <c r="C6" t="n">
-        <v>10734</v>
+        <v>11455</v>
       </c>
       <c r="D6" t="n">
-        <v>11891</v>
+        <v>12612</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.9083</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4582</v>
+        <v>4588</v>
       </c>
       <c r="C7" t="n">
-        <v>69023</v>
+        <v>71989</v>
       </c>
       <c r="D7" t="n">
-        <v>73605</v>
+        <v>76577</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9377</v>
+        <v>0.9401</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2457</v>
+        <v>2610</v>
       </c>
       <c r="D8" t="n">
-        <v>2469</v>
+        <v>2622</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9951000000000001</v>
+        <v>0.9954000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17942</v>
+        <v>18092</v>
       </c>
       <c r="C9" t="n">
-        <v>168494</v>
+        <v>173427</v>
       </c>
       <c r="D9" t="n">
-        <v>186436</v>
+        <v>191519</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9037999999999999</v>
+        <v>0.9055</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F260"/>
+  <dimension ref="A1:F269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6668,8 +6668,216 @@
       </c>
       <c r="F260" s="2" t="n"/>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>372</v>
+      </c>
+      <c r="D261" t="n">
+        <v>1459</v>
+      </c>
+      <c r="E261" t="n">
+        <v>1831</v>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>0.7968000000000001</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>0</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" s="2" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>0</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" s="2" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>0</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" s="2" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>0</v>
+      </c>
+      <c r="D265" t="n">
+        <v>721</v>
+      </c>
+      <c r="E265" t="n">
+        <v>721</v>
+      </c>
+      <c r="F265" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>6</v>
+      </c>
+      <c r="D266" t="n">
+        <v>2966</v>
+      </c>
+      <c r="E266" t="n">
+        <v>2972</v>
+      </c>
+      <c r="F266" s="2" t="n">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D267" t="n">
+        <v>153</v>
+      </c>
+      <c r="E267" t="n">
+        <v>153</v>
+      </c>
+      <c r="F267" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>150</v>
+      </c>
+      <c r="D268" t="n">
+        <v>4933</v>
+      </c>
+      <c r="E268" t="n">
+        <v>5083</v>
+      </c>
+      <c r="F268" s="2" t="n">
+        <v>0.9704999999999999</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>0</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0</v>
+      </c>
+      <c r="F269" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F260"/>
+  <autoFilter ref="A1:F269"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_painel_mensal.xlsx
+++ b/output/DROPOFF_painel_mensal.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Consolidado'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$269</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geral Diário'!$A$1:$F$278</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4333</v>
+        <v>4440</v>
       </c>
       <c r="C2" t="n">
-        <v>83370</v>
+        <v>85734</v>
       </c>
       <c r="D2" t="n">
-        <v>87703</v>
+        <v>90174</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9506</v>
+        <v>0.9508</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>1157</v>
       </c>
       <c r="C6" t="n">
-        <v>11455</v>
+        <v>12054</v>
       </c>
       <c r="D6" t="n">
-        <v>12612</v>
+        <v>13211</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9083</v>
+        <v>0.9124</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4588</v>
+        <v>4629</v>
       </c>
       <c r="C7" t="n">
-        <v>71989</v>
+        <v>75483</v>
       </c>
       <c r="D7" t="n">
-        <v>76577</v>
+        <v>80112</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9401</v>
+        <v>0.9422</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2610</v>
+        <v>2664</v>
       </c>
       <c r="D8" t="n">
-        <v>2622</v>
+        <v>2676</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.9954000000000001</v>
+        <v>0.9954999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18092</v>
+        <v>18471</v>
       </c>
       <c r="C9" t="n">
-        <v>173427</v>
+        <v>178469</v>
       </c>
       <c r="D9" t="n">
-        <v>191519</v>
+        <v>196940</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9055</v>
+        <v>0.9062</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F269"/>
+  <dimension ref="A1:F278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6876,8 +6876,216 @@
       </c>
       <c r="F269" s="2" t="n"/>
     </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>CHM-SP</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>107</v>
+      </c>
+      <c r="D270" t="n">
+        <v>2364</v>
+      </c>
+      <c r="E270" t="n">
+        <v>2471</v>
+      </c>
+      <c r="F270" s="2" t="n">
+        <v>0.9567</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>CLP-SP</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>0</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" s="2" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>F JND-SP</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>0</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" s="2" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>F S-JRG-SP</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>0</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" s="2" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ITUP-SP</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>0</v>
+      </c>
+      <c r="D274" t="n">
+        <v>599</v>
+      </c>
+      <c r="E274" t="n">
+        <v>599</v>
+      </c>
+      <c r="F274" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>JND 02-SP</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>41</v>
+      </c>
+      <c r="D275" t="n">
+        <v>3494</v>
+      </c>
+      <c r="E275" t="n">
+        <v>3535</v>
+      </c>
+      <c r="F275" s="2" t="n">
+        <v>0.9884000000000001</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>JND-SP</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>0</v>
+      </c>
+      <c r="D276" t="n">
+        <v>54</v>
+      </c>
+      <c r="E276" t="n">
+        <v>54</v>
+      </c>
+      <c r="F276" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>S-CSVD-SP</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>379</v>
+      </c>
+      <c r="D277" t="n">
+        <v>5042</v>
+      </c>
+      <c r="E277" t="n">
+        <v>5421</v>
+      </c>
+      <c r="F277" s="2" t="n">
+        <v>0.9301</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>S-FREG-SP</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>0</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F269"/>
+  <autoFilter ref="A1:F278"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>